--- a/indicadores/ARG-ESS_out.xlsx
+++ b/indicadores/ARG-ESS_out.xlsx
@@ -59,7 +59,7 @@
     <t xml:space="preserve">log</t>
   </si>
   <si>
-    <t xml:space="preserve">(0 1 1)(0 1 1)</t>
+    <t xml:space="preserve">(0 1 0)(0 1 1)</t>
   </si>
   <si>
     <t xml:space="preserve">Código</t>
@@ -110,13 +110,13 @@
     <t xml:space="preserve">Fecha</t>
   </si>
   <si>
-    <t xml:space="preserve">25/06/2026</t>
+    <t xml:space="preserve">01/10/2026</t>
   </si>
   <si>
     <t xml:space="preserve">Usuario</t>
   </si>
   <si>
-    <t xml:space="preserve">arodriguez</t>
+    <t xml:space="preserve">ysonder</t>
   </si>
   <si>
     <t xml:space="preserve">fecha</t>
@@ -1269,7 +1269,7 @@
       <c r="B11"/>
       <c r="C11"/>
       <c r="D11" t="n">
-        <v>0.566138820054058</v>
+        <v>0.562395345897271</v>
       </c>
       <c r="E11"/>
       <c r="F11"/>
@@ -1285,7 +1285,7 @@
       <c r="B12"/>
       <c r="C12"/>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12"/>
       <c r="F12"/>
@@ -1327,7 +1327,7 @@
       <c r="B15"/>
       <c r="C15"/>
       <c r="D15" t="n">
-        <v>0.320513163572201</v>
+        <v>0.312727342720219</v>
       </c>
       <c r="E15"/>
       <c r="F15"/>
@@ -1397,7 +1397,7 @@
       <c r="B20"/>
       <c r="C20"/>
       <c r="D20" t="n">
-        <v>0.00918669217091027</v>
+        <v>0.0170100967972124</v>
       </c>
       <c r="E20"/>
       <c r="F20"/>
@@ -1427,7 +1427,7 @@
       <c r="B22"/>
       <c r="C22"/>
       <c r="D22" t="n">
-        <v>0.601090922048891</v>
+        <v>0.560040593099971</v>
       </c>
       <c r="E22"/>
       <c r="F22"/>
@@ -1672,10 +1672,10 @@
         <v>1760.64557739452</v>
       </c>
       <c r="I2" s="9" t="n">
-        <v>1781.56149111148</v>
+        <v>1781.56149331555</v>
       </c>
       <c r="J2" s="10" t="n">
-        <v>1729.66080480816</v>
+        <v>1729.66080480683</v>
       </c>
       <c r="K2" s="11" t="n">
         <v>1775.24874755028</v>
@@ -1696,7 +1696,7 @@
         <v>1.00439540324969</v>
       </c>
       <c r="S2" s="19" t="n">
-        <v>0.99260358596082</v>
+        <v>0.992603584732812</v>
       </c>
     </row>
     <row r="3">
@@ -1725,10 +1725,10 @@
         <v>1771.99220927855</v>
       </c>
       <c r="I3" s="9" t="n">
-        <v>1812.37023936634</v>
+        <v>1812.37024001269</v>
       </c>
       <c r="J3" s="10" t="n">
-        <v>1757.34941931496</v>
+        <v>1757.34941931829</v>
       </c>
       <c r="K3" s="11" t="n">
         <v>1754.65547896032</v>
@@ -1753,7 +1753,7 @@
         <v>1.00173783722545</v>
       </c>
       <c r="S3" s="19" t="n">
-        <v>0.979419990875405</v>
+        <v>0.979419990526111</v>
       </c>
     </row>
     <row r="4">
@@ -1782,10 +1782,10 @@
         <v>1815.72686774121</v>
       </c>
       <c r="I4" s="9" t="n">
-        <v>1843.17504215647</v>
+        <v>1843.17504124372</v>
       </c>
       <c r="J4" s="10" t="n">
-        <v>1785.26597353546</v>
+        <v>1785.26597354347</v>
       </c>
       <c r="K4" s="11" t="n">
         <v>1732.50233872429</v>
@@ -1810,7 +1810,7 @@
         <v>1.00011996967783</v>
       </c>
       <c r="S4" s="19" t="n">
-        <v>0.985226393790547</v>
+        <v>0.985226394278435</v>
       </c>
     </row>
     <row r="5">
@@ -1839,10 +1839,10 @@
         <v>1860.95703972976</v>
       </c>
       <c r="I5" s="9" t="n">
-        <v>1873.9358822919</v>
+        <v>1873.93587981689</v>
       </c>
       <c r="J5" s="10" t="n">
-        <v>1813.62493748161</v>
+        <v>1813.6249374943</v>
       </c>
       <c r="K5" s="11" t="n">
         <v>1877.66958519149</v>
@@ -1867,7 +1867,7 @@
         <v>0.996082087039312</v>
       </c>
       <c r="S5" s="19" t="n">
-        <v>0.98918324236228</v>
+        <v>0.989183243668747</v>
       </c>
     </row>
     <row r="6">
@@ -1896,10 +1896,10 @@
         <v>1856.60744927745</v>
       </c>
       <c r="I6" s="9" t="n">
-        <v>1904.59558747363</v>
+        <v>1904.59558343199</v>
       </c>
       <c r="J6" s="10" t="n">
-        <v>1842.79308563638</v>
+        <v>1842.79308565368</v>
       </c>
       <c r="K6" s="11" t="n">
         <v>1843.59784997389</v>
@@ -1926,7 +1926,7 @@
         <v>0.996528854768895</v>
       </c>
       <c r="S6" s="19" t="n">
-        <v>0.971420341069899</v>
+        <v>0.971420343131295</v>
       </c>
     </row>
     <row r="7">
@@ -1955,10 +1955,10 @@
         <v>1824.37010523696</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>1935.09931896699</v>
+        <v>1935.09931335469</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v>1873.45741572127</v>
+        <v>1873.45741574303</v>
       </c>
       <c r="K7" s="11" t="n">
         <v>1835.78629559616</v>
@@ -1985,7 +1985,7 @@
         <v>1.00414065645182</v>
       </c>
       <c r="S7" s="19" t="n">
-        <v>0.946682259214294</v>
+        <v>0.946682261959922</v>
       </c>
     </row>
     <row r="8">
@@ -2014,10 +2014,10 @@
         <v>1812.52633916864</v>
       </c>
       <c r="I8" s="9" t="n">
-        <v>1965.35411445137</v>
+        <v>1965.35410726723</v>
       </c>
       <c r="J8" s="10" t="n">
-        <v>1906.3089492795</v>
+        <v>1906.30894930535</v>
       </c>
       <c r="K8" s="11" t="n">
         <v>1730.66717915826</v>
@@ -2044,7 +2044,7 @@
         <v>1.00744660195661</v>
       </c>
       <c r="S8" s="19" t="n">
-        <v>0.929106611335556</v>
+        <v>0.929106614731802</v>
       </c>
     </row>
     <row r="9">
@@ -2073,10 +2073,10 @@
         <v>1843.44643514561</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>1995.20494096654</v>
+        <v>1995.20493221576</v>
       </c>
       <c r="J9" s="10" t="n">
-        <v>1941.85035225364</v>
+        <v>1941.85035228289</v>
       </c>
       <c r="K9" s="11" t="n">
         <v>1843.25503147577</v>
@@ -2103,7 +2103,7 @@
         <v>1.005182977798</v>
       </c>
       <c r="S9" s="19" t="n">
-        <v>0.928727139274783</v>
+        <v>0.928727143348089</v>
       </c>
     </row>
     <row r="10">
@@ -2132,10 +2132,10 @@
         <v>1907.0072419922</v>
       </c>
       <c r="I10" s="9" t="n">
-        <v>2024.40124819273</v>
+        <v>2024.40123789137</v>
       </c>
       <c r="J10" s="10" t="n">
-        <v>1980.11537753571</v>
+        <v>1980.11537756726</v>
       </c>
       <c r="K10" s="11" t="n">
         <v>1912.96750624288</v>
@@ -2162,7 +2162,7 @@
         <v>1.00011552539216</v>
       </c>
       <c r="S10" s="19" t="n">
-        <v>0.942119331063614</v>
+        <v>0.942119335857675</v>
       </c>
     </row>
     <row r="11">
@@ -2191,10 +2191,10 @@
         <v>1961.23239831564</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>2052.59751711674</v>
+        <v>2052.59750529719</v>
       </c>
       <c r="J11" s="10" t="n">
-        <v>2020.64480141385</v>
+        <v>2020.644801446</v>
       </c>
       <c r="K11" s="11" t="n">
         <v>1959.72015504519</v>
@@ -2221,7 +2221,7 @@
         <v>1.000166185914</v>
       </c>
       <c r="S11" s="19" t="n">
-        <v>0.955646838289901</v>
+        <v>0.95564684379284</v>
       </c>
     </row>
     <row r="12">
@@ -2250,10 +2250,10 @@
         <v>2014.57756141362</v>
       </c>
       <c r="I12" s="9" t="n">
-        <v>2079.37858263665</v>
+        <v>2079.37856935404</v>
       </c>
       <c r="J12" s="10" t="n">
-        <v>2062.64366081972</v>
+        <v>2062.64366085003</v>
       </c>
       <c r="K12" s="11" t="n">
         <v>2013.82549372401</v>
@@ -2280,7 +2280,7 @@
         <v>1.00174498392577</v>
       </c>
       <c r="S12" s="19" t="n">
-        <v>0.970526956335467</v>
+        <v>0.970526962534975</v>
       </c>
     </row>
     <row r="13">
@@ -2309,10 +2309,10 @@
         <v>2090.01563239174</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>2104.27123129923</v>
+        <v>2104.27121663888</v>
       </c>
       <c r="J13" s="10" t="n">
-        <v>2105.01236945317</v>
+        <v>2105.01236947829</v>
       </c>
       <c r="K13" s="11" t="n">
         <v>2085.00072500881</v>
@@ -2339,7 +2339,7 @@
         <v>0.999579551006778</v>
       </c>
       <c r="S13" s="19" t="n">
-        <v>0.992807797944088</v>
+        <v>0.992807804860926</v>
       </c>
     </row>
     <row r="14">
@@ -2368,10 +2368,10 @@
         <v>2158.61881531001</v>
       </c>
       <c r="I14" s="9" t="n">
-        <v>2126.7612789707</v>
+        <v>2126.76126305638</v>
       </c>
       <c r="J14" s="10" t="n">
-        <v>2146.40725017852</v>
+        <v>2146.40725019405</v>
       </c>
       <c r="K14" s="11" t="n">
         <v>2172.72060595151</v>
@@ -2398,7 +2398,7 @@
         <v>1.0004781190168</v>
       </c>
       <c r="S14" s="19" t="n">
-        <v>1.01546464728794</v>
+        <v>1.01546465488655</v>
       </c>
     </row>
     <row r="15">
@@ -2427,10 +2427,10 @@
         <v>2231.26859147113</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>2146.32249745084</v>
+        <v>2146.32248045393</v>
       </c>
       <c r="J15" s="10" t="n">
-        <v>2185.38456763791</v>
+        <v>2185.38456763828</v>
       </c>
       <c r="K15" s="11" t="n">
         <v>2208.16163115073</v>
@@ -2457,7 +2457,7 @@
         <v>0.997740313029939</v>
       </c>
       <c r="S15" s="19" t="n">
-        <v>1.03722838741724</v>
+        <v>1.03722839563114</v>
       </c>
     </row>
     <row r="16">
@@ -2486,10 +2486,10 @@
         <v>2291.00911646623</v>
       </c>
       <c r="I16" s="9" t="n">
-        <v>2162.45738311879</v>
+        <v>2162.45736526823</v>
       </c>
       <c r="J16" s="10" t="n">
-        <v>2220.63215325233</v>
+        <v>2220.6321532307</v>
       </c>
       <c r="K16" s="11" t="n">
         <v>2320.89142607142</v>
@@ -2516,7 +2516,7 @@
         <v>0.997411680407171</v>
       </c>
       <c r="S16" s="19" t="n">
-        <v>1.05670487220751</v>
+        <v>1.05670488093035</v>
       </c>
     </row>
     <row r="17">
@@ -2545,10 +2545,10 @@
         <v>2303.53627422467</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>2174.70708181226</v>
+        <v>2174.70706340519</v>
       </c>
       <c r="J17" s="10" t="n">
-        <v>2250.95172376033</v>
+        <v>2250.95172370861</v>
       </c>
       <c r="K17" s="11" t="n">
         <v>2300.43013281991</v>
@@ -2575,7 +2575,7 @@
         <v>0.999734478264393</v>
       </c>
       <c r="S17" s="19" t="n">
-        <v>1.05895853953627</v>
+        <v>1.05895854849947</v>
       </c>
     </row>
     <row r="18">
@@ -2604,10 +2604,10 @@
         <v>2319.0340318488</v>
       </c>
       <c r="I18" s="9" t="n">
-        <v>2182.70861764412</v>
+        <v>2182.70859905702</v>
       </c>
       <c r="J18" s="10" t="n">
-        <v>2275.62114825111</v>
+        <v>2275.62114816005</v>
       </c>
       <c r="K18" s="11" t="n">
         <v>2294.97565208045</v>
@@ -2622,19 +2622,19 @@
         <v>2318.86298584789</v>
       </c>
       <c r="O18" s="15" t="n">
-        <v>0.0068970775211502</v>
+        <v>0.00689707752114998</v>
       </c>
       <c r="P18" s="16" t="n">
-        <v>0.0737212178231539</v>
+        <v>0.0737212178231534</v>
       </c>
       <c r="Q18" s="17" t="n">
-        <v>0.00692091713669307</v>
+        <v>0.00692091713669285</v>
       </c>
       <c r="R18" s="18" t="n">
         <v>0.999926242565413</v>
       </c>
       <c r="S18" s="19" t="n">
-        <v>1.0623786276845</v>
+        <v>1.06237863673131</v>
       </c>
     </row>
     <row r="19">
@@ -2654,7 +2654,7 @@
         <v>2074.47075910088</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>0.869773347800401</v>
+        <v>0.869773347800402</v>
       </c>
       <c r="G19" s="7" t="n">
         <v>1</v>
@@ -2663,37 +2663,37 @@
         <v>2354.81514801591</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>2186.17759163411</v>
+        <v>2186.17757333431</v>
       </c>
       <c r="J19" s="10" t="n">
-        <v>2294.16568785917</v>
+        <v>2294.16568771862</v>
       </c>
       <c r="K19" s="11" t="n">
-        <v>2385.07050641076</v>
+        <v>2385.07050641075</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>2385.07050641076</v>
+        <v>2385.07050641075</v>
       </c>
       <c r="M19" s="13" t="n">
-        <v>2348.76495904353</v>
+        <v>2348.76495904352</v>
       </c>
       <c r="N19" s="14" t="n">
-        <v>2348.76495904353</v>
+        <v>2348.76495904352</v>
       </c>
       <c r="O19" s="15" t="n">
-        <v>0.0128126674266385</v>
+        <v>0.0128126674266383</v>
       </c>
       <c r="P19" s="16" t="n">
-        <v>0.0550430647420648</v>
+        <v>0.0550430647420643</v>
       </c>
       <c r="Q19" s="17" t="n">
-        <v>0.0128951013398064</v>
+        <v>0.0128951013398062</v>
       </c>
       <c r="R19" s="18" t="n">
         <v>0.997430715961938</v>
       </c>
       <c r="S19" s="19" t="n">
-        <v>1.07437061290519</v>
+        <v>1.0743706218984</v>
       </c>
     </row>
     <row r="20">
@@ -2722,10 +2722,10 @@
         <v>2346.92948857003</v>
       </c>
       <c r="I20" s="9" t="n">
-        <v>2184.89977169851</v>
+        <v>2184.8997542558</v>
       </c>
       <c r="J20" s="10" t="n">
-        <v>2306.20737623813</v>
+        <v>2306.20737603752</v>
       </c>
       <c r="K20" s="11" t="n">
         <v>2329.94317127214</v>
@@ -2740,19 +2740,19 @@
         <v>2336.45703444793</v>
       </c>
       <c r="O20" s="15" t="n">
-        <v>-0.00525394652589188</v>
+        <v>-0.00525394652589166</v>
       </c>
       <c r="P20" s="16" t="n">
-        <v>0.0224840261907231</v>
+        <v>0.0224840261907227</v>
       </c>
       <c r="Q20" s="17" t="n">
-        <v>-0.00524016868874411</v>
+        <v>-0.00524016868874388</v>
       </c>
       <c r="R20" s="18" t="n">
         <v>0.995537806238702</v>
       </c>
       <c r="S20" s="19" t="n">
-        <v>1.06936577353001</v>
+        <v>1.06936578206708</v>
       </c>
     </row>
     <row r="21">
@@ -2781,10 +2781,10 @@
         <v>2294.61439283767</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>2178.78523382533</v>
+        <v>2178.78521792341</v>
       </c>
       <c r="J21" s="10" t="n">
-        <v>2311.8227711344</v>
+        <v>2311.82277086341</v>
       </c>
       <c r="K21" s="11" t="n">
         <v>2300.87128883667</v>
@@ -2799,19 +2799,19 @@
         <v>2292.37019651742</v>
       </c>
       <c r="O21" s="15" t="n">
-        <v>-0.019049391522318</v>
+        <v>-0.0190493915223175</v>
       </c>
       <c r="P21" s="16" t="n">
         <v>-0.00458305868807563</v>
       </c>
       <c r="Q21" s="17" t="n">
-        <v>-0.0188690985027773</v>
+        <v>-0.0188690985027768</v>
       </c>
       <c r="R21" s="18" t="n">
         <v>0.999021972350887</v>
       </c>
       <c r="S21" s="19" t="n">
-        <v>1.05213224365977</v>
+        <v>1.05213225133878</v>
       </c>
     </row>
     <row r="22">
@@ -2840,10 +2840,10 @@
         <v>2231.15104945891</v>
       </c>
       <c r="I22" s="9" t="n">
-        <v>2167.8347061273</v>
+        <v>2167.83469257469</v>
       </c>
       <c r="J22" s="10" t="n">
-        <v>2311.20710926954</v>
+        <v>2311.20710891914</v>
       </c>
       <c r="K22" s="11" t="n">
         <v>2237.79503712421</v>
@@ -2861,7 +2861,7 @@
         <v>-0.0250846026815214</v>
       </c>
       <c r="P22" s="16" t="n">
-        <v>-0.035914478736682</v>
+        <v>-0.0359144787366816</v>
       </c>
       <c r="Q22" s="17" t="n">
         <v>-0.024772598315192</v>
@@ -2870,7 +2870,7 @@
         <v>1.0019860515457</v>
       </c>
       <c r="S22" s="19" t="n">
-        <v>1.03125124075677</v>
+        <v>1.03125124720383</v>
       </c>
     </row>
     <row r="23">
@@ -2896,13 +2896,13 @@
         <v>1</v>
       </c>
       <c r="H23" s="8" t="n">
-        <v>2182.97523299183</v>
+        <v>2182.97523299182</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>2152.12522050155</v>
+        <v>2152.12521024149</v>
       </c>
       <c r="J23" s="10" t="n">
-        <v>2304.50086995363</v>
+        <v>2304.50086951739</v>
       </c>
       <c r="K23" s="11" t="n">
         <v>2165.86755871242</v>
@@ -2917,19 +2917,19 @@
         <v>2192.56423378053</v>
       </c>
       <c r="O23" s="15" t="n">
-        <v>-0.0194299580493702</v>
+        <v>-0.01942995804937</v>
       </c>
       <c r="P23" s="16" t="n">
-        <v>-0.066503344517964</v>
+        <v>-0.0665033445179632</v>
       </c>
       <c r="Q23" s="17" t="n">
-        <v>-0.0192424130425292</v>
+        <v>-0.0192424130425289</v>
       </c>
       <c r="R23" s="18" t="n">
         <v>1.00439262921713</v>
       </c>
       <c r="S23" s="19" t="n">
-        <v>1.01879026968029</v>
+        <v>1.01879027453728</v>
       </c>
     </row>
     <row r="24">
@@ -2949,7 +2949,7 @@
         <v>2098.32520367766</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>0.953469200357192</v>
+        <v>0.953469200357191</v>
       </c>
       <c r="G24" s="7" t="n">
         <v>1</v>
@@ -2958,10 +2958,10 @@
         <v>2183.98489379688</v>
       </c>
       <c r="I24" s="9" t="n">
-        <v>2131.77753405208</v>
+        <v>2131.77752817102</v>
       </c>
       <c r="J24" s="10" t="n">
-        <v>2291.47747213602</v>
+        <v>2291.47747161191</v>
       </c>
       <c r="K24" s="11" t="n">
         <v>2200.72678057307</v>
@@ -2976,19 +2976,19 @@
         <v>2197.21465100989</v>
       </c>
       <c r="O24" s="15" t="n">
-        <v>0.00211874861631252</v>
+        <v>0.00211874861631274</v>
       </c>
       <c r="P24" s="16" t="n">
-        <v>-0.0595955249273145</v>
+        <v>-0.0595955249273137</v>
       </c>
       <c r="Q24" s="17" t="n">
-        <v>0.00212099475021299</v>
+        <v>0.00212099475021321</v>
       </c>
       <c r="R24" s="18" t="n">
         <v>1.00605762304061</v>
       </c>
       <c r="S24" s="19" t="n">
-        <v>1.03069603460612</v>
+        <v>1.03069603744956</v>
       </c>
     </row>
     <row r="25">
@@ -3017,10 +3017,10 @@
         <v>2252.74044292679</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>2106.92099284425</v>
+        <v>2106.9209925783</v>
       </c>
       <c r="J25" s="10" t="n">
-        <v>2271.21716820987</v>
+        <v>2271.21716760238</v>
       </c>
       <c r="K25" s="11" t="n">
         <v>2201.75704791857</v>
@@ -3029,25 +3029,25 @@
         <v>2221.53748418098</v>
       </c>
       <c r="M25" s="13" t="n">
-        <v>2249.24029580154</v>
+        <v>2249.24029580153</v>
       </c>
       <c r="N25" s="14" t="n">
-        <v>2249.24029580154</v>
+        <v>2249.24029580153</v>
       </c>
       <c r="O25" s="15" t="n">
-        <v>0.0234020223899127</v>
+        <v>0.0234020223899106</v>
       </c>
       <c r="P25" s="16" t="n">
-        <v>-0.0188145443442819</v>
+        <v>-0.0188145443442835</v>
       </c>
       <c r="Q25" s="17" t="n">
-        <v>0.0236779983092397</v>
+        <v>0.0236779983092374</v>
       </c>
       <c r="R25" s="18" t="n">
-        <v>0.998446271457396</v>
+        <v>0.998446271457394</v>
       </c>
       <c r="S25" s="19" t="n">
-        <v>1.06754847639785</v>
+        <v>1.06754847653261</v>
       </c>
     </row>
     <row r="26">
@@ -3067,25 +3067,25 @@
         <v>2878.0472386878</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>1.21923217155114</v>
+        <v>1.21923217155115</v>
       </c>
       <c r="G26" s="7" t="n">
-        <v>0.834599830389808</v>
+        <v>0.83459983038981</v>
       </c>
       <c r="H26" s="8" t="n">
         <v>2315.91367766713</v>
       </c>
       <c r="I26" s="9" t="n">
-        <v>2077.72803622252</v>
+        <v>2077.72804296107</v>
       </c>
       <c r="J26" s="10" t="n">
-        <v>2242.34645711049</v>
+        <v>2242.34645643331</v>
       </c>
       <c r="K26" s="11" t="n">
-        <v>2360.54076150752</v>
+        <v>2360.5407615075</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>2353.15943427111</v>
+        <v>2353.1594342711</v>
       </c>
       <c r="M26" s="13" t="n">
         <v>2308.71789463234</v>
@@ -3094,19 +3094,19 @@
         <v>2308.71789463234</v>
       </c>
       <c r="O26" s="15" t="n">
-        <v>0.0260998335916515</v>
+        <v>0.0260998335916497</v>
       </c>
       <c r="P26" s="16" t="n">
-        <v>0.0327143699689656</v>
+        <v>0.0327143699689618</v>
       </c>
       <c r="Q26" s="17" t="n">
-        <v>0.0264434168913972</v>
+        <v>0.0264434168913954</v>
       </c>
       <c r="R26" s="18" t="n">
-        <v>0.996892896698104</v>
+        <v>0.996892896698101</v>
       </c>
       <c r="S26" s="19" t="n">
-        <v>1.11117425109678</v>
+        <v>1.11117424749299</v>
       </c>
     </row>
     <row r="27">
@@ -3135,10 +3135,10 @@
         <v>2316.98853854445</v>
       </c>
       <c r="I27" s="9" t="n">
-        <v>2044.44273883844</v>
+        <v>2044.44275412434</v>
       </c>
       <c r="J27" s="10" t="n">
-        <v>2203.24343935308</v>
+        <v>2203.24343863212</v>
       </c>
       <c r="K27" s="11" t="n">
         <v>2307.01522580618</v>
@@ -3153,19 +3153,19 @@
         <v>2313.57323878201</v>
       </c>
       <c r="O27" s="15" t="n">
-        <v>0.00210083951672225</v>
+        <v>0.00210083951672403</v>
       </c>
       <c r="P27" s="16" t="n">
-        <v>0.0551906316527073</v>
+        <v>0.0551906316527053</v>
       </c>
       <c r="Q27" s="17" t="n">
-        <v>0.00210304782622361</v>
+        <v>0.00210304782622539</v>
       </c>
       <c r="R27" s="18" t="n">
-        <v>0.998525974684113</v>
+        <v>0.998525974684111</v>
       </c>
       <c r="S27" s="19" t="n">
-        <v>1.13164002827317</v>
+        <v>1.13164001981212</v>
       </c>
     </row>
     <row r="28">
@@ -3194,10 +3194,10 @@
         <v>2292.52747883232</v>
       </c>
       <c r="I28" s="9" t="n">
-        <v>2007.48131996731</v>
+        <v>2007.48134549268</v>
       </c>
       <c r="J28" s="10" t="n">
-        <v>2152.84028033862</v>
+        <v>2152.84027961538</v>
       </c>
       <c r="K28" s="11" t="n">
         <v>2287.1030692446</v>
@@ -3212,19 +3212,19 @@
         <v>2311.23685247284</v>
       </c>
       <c r="O28" s="15" t="n">
-        <v>-0.00101037078791494</v>
+        <v>-0.00101037078791316</v>
       </c>
       <c r="P28" s="16" t="n">
-        <v>0.0518939746786007</v>
+        <v>0.0518939746786002</v>
       </c>
       <c r="Q28" s="17" t="n">
-        <v>-0.00100986053521301</v>
+        <v>-0.00100986053521124</v>
       </c>
       <c r="R28" s="18" t="n">
         <v>1.00816102481356</v>
       </c>
       <c r="S28" s="19" t="n">
-        <v>1.15131176040556</v>
+        <v>1.15131174576649</v>
       </c>
     </row>
     <row r="29">
@@ -3244,7 +3244,7 @@
         <v>2112.86602822575</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>0.952874437844268</v>
+        <v>0.952874437844267</v>
       </c>
       <c r="G29" s="7" t="n">
         <v>0</v>
@@ -3253,10 +3253,10 @@
         <v>2363.72604559601</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>1967.42410668882</v>
+        <v>1967.42414428548</v>
       </c>
       <c r="J29" s="10" t="n">
-        <v>2090.58800440037</v>
+        <v>2090.58800373556</v>
       </c>
       <c r="K29" s="11" t="n">
         <v>2217.36038276542</v>
@@ -3271,19 +3271,19 @@
         <v>2368.44945259941</v>
       </c>
       <c r="O29" s="15" t="n">
-        <v>0.0244526864185055</v>
+        <v>0.0244526864185066</v>
       </c>
       <c r="P29" s="16" t="n">
-        <v>0.0529997426332751</v>
+        <v>0.052999742633278</v>
       </c>
       <c r="Q29" s="17" t="n">
-        <v>0.0247541051733191</v>
+        <v>0.0247541051733202</v>
       </c>
       <c r="R29" s="18" t="n">
         <v>1.00199828868163</v>
       </c>
       <c r="S29" s="19" t="n">
-        <v>1.20383268891907</v>
+        <v>1.20383266591433</v>
       </c>
     </row>
     <row r="30">
@@ -3306,43 +3306,43 @@
         <v>1.19162939212284</v>
       </c>
       <c r="G30" s="7" t="n">
-        <v>0.872461918316871</v>
+        <v>0.872461918317158</v>
       </c>
       <c r="H30" s="8" t="n">
-        <v>2429.79789895375</v>
+        <v>2429.79789895376</v>
       </c>
       <c r="I30" s="9" t="n">
-        <v>1925.02618967593</v>
+        <v>1925.02624129945</v>
       </c>
       <c r="J30" s="10" t="n">
-        <v>2016.60894981612</v>
+        <v>2016.60894929326</v>
       </c>
       <c r="K30" s="11" t="n">
         <v>2463.54693760987</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>2459.24264996101</v>
+        <v>2459.24264996103</v>
       </c>
       <c r="M30" s="13" t="n">
-        <v>2400.54154181529</v>
+        <v>2400.5415418153</v>
       </c>
       <c r="N30" s="14" t="n">
-        <v>2400.54154181529</v>
+        <v>2400.5415418153</v>
       </c>
       <c r="O30" s="15" t="n">
-        <v>0.0134588526940009</v>
+        <v>0.0134588526940025</v>
       </c>
       <c r="P30" s="16" t="n">
-        <v>0.0397725713463877</v>
+        <v>0.0397725713463941</v>
       </c>
       <c r="Q30" s="17" t="n">
-        <v>0.0135498307471422</v>
+        <v>0.0135498307471438</v>
       </c>
       <c r="R30" s="18" t="n">
-        <v>0.987959345445538</v>
+        <v>0.987959345445537</v>
       </c>
       <c r="S30" s="19" t="n">
-        <v>1.24701760146931</v>
+        <v>1.24701756802798</v>
       </c>
     </row>
     <row r="31">
@@ -3362,7 +3362,7 @@
         <v>2085.81764439801</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>0.899076837552728</v>
+        <v>0.899076837552727</v>
       </c>
       <c r="G31" s="7" t="n">
         <v>1</v>
@@ -3371,10 +3371,10 @@
         <v>2307.53924736258</v>
       </c>
       <c r="I31" s="9" t="n">
-        <v>1881.29034831345</v>
+        <v>1881.29041601965</v>
       </c>
       <c r="J31" s="10" t="n">
-        <v>1932.39114506962</v>
+        <v>1932.3911447984</v>
       </c>
       <c r="K31" s="11" t="n">
         <v>2319.95482174313</v>
@@ -3389,19 +3389,19 @@
         <v>2268.47340378073</v>
       </c>
       <c r="O31" s="15" t="n">
-        <v>-0.0565872584137486</v>
+        <v>-0.0565872584137488</v>
       </c>
       <c r="P31" s="16" t="n">
-        <v>-0.0194935843159345</v>
+        <v>-0.0194935843159304</v>
       </c>
       <c r="Q31" s="17" t="n">
-        <v>-0.0550159769093992</v>
+        <v>-0.0550159769093994</v>
       </c>
       <c r="R31" s="18" t="n">
-        <v>0.983070344902474</v>
+        <v>0.983070344902477</v>
       </c>
       <c r="S31" s="19" t="n">
-        <v>1.20580717687431</v>
+        <v>1.20580713347823</v>
       </c>
     </row>
     <row r="32">
@@ -3421,7 +3421,7 @@
         <v>1894.04001281739</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>0.959133225211607</v>
+        <v>0.959133225211605</v>
       </c>
       <c r="G32" s="7" t="n">
         <v>1</v>
@@ -3430,37 +3430,37 @@
         <v>1984.39953936685</v>
       </c>
       <c r="I32" s="9" t="n">
-        <v>1837.55324727382</v>
+        <v>1837.55333318653</v>
       </c>
       <c r="J32" s="10" t="n">
-        <v>1841.63578714537</v>
+        <v>1841.63578726421</v>
       </c>
       <c r="K32" s="11" t="n">
-        <v>1974.74132167564</v>
+        <v>1974.74132167565</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>1974.74132167564</v>
+        <v>1974.74132167565</v>
       </c>
       <c r="M32" s="13" t="n">
-        <v>1973.19864809583</v>
+        <v>1973.19864809584</v>
       </c>
       <c r="N32" s="14" t="n">
-        <v>1973.19864809583</v>
+        <v>1973.19864809584</v>
       </c>
       <c r="O32" s="15" t="n">
-        <v>-0.139451190665419</v>
+        <v>-0.13945119066542</v>
       </c>
       <c r="P32" s="16" t="n">
-        <v>-0.146258573203061</v>
+        <v>-0.146258573203059</v>
       </c>
       <c r="Q32" s="17" t="n">
-        <v>-0.130164521740823</v>
+        <v>-0.130164521740824</v>
       </c>
       <c r="R32" s="18" t="n">
-        <v>0.994355526168591</v>
+        <v>0.994355526168592</v>
       </c>
       <c r="S32" s="19" t="n">
-        <v>1.07381848717758</v>
+        <v>1.07381843697243</v>
       </c>
     </row>
     <row r="33">
@@ -3486,13 +3486,13 @@
         <v>1</v>
       </c>
       <c r="H33" s="8" t="n">
-        <v>1620.24163556229</v>
+        <v>1620.24163556228</v>
       </c>
       <c r="I33" s="9" t="n">
-        <v>1795.42571652543</v>
+        <v>1795.42582279411</v>
       </c>
       <c r="J33" s="10" t="n">
-        <v>1749.98189141122</v>
+        <v>1749.98189208867</v>
       </c>
       <c r="K33" s="11" t="n">
         <v>1623.35712728892</v>
@@ -3501,25 +3501,25 @@
         <v>1623.35712728892</v>
       </c>
       <c r="M33" s="13" t="n">
-        <v>1644.4417714242</v>
+        <v>1644.44177142421</v>
       </c>
       <c r="N33" s="14" t="n">
-        <v>1644.4417714242</v>
+        <v>1644.44177142421</v>
       </c>
       <c r="O33" s="15" t="n">
-        <v>-0.1822549272971</v>
+        <v>-0.182254927297101</v>
       </c>
       <c r="P33" s="16" t="n">
-        <v>-0.305688466511537</v>
+        <v>-0.305688466511538</v>
       </c>
       <c r="Q33" s="17" t="n">
         <v>-0.166611140236126</v>
       </c>
       <c r="R33" s="18" t="n">
-        <v>1.01493612763106</v>
+        <v>1.01493612763107</v>
       </c>
       <c r="S33" s="19" t="n">
-        <v>0.915906325886091</v>
+        <v>0.915906271674906</v>
       </c>
     </row>
     <row r="34">
@@ -3548,10 +3548,10 @@
         <v>1356.31150944334</v>
       </c>
       <c r="I34" s="9" t="n">
-        <v>1756.60432858311</v>
+        <v>1756.60445732924</v>
       </c>
       <c r="J34" s="10" t="n">
-        <v>1663.73400090767</v>
+        <v>1663.7340023418</v>
       </c>
       <c r="K34" s="11" t="n">
         <v>1276.78822092102</v>
@@ -3569,7 +3569,7 @@
         <v>-0.165903630132125</v>
       </c>
       <c r="P34" s="16" t="n">
-        <v>-0.419692420491352</v>
+        <v>-0.419692420491353</v>
       </c>
       <c r="Q34" s="17" t="n">
         <v>-0.152872132143478</v>
@@ -3578,7 +3578,7 @@
         <v>1.02708886707931</v>
       </c>
       <c r="S34" s="19" t="n">
-        <v>0.79303712792535</v>
+        <v>0.793037069801588</v>
       </c>
     </row>
     <row r="35">
@@ -3598,19 +3598,19 @@
         <v>1124.55064572027</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>0.909661595862145</v>
+        <v>0.909661595862143</v>
       </c>
       <c r="G35" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H35" s="8" t="n">
-        <v>1226.10512660255</v>
+        <v>1226.10512660256</v>
       </c>
       <c r="I35" s="9" t="n">
-        <v>1722.67811309348</v>
+        <v>1722.67826634406</v>
       </c>
       <c r="J35" s="10" t="n">
-        <v>1588.56353485462</v>
+        <v>1588.56353726965</v>
       </c>
       <c r="K35" s="11" t="n">
         <v>1236.22966038756</v>
@@ -3625,19 +3625,19 @@
         <v>1255.14399169789</v>
       </c>
       <c r="O35" s="15" t="n">
-        <v>-0.10424704739224</v>
+        <v>-0.104247047392233</v>
       </c>
       <c r="P35" s="16" t="n">
-        <v>-0.446701032683031</v>
+        <v>-0.446701032683029</v>
       </c>
       <c r="Q35" s="17" t="n">
-        <v>-0.0989973204386306</v>
+        <v>-0.0989973204386246</v>
       </c>
       <c r="R35" s="18" t="n">
         <v>1.02368382976735</v>
       </c>
       <c r="S35" s="19" t="n">
-        <v>0.728600417081968</v>
+        <v>0.728600352265204</v>
       </c>
     </row>
     <row r="36">
@@ -3657,46 +3657,46 @@
         <v>1152.15904543455</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>0.966734418302199</v>
+        <v>0.966734418302174</v>
       </c>
       <c r="G36" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H36" s="8" t="n">
-        <v>1196.45173875525</v>
+        <v>1196.45173875535</v>
       </c>
       <c r="I36" s="9" t="n">
-        <v>1694.98591669114</v>
+        <v>1694.9860962983</v>
       </c>
       <c r="J36" s="10" t="n">
-        <v>1528.60480001465</v>
+        <v>1528.60480365373</v>
       </c>
       <c r="K36" s="11" t="n">
-        <v>1191.80513657308</v>
+        <v>1191.80513657312</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>1191.80513657308</v>
+        <v>1191.80513657312</v>
       </c>
       <c r="M36" s="13" t="n">
-        <v>1209.78595673258</v>
+        <v>1209.78595673261</v>
       </c>
       <c r="N36" s="14" t="n">
-        <v>1209.78595673258</v>
+        <v>1209.78595673261</v>
       </c>
       <c r="O36" s="15" t="n">
-        <v>-0.0368068517243733</v>
+        <v>-0.036806851724357</v>
       </c>
       <c r="P36" s="16" t="n">
-        <v>-0.386890945876106</v>
+        <v>-0.386890945876092</v>
       </c>
       <c r="Q36" s="17" t="n">
-        <v>-0.0361377142904095</v>
+        <v>-0.0361377142903937</v>
       </c>
       <c r="R36" s="18" t="n">
-        <v>1.0111448022059</v>
+        <v>1.01114480220584</v>
       </c>
       <c r="S36" s="19" t="n">
-        <v>0.713743957881527</v>
+        <v>0.713743882250526</v>
       </c>
     </row>
     <row r="37">
@@ -3716,46 +3716,46 @@
         <v>1203.71436422561</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>0.987214402204881</v>
+        <v>0.98721440220484</v>
       </c>
       <c r="G37" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H37" s="8" t="n">
-        <v>1210.93719858975</v>
+        <v>1210.93719858969</v>
       </c>
       <c r="I37" s="9" t="n">
-        <v>1674.5625557278</v>
+        <v>1674.56276327294</v>
       </c>
       <c r="J37" s="10" t="n">
-        <v>1486.23043377799</v>
+        <v>1486.23043889119</v>
       </c>
       <c r="K37" s="11" t="n">
-        <v>1219.30389339661</v>
+        <v>1219.30389339666</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>1219.30389339661</v>
+        <v>1219.30389339666</v>
       </c>
       <c r="M37" s="13" t="n">
-        <v>1224.92526010845</v>
+        <v>1224.92526010826</v>
       </c>
       <c r="N37" s="14" t="n">
-        <v>1224.92526010845</v>
+        <v>1224.92526010826</v>
       </c>
       <c r="O37" s="15" t="n">
-        <v>0.012436381280492</v>
+        <v>0.0124363812803201</v>
       </c>
       <c r="P37" s="16" t="n">
-        <v>-0.255111806696827</v>
+        <v>-0.255111806696938</v>
       </c>
       <c r="Q37" s="17" t="n">
-        <v>0.0125140346452279</v>
+        <v>0.0125140346450539</v>
       </c>
       <c r="R37" s="18" t="n">
-        <v>1.01155143432292</v>
+        <v>1.01155143432282</v>
       </c>
       <c r="S37" s="19" t="n">
-        <v>0.731489699156725</v>
+        <v>0.731489608495858</v>
       </c>
     </row>
     <row r="38">
@@ -3775,46 +3775,46 @@
         <v>1425.89524509937</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>1.12338185942661</v>
+        <v>1.12338185942737</v>
       </c>
       <c r="G38" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H38" s="8" t="n">
-        <v>1282.77625807403</v>
+        <v>1282.7762580723</v>
       </c>
       <c r="I38" s="9" t="n">
-        <v>1662.12835856756</v>
+        <v>1662.12859524916</v>
       </c>
       <c r="J38" s="10" t="n">
-        <v>1462.12907521768</v>
+        <v>1462.12908204374</v>
       </c>
       <c r="K38" s="11" t="n">
-        <v>1269.28811706749</v>
+        <v>1269.28811706663</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>1269.28811706749</v>
+        <v>1269.28811706663</v>
       </c>
       <c r="M38" s="13" t="n">
-        <v>1291.0366340788</v>
+        <v>1291.03663407787</v>
       </c>
       <c r="N38" s="14" t="n">
-        <v>1291.0366340788</v>
+        <v>1291.03663407787</v>
       </c>
       <c r="O38" s="15" t="n">
-        <v>0.0525656579962992</v>
+        <v>0.052565657995723</v>
       </c>
       <c r="P38" s="16" t="n">
-        <v>-0.0732318567343461</v>
+        <v>-0.0732318567350182</v>
       </c>
       <c r="Q38" s="17" t="n">
-        <v>0.0539717614807802</v>
+        <v>0.0539717614801729</v>
       </c>
       <c r="R38" s="18" t="n">
-        <v>1.00643945189411</v>
+        <v>1.00643945189474</v>
       </c>
       <c r="S38" s="19" t="n">
-        <v>0.776737023602337</v>
+        <v>0.776736912996995</v>
       </c>
     </row>
     <row r="39">
@@ -3834,46 +3834,46 @@
         <v>1290.38528816145</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>0.917596609078922</v>
+        <v>0.917596609080276</v>
       </c>
       <c r="G39" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H39" s="8" t="n">
-        <v>1403.09826440125</v>
+        <v>1403.09826440156</v>
       </c>
       <c r="I39" s="9" t="n">
-        <v>1658.11911691057</v>
+        <v>1658.11938341445</v>
       </c>
       <c r="J39" s="10" t="n">
-        <v>1455.65473070483</v>
+        <v>1455.65473944564</v>
       </c>
       <c r="K39" s="11" t="n">
-        <v>1406.26640878363</v>
+        <v>1406.26640878155</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>1406.26640878363</v>
+        <v>1406.26640878155</v>
       </c>
       <c r="M39" s="13" t="n">
-        <v>1398.21816742928</v>
+        <v>1398.21816743024</v>
       </c>
       <c r="N39" s="14" t="n">
-        <v>1398.21816742928</v>
+        <v>1398.21816743024</v>
       </c>
       <c r="O39" s="15" t="n">
-        <v>0.0797532004770873</v>
+        <v>0.0797532004784974</v>
       </c>
       <c r="P39" s="16" t="n">
-        <v>0.113990248670875</v>
+        <v>0.113990248671631</v>
       </c>
       <c r="Q39" s="17" t="n">
-        <v>0.083019745932275</v>
+        <v>0.0830197459338022</v>
       </c>
       <c r="R39" s="18" t="n">
-        <v>0.996521913613763</v>
+        <v>0.996521913614226</v>
       </c>
       <c r="S39" s="19" t="n">
-        <v>0.843255561780425</v>
+        <v>0.84325542624741</v>
       </c>
     </row>
     <row r="40">
@@ -3893,46 +3893,46 @@
         <v>1470.49652561565</v>
       </c>
       <c r="F40" s="6" t="n">
-        <v>0.973160939149098</v>
+        <v>0.973160939143403</v>
       </c>
       <c r="G40" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H40" s="8" t="n">
-        <v>1495.26012878051</v>
+        <v>1495.26012879122</v>
       </c>
       <c r="I40" s="9" t="n">
-        <v>1662.72509730606</v>
+        <v>1662.72539365743</v>
       </c>
       <c r="J40" s="10" t="n">
-        <v>1465.19720181982</v>
+        <v>1465.19721260624</v>
       </c>
       <c r="K40" s="11" t="n">
-        <v>1511.05173508239</v>
+        <v>1511.05173509123</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>1511.05173508239</v>
+        <v>1511.05173509123</v>
       </c>
       <c r="M40" s="13" t="n">
-        <v>1483.99351266427</v>
+        <v>1483.99351267116</v>
       </c>
       <c r="N40" s="14" t="n">
-        <v>1483.99351266427</v>
+        <v>1483.99351267116</v>
       </c>
       <c r="O40" s="15" t="n">
-        <v>0.0595380847632135</v>
+        <v>0.0595380847671655</v>
       </c>
       <c r="P40" s="16" t="n">
-        <v>0.226657909529943</v>
+        <v>0.226657909535603</v>
       </c>
       <c r="Q40" s="17" t="n">
-        <v>0.0613461813278353</v>
+        <v>0.0613461813320297</v>
       </c>
       <c r="R40" s="18" t="n">
-        <v>0.992465112993132</v>
+        <v>0.992465112990626</v>
       </c>
       <c r="S40" s="19" t="n">
-        <v>0.892506834153546</v>
+        <v>0.892506675084139</v>
       </c>
     </row>
     <row r="41">
@@ -3952,46 +3952,46 @@
         <v>1506.23806134637</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>0.999093853421243</v>
+        <v>0.999093853413345</v>
       </c>
       <c r="G41" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H41" s="8" t="n">
-        <v>1520.18026157801</v>
+        <v>1520.18026157686</v>
       </c>
       <c r="I41" s="9" t="n">
-        <v>1675.97915836065</v>
+        <v>1675.97948375759</v>
       </c>
       <c r="J41" s="10" t="n">
-        <v>1488.89934853342</v>
+        <v>1488.8993613816</v>
       </c>
       <c r="K41" s="11" t="n">
-        <v>1507.60417170868</v>
+        <v>1507.6041717206</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>1507.60417170868</v>
+        <v>1507.6041717206</v>
       </c>
       <c r="M41" s="13" t="n">
-        <v>1515.30262777842</v>
+        <v>1515.30262777702</v>
       </c>
       <c r="N41" s="14" t="n">
-        <v>1515.30262777842</v>
+        <v>1515.30262777702</v>
       </c>
       <c r="O41" s="15" t="n">
-        <v>0.0208784001066833</v>
+        <v>0.0208784001011205</v>
       </c>
       <c r="P41" s="16" t="n">
-        <v>0.237057212490065</v>
+        <v>0.237057212489103</v>
       </c>
       <c r="Q41" s="17" t="n">
-        <v>0.0210978786948581</v>
+        <v>0.021097878689178</v>
       </c>
       <c r="R41" s="18" t="n">
-        <v>0.996791410911673</v>
+        <v>0.996791410911505</v>
       </c>
       <c r="S41" s="19" t="n">
-        <v>0.904129756160336</v>
+        <v>0.904129580619726</v>
       </c>
     </row>
     <row r="42">
@@ -4011,46 +4011,46 @@
         <v>1689.82206595359</v>
       </c>
       <c r="F42" s="6" t="n">
-        <v>1.10089683031388</v>
+        <v>1.10089683034134</v>
       </c>
       <c r="G42" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H42" s="8" t="n">
-        <v>1524.68175925254</v>
+        <v>1524.68175922532</v>
       </c>
       <c r="I42" s="9" t="n">
-        <v>1697.8193628296</v>
+        <v>1697.81971545783</v>
       </c>
       <c r="J42" s="10" t="n">
-        <v>1525.13330348269</v>
+        <v>1525.13331824018</v>
       </c>
       <c r="K42" s="11" t="n">
-        <v>1534.95043261392</v>
+        <v>1534.95043257564</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>1534.95043261392</v>
+        <v>1534.95043257564</v>
       </c>
       <c r="M42" s="13" t="n">
-        <v>1534.58697547355</v>
+        <v>1534.5869754551</v>
       </c>
       <c r="N42" s="14" t="n">
-        <v>1534.58697547355</v>
+        <v>1534.5869754551</v>
       </c>
       <c r="O42" s="15" t="n">
-        <v>0.0126461001579471</v>
+        <v>0.0126461001468484</v>
       </c>
       <c r="P42" s="16" t="n">
-        <v>0.188647118885615</v>
+        <v>0.188647118872184</v>
       </c>
       <c r="Q42" s="17" t="n">
-        <v>0.0127264002197378</v>
+        <v>0.0127264002084979</v>
       </c>
       <c r="R42" s="18" t="n">
-        <v>1.00649657947365</v>
+        <v>1.00649657947952</v>
       </c>
       <c r="S42" s="19" t="n">
-        <v>0.903857624120856</v>
+        <v>0.903857436383513</v>
       </c>
     </row>
     <row r="43">
@@ -4070,46 +4070,46 @@
         <v>1445.19764128156</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>0.925908477866382</v>
+        <v>0.92590847787181</v>
       </c>
       <c r="G43" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H43" s="8" t="n">
-        <v>1576.54392873864</v>
+        <v>1576.54392874005</v>
       </c>
       <c r="I43" s="9" t="n">
-        <v>1728.0785391015</v>
+        <v>1728.07891593098</v>
       </c>
       <c r="J43" s="10" t="n">
-        <v>1572.36472342061</v>
+        <v>1572.36473970215</v>
       </c>
       <c r="K43" s="11" t="n">
-        <v>1560.84286495767</v>
+        <v>1560.84286494852</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>1560.84286495767</v>
+        <v>1560.84286494852</v>
       </c>
       <c r="M43" s="13" t="n">
-        <v>1587.37988248048</v>
+        <v>1587.37988248663</v>
       </c>
       <c r="N43" s="14" t="n">
-        <v>1587.37988248048</v>
+        <v>1587.37988248663</v>
       </c>
       <c r="O43" s="15" t="n">
-        <v>0.0338235108625443</v>
+        <v>0.0338235108784444</v>
       </c>
       <c r="P43" s="16" t="n">
-        <v>0.135287696482292</v>
+        <v>0.135287696485914</v>
       </c>
       <c r="Q43" s="17" t="n">
-        <v>0.0344020298951393</v>
+        <v>0.0344020299115864</v>
       </c>
       <c r="R43" s="18" t="n">
-        <v>1.00687323299041</v>
+        <v>1.00687323299342</v>
       </c>
       <c r="S43" s="19" t="n">
-        <v>0.91858086687763</v>
+        <v>0.918580666573004</v>
       </c>
     </row>
     <row r="44">
@@ -4129,46 +4129,46 @@
         <v>1649.16622342598</v>
       </c>
       <c r="F44" s="6" t="n">
-        <v>0.974175926818855</v>
+        <v>0.974175926772128</v>
       </c>
       <c r="G44" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H44" s="8" t="n">
-        <v>1690.86540285764</v>
+        <v>1690.86540294014</v>
       </c>
       <c r="I44" s="9" t="n">
-        <v>1766.48772248355</v>
+        <v>1766.48811904811</v>
       </c>
       <c r="J44" s="10" t="n">
-        <v>1629.10835074577</v>
+        <v>1629.10836785935</v>
       </c>
       <c r="K44" s="11" t="n">
-        <v>1692.88336739267</v>
+        <v>1692.88336747387</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>1692.88336739267</v>
+        <v>1692.88336747387</v>
       </c>
       <c r="M44" s="13" t="n">
-        <v>1692.86247575298</v>
+        <v>1692.862475809</v>
       </c>
       <c r="N44" s="14" t="n">
-        <v>1692.86247575298</v>
+        <v>1692.862475809</v>
       </c>
       <c r="O44" s="15" t="n">
-        <v>0.0643360844119153</v>
+        <v>0.0643360844411337</v>
       </c>
       <c r="P44" s="16" t="n">
-        <v>0.140747894991613</v>
+        <v>0.140747895024075</v>
       </c>
       <c r="Q44" s="17" t="n">
-        <v>0.0664507560141605</v>
+        <v>0.0664507560453205</v>
       </c>
       <c r="R44" s="18" t="n">
-        <v>1.0011810951315</v>
+        <v>1.00118109511579</v>
       </c>
       <c r="S44" s="19" t="n">
-        <v>0.958321110419573</v>
+        <v>0.958320895314723</v>
       </c>
     </row>
     <row r="45">
@@ -4188,46 +4188,46 @@
         <v>1834.94060897935</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>1.00553489841952</v>
+        <v>1.00553489838048</v>
       </c>
       <c r="G45" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H45" s="8" t="n">
-        <v>1815.76599813184</v>
+        <v>1815.76599813483</v>
       </c>
       <c r="I45" s="9" t="n">
-        <v>1812.67342598662</v>
+        <v>1812.67383614841</v>
       </c>
       <c r="J45" s="10" t="n">
-        <v>1693.82131856448</v>
+        <v>1693.82133542986</v>
       </c>
       <c r="K45" s="11" t="n">
-        <v>1824.84030326891</v>
+        <v>1824.84030333976</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>1824.84030326891</v>
+        <v>1824.84030333976</v>
       </c>
       <c r="M45" s="13" t="n">
-        <v>1806.07089443793</v>
+        <v>1806.07089445832</v>
       </c>
       <c r="N45" s="14" t="n">
-        <v>1806.07089443793</v>
+        <v>1806.07089445832</v>
       </c>
       <c r="O45" s="15" t="n">
-        <v>0.0647328404186689</v>
+        <v>0.0647328403968639</v>
       </c>
       <c r="P45" s="16" t="n">
-        <v>0.191887918181603</v>
+        <v>0.191887918196162</v>
       </c>
       <c r="Q45" s="17" t="n">
-        <v>0.0668739607064663</v>
+        <v>0.0668739606832032</v>
       </c>
       <c r="R45" s="18" t="n">
-        <v>0.994660598500093</v>
+        <v>0.994660598509685</v>
       </c>
       <c r="S45" s="19" t="n">
-        <v>0.996357572492635</v>
+        <v>0.996357347053611</v>
       </c>
     </row>
     <row r="46">
@@ -4247,46 +4247,46 @@
         <v>1933.00273454338</v>
       </c>
       <c r="F46" s="6" t="n">
-        <v>1.08672517818172</v>
+        <v>1.08672517830914</v>
       </c>
       <c r="G46" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H46" s="8" t="n">
-        <v>1881.71960382125</v>
+        <v>1881.71960367991</v>
       </c>
       <c r="I46" s="9" t="n">
-        <v>1866.21615989963</v>
+        <v>1866.21657560134</v>
       </c>
       <c r="J46" s="10" t="n">
-        <v>1765.27963506627</v>
+        <v>1765.27965012981</v>
       </c>
       <c r="K46" s="11" t="n">
-        <v>1778.74109604935</v>
+        <v>1778.74109584079</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>1881.71960382125</v>
+        <v>1881.71960367991</v>
       </c>
       <c r="M46" s="13" t="n">
-        <v>1868.43026782004</v>
+        <v>1868.43026775642</v>
       </c>
       <c r="N46" s="14" t="n">
-        <v>1868.43026782004</v>
+        <v>1868.43026775642</v>
       </c>
       <c r="O46" s="15" t="n">
-        <v>0.0339449402021037</v>
+        <v>0.0339449401567613</v>
       </c>
       <c r="P46" s="16" t="n">
-        <v>0.217546022273174</v>
+        <v>0.217546022246353</v>
       </c>
       <c r="Q46" s="17" t="n">
-        <v>0.0345276442769498</v>
+        <v>0.0345276442300417</v>
       </c>
       <c r="R46" s="18" t="n">
-        <v>0.992937664052485</v>
+        <v>0.992937664093255</v>
       </c>
       <c r="S46" s="19" t="n">
-        <v>1.00118641557606</v>
+        <v>1.00118619252664</v>
       </c>
     </row>
     <row r="47">
@@ -4306,46 +4306,46 @@
         <v>1888.09456688716</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>0.935898062565543</v>
+        <v>0.935898062588538</v>
       </c>
       <c r="G47" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H47" s="8" t="n">
-        <v>1885.44156036875</v>
+        <v>1885.44156032608</v>
       </c>
       <c r="I47" s="9" t="n">
-        <v>1926.70403880985</v>
+        <v>1926.70444981835</v>
       </c>
       <c r="J47" s="10" t="n">
-        <v>1842.91440336419</v>
+        <v>1842.91441451491</v>
       </c>
       <c r="K47" s="11" t="n">
-        <v>2017.41476172244</v>
+        <v>2017.41476167288</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>1885.44156036875</v>
+        <v>1885.44156032608</v>
       </c>
       <c r="M47" s="13" t="n">
-        <v>1882.13005537053</v>
+        <v>1882.13005537985</v>
       </c>
       <c r="N47" s="14" t="n">
-        <v>1882.13005537053</v>
+        <v>1882.13005537985</v>
       </c>
       <c r="O47" s="15" t="n">
-        <v>0.00730549427284955</v>
+        <v>0.00730549431185633</v>
       </c>
       <c r="P47" s="16" t="n">
-        <v>0.185683449905806</v>
+        <v>0.185683449907084</v>
       </c>
       <c r="Q47" s="17" t="n">
-        <v>0.0073322444976629</v>
+        <v>0.00733224453695569</v>
       </c>
       <c r="R47" s="18" t="n">
-        <v>0.998243644848068</v>
+        <v>0.998243644875605</v>
       </c>
       <c r="S47" s="19" t="n">
-        <v>0.976865163231374</v>
+        <v>0.976864954849355</v>
       </c>
     </row>
     <row r="48">
@@ -4365,46 +4365,46 @@
         <v>1827.0050126273</v>
       </c>
       <c r="F48" s="6" t="n">
-        <v>0.973926100494134</v>
+        <v>0.973926100357084</v>
       </c>
       <c r="G48" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H48" s="8" t="n">
-        <v>1899.24725122733</v>
+        <v>1899.24725151055</v>
       </c>
       <c r="I48" s="9" t="n">
-        <v>1993.73486695694</v>
+        <v>1993.73526060345</v>
       </c>
       <c r="J48" s="10" t="n">
-        <v>1926.73892641507</v>
+        <v>1926.7389309086</v>
       </c>
       <c r="K48" s="11" t="n">
-        <v>1875.91749692337</v>
+        <v>1875.91749718735</v>
       </c>
       <c r="L48" s="12" t="n">
-        <v>1875.91749692337</v>
+        <v>1875.91749718735</v>
       </c>
       <c r="M48" s="13" t="n">
-        <v>1901.01907210635</v>
+        <v>1901.01907231005</v>
       </c>
       <c r="N48" s="14" t="n">
-        <v>1901.01907210635</v>
+        <v>1901.01907231005</v>
       </c>
       <c r="O48" s="15" t="n">
-        <v>0.00998595247800682</v>
+        <v>0.00998595258020569</v>
       </c>
       <c r="P48" s="16" t="n">
-        <v>0.122961315130327</v>
+        <v>0.122961315213491</v>
       </c>
       <c r="Q48" s="17" t="n">
-        <v>0.0100359784818893</v>
+        <v>0.0100359785851138</v>
       </c>
       <c r="R48" s="18" t="n">
-        <v>1.00093290690713</v>
+        <v>1.00093290686512</v>
       </c>
       <c r="S48" s="19" t="n">
-        <v>0.953496427038914</v>
+        <v>0.953496238881112</v>
       </c>
     </row>
     <row r="49">
@@ -4424,46 +4424,46 @@
         <v>1977.85475412658</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>1.00562081625516</v>
+        <v>1.00562081608668</v>
       </c>
       <c r="G49" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H49" s="8" t="n">
-        <v>1942.45703142052</v>
+        <v>1942.45703160879</v>
       </c>
       <c r="I49" s="9" t="n">
-        <v>2066.88065953157</v>
+        <v>2066.88102045471</v>
       </c>
       <c r="J49" s="10" t="n">
-        <v>2016.97914296076</v>
+        <v>2016.97913736338</v>
       </c>
       <c r="K49" s="11" t="n">
-        <v>1966.79973420989</v>
+        <v>1966.79973453941</v>
       </c>
       <c r="L49" s="12" t="n">
-        <v>1966.79973420989</v>
+        <v>1966.79973453941</v>
       </c>
       <c r="M49" s="13" t="n">
-        <v>1953.47061660227</v>
+        <v>1953.4706167092</v>
       </c>
       <c r="N49" s="14" t="n">
-        <v>1953.47061660227</v>
+        <v>1953.4706167092</v>
       </c>
       <c r="O49" s="15" t="n">
-        <v>0.0272174978618555</v>
+        <v>0.0272174978094447</v>
       </c>
       <c r="P49" s="16" t="n">
-        <v>0.0816134752064666</v>
+        <v>0.0816134752534652</v>
       </c>
       <c r="Q49" s="17" t="n">
-        <v>0.0275912773656728</v>
+        <v>0.0275912773118159</v>
       </c>
       <c r="R49" s="18" t="n">
-        <v>1.0056699247415</v>
+        <v>1.00566992469908</v>
       </c>
       <c r="S49" s="19" t="n">
-        <v>0.945129854301791</v>
+        <v>0.945129689312955</v>
       </c>
     </row>
     <row r="50">
@@ -4483,46 +4483,46 @@
         <v>2160.36159801246</v>
       </c>
       <c r="F50" s="6" t="n">
-        <v>1.07782816899592</v>
+        <v>1.07782816926224</v>
       </c>
       <c r="G50" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H50" s="8" t="n">
-        <v>2031.37412934923</v>
+        <v>2031.37412875433</v>
       </c>
       <c r="I50" s="9" t="n">
-        <v>2145.63979586813</v>
+        <v>2145.64010576806</v>
       </c>
       <c r="J50" s="10" t="n">
-        <v>2113.60688459564</v>
+        <v>2113.60686476316</v>
       </c>
       <c r="K50" s="11" t="n">
-        <v>2004.36550106591</v>
+        <v>2004.36550057065</v>
       </c>
       <c r="L50" s="12" t="n">
-        <v>2004.36550106591</v>
+        <v>2004.36550057065</v>
       </c>
       <c r="M50" s="13" t="n">
-        <v>2032.57435215072</v>
+        <v>2032.57435175253</v>
       </c>
       <c r="N50" s="14" t="n">
-        <v>2032.57435215072</v>
+        <v>2032.57435175253</v>
       </c>
       <c r="O50" s="15" t="n">
-        <v>0.0396955494065331</v>
+        <v>0.0396955491558837</v>
       </c>
       <c r="P50" s="16" t="n">
-        <v>0.087851330155444</v>
+        <v>0.0878513299793704</v>
       </c>
       <c r="Q50" s="17" t="n">
-        <v>0.0404939469660643</v>
+        <v>0.0404939467052652</v>
       </c>
       <c r="R50" s="18" t="n">
-        <v>1.00059084281135</v>
+        <v>1.00059084290836</v>
       </c>
       <c r="S50" s="19" t="n">
-        <v>0.947304555063186</v>
+        <v>0.947304418056142</v>
       </c>
     </row>
     <row r="51">
@@ -4542,46 +4542,46 @@
         <v>2033.21078101257</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>0.943587446003581</v>
+        <v>0.943587446411616</v>
       </c>
       <c r="G51" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H51" s="8" t="n">
-        <v>2130.76088721351</v>
+        <v>2130.76088699259</v>
       </c>
       <c r="I51" s="9" t="n">
-        <v>2229.44810472267</v>
+        <v>2229.44834213573</v>
       </c>
       <c r="J51" s="10" t="n">
-        <v>2216.34308587037</v>
+        <v>2216.3430469777</v>
       </c>
       <c r="K51" s="11" t="n">
-        <v>2154.76667226118</v>
+        <v>2154.7666713294</v>
       </c>
       <c r="L51" s="12" t="n">
-        <v>2154.76667226118</v>
+        <v>2154.7666713294</v>
       </c>
       <c r="M51" s="13" t="n">
-        <v>2132.55554335949</v>
+        <v>2132.55554318369</v>
       </c>
       <c r="N51" s="14" t="n">
-        <v>2132.55554335949</v>
+        <v>2132.55554318369</v>
       </c>
       <c r="O51" s="15" t="n">
-        <v>0.0480179027738232</v>
+        <v>0.0480179028872925</v>
       </c>
       <c r="P51" s="16" t="n">
-        <v>0.133054295198353</v>
+        <v>0.133054295099333</v>
       </c>
       <c r="Q51" s="17" t="n">
-        <v>0.0491894385575502</v>
+        <v>0.049189438676601</v>
       </c>
       <c r="R51" s="18" t="n">
-        <v>1.00084226069511</v>
+        <v>1.00084226071637</v>
       </c>
       <c r="S51" s="19" t="n">
-        <v>0.956539665059738</v>
+        <v>0.95653956311936</v>
       </c>
     </row>
     <row r="52">
@@ -4601,46 +4601,46 @@
         <v>2167.47837936594</v>
       </c>
       <c r="F52" s="6" t="n">
-        <v>0.97796127132265</v>
+        <v>0.977961270592105</v>
       </c>
       <c r="G52" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H52" s="8" t="n">
-        <v>2221.35218985207</v>
+        <v>2221.35219065315</v>
       </c>
       <c r="I52" s="9" t="n">
-        <v>2317.65311841702</v>
+        <v>2317.65325852172</v>
       </c>
       <c r="J52" s="10" t="n">
-        <v>2324.36247441793</v>
+        <v>2324.36241105581</v>
       </c>
       <c r="K52" s="11" t="n">
-        <v>2216.3233278497</v>
+        <v>2216.32332950531</v>
       </c>
       <c r="L52" s="12" t="n">
-        <v>2216.3233278497</v>
+        <v>2216.32332950531</v>
       </c>
       <c r="M52" s="13" t="n">
-        <v>2225.42620138575</v>
+        <v>2225.42620203593</v>
       </c>
       <c r="N52" s="14" t="n">
-        <v>2225.42620138575</v>
+        <v>2225.42620203593</v>
       </c>
       <c r="O52" s="15" t="n">
-        <v>0.0426274022906919</v>
+        <v>0.0426274026652907</v>
       </c>
       <c r="P52" s="16" t="n">
-        <v>0.170649066092723</v>
+        <v>0.170649066309303</v>
       </c>
       <c r="Q52" s="17" t="n">
-        <v>0.0435489984377868</v>
+        <v>0.043548998828699</v>
       </c>
       <c r="R52" s="18" t="n">
-        <v>1.00183402323697</v>
+        <v>1.00183402316838</v>
       </c>
       <c r="S52" s="19" t="n">
-        <v>0.960206764205394</v>
+        <v>0.960206706440372</v>
       </c>
     </row>
     <row r="53">
@@ -4660,46 +4660,46 @@
         <v>2312.92176137013</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>0.999408148789573</v>
+        <v>0.99940814869401</v>
       </c>
       <c r="G53" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H53" s="8" t="n">
-        <v>2327.8001369125</v>
+        <v>2327.80013761855</v>
       </c>
       <c r="I53" s="9" t="n">
-        <v>2409.5556933777</v>
+        <v>2409.55570784576</v>
       </c>
       <c r="J53" s="10" t="n">
-        <v>2436.53189580326</v>
+        <v>2436.53180216808</v>
       </c>
       <c r="K53" s="11" t="n">
-        <v>2314.29147758242</v>
+        <v>2314.29147780371</v>
       </c>
       <c r="L53" s="12" t="n">
-        <v>2314.29147758242</v>
+        <v>2314.29147780371</v>
       </c>
       <c r="M53" s="13" t="n">
-        <v>2337.58627578624</v>
+        <v>2337.58627615018</v>
       </c>
       <c r="N53" s="14" t="n">
-        <v>2337.58627578624</v>
+        <v>2337.58627615018</v>
       </c>
       <c r="O53" s="15" t="n">
-        <v>0.0491704424676108</v>
+        <v>0.0491704423311444</v>
       </c>
       <c r="P53" s="16" t="n">
-        <v>0.196632422274195</v>
+        <v>0.196632422394998</v>
       </c>
       <c r="Q53" s="17" t="n">
-        <v>0.050399368143794</v>
+        <v>0.0503993680004498</v>
       </c>
       <c r="R53" s="18" t="n">
-        <v>1.00420402882471</v>
+        <v>1.00420402867647</v>
       </c>
       <c r="S53" s="19" t="n">
-        <v>0.970131664609679</v>
+        <v>0.970131658935615</v>
       </c>
     </row>
     <row r="54">
@@ -4719,46 +4719,46 @@
         <v>2696.86049566001</v>
       </c>
       <c r="F54" s="6" t="n">
-        <v>1.07640245452876</v>
+        <v>1.07640245480475</v>
       </c>
       <c r="G54" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H54" s="8" t="n">
-        <v>2491.07623199219</v>
+        <v>2491.07623042344</v>
       </c>
       <c r="I54" s="9" t="n">
-        <v>2504.39335491212</v>
+        <v>2504.39321182195</v>
       </c>
       <c r="J54" s="10" t="n">
-        <v>2551.17799985847</v>
+        <v>2551.17787007732</v>
       </c>
       <c r="K54" s="11" t="n">
-        <v>2505.43882013041</v>
+        <v>2505.43881948801</v>
       </c>
       <c r="L54" s="12" t="n">
-        <v>2505.43882013041</v>
+        <v>2505.43881948801</v>
       </c>
       <c r="M54" s="13" t="n">
-        <v>2496.93177433051</v>
+        <v>2496.93177332839</v>
       </c>
       <c r="N54" s="14" t="n">
-        <v>2496.93177433051</v>
+        <v>2496.93177332839</v>
       </c>
       <c r="O54" s="15" t="n">
-        <v>0.0659437969420579</v>
+        <v>0.0659437963850227</v>
       </c>
       <c r="P54" s="16" t="n">
-        <v>0.228457779017254</v>
+        <v>0.228457778764888</v>
       </c>
       <c r="Q54" s="17" t="n">
-        <v>0.0681666812450301</v>
+        <v>0.0681666806500236</v>
       </c>
       <c r="R54" s="18" t="n">
-        <v>1.00235060744554</v>
+        <v>1.00235060767448</v>
       </c>
       <c r="S54" s="19" t="n">
-        <v>0.997020603585704</v>
+        <v>0.997020660150995</v>
       </c>
     </row>
     <row r="55">
@@ -4778,46 +4778,46 @@
         <v>2516.13485121782</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>0.945006595390775</v>
+        <v>0.945006596436021</v>
       </c>
       <c r="G55" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H55" s="8" t="n">
-        <v>2671.90894083506</v>
+        <v>2671.90894012879</v>
       </c>
       <c r="I55" s="9" t="n">
-        <v>2601.34408819285</v>
+        <v>2601.34375202062</v>
       </c>
       <c r="J55" s="10" t="n">
-        <v>2666.01623432455</v>
+        <v>2666.01606292453</v>
       </c>
       <c r="K55" s="11" t="n">
-        <v>2662.55797947882</v>
+        <v>2662.55797653384</v>
       </c>
       <c r="L55" s="12" t="n">
-        <v>2662.55797947882</v>
+        <v>2662.55797653384</v>
       </c>
       <c r="M55" s="13" t="n">
-        <v>2671.15028262202</v>
+        <v>2671.15028196892</v>
       </c>
       <c r="N55" s="14" t="n">
-        <v>2671.15028262202</v>
+        <v>2671.15028196892</v>
       </c>
       <c r="O55" s="15" t="n">
-        <v>0.0674465092294979</v>
+        <v>0.0674465093863366</v>
       </c>
       <c r="P55" s="16" t="n">
-        <v>0.252558364043385</v>
+        <v>0.25255836384039</v>
       </c>
       <c r="Q55" s="17" t="n">
-        <v>0.0697730350835151</v>
+        <v>0.0697730352512969</v>
       </c>
       <c r="R55" s="18" t="n">
-        <v>0.9997160613517</v>
+        <v>0.999716061371524</v>
       </c>
       <c r="S55" s="19" t="n">
-        <v>1.02683466395161</v>
+        <v>1.02683479639862</v>
       </c>
     </row>
     <row r="56">
@@ -4837,46 +4837,46 @@
         <v>2803.88411969971</v>
       </c>
       <c r="F56" s="6" t="n">
-        <v>0.98242417062508</v>
+        <v>0.982424169275746</v>
       </c>
       <c r="G56" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H56" s="8" t="n">
-        <v>2842.79402753187</v>
+        <v>2842.79402885735</v>
       </c>
       <c r="I56" s="9" t="n">
-        <v>2699.58653180817</v>
+        <v>2699.58596351688</v>
       </c>
       <c r="J56" s="10" t="n">
-        <v>2778.53335104386</v>
+        <v>2778.53313359775</v>
       </c>
       <c r="K56" s="11" t="n">
-        <v>2854.04635140003</v>
+        <v>2854.04635531999</v>
       </c>
       <c r="L56" s="12" t="n">
-        <v>2854.04635140003</v>
+        <v>2854.04635531999</v>
       </c>
       <c r="M56" s="13" t="n">
-        <v>2847.90020648769</v>
+        <v>2847.90020772884</v>
       </c>
       <c r="N56" s="14" t="n">
-        <v>2847.90020648769</v>
+        <v>2847.90020772884</v>
       </c>
       <c r="O56" s="15" t="n">
-        <v>0.0640727559805762</v>
+        <v>0.0640727566608912</v>
       </c>
       <c r="P56" s="16" t="n">
-        <v>0.279710019013135</v>
+        <v>0.279710019196968</v>
       </c>
       <c r="Q56" s="17" t="n">
-        <v>0.0661699661810746</v>
+        <v>0.066169966906406</v>
       </c>
       <c r="R56" s="18" t="n">
-        <v>1.00179618322902</v>
+        <v>1.00179618319852</v>
       </c>
       <c r="S56" s="19" t="n">
-        <v>1.05493940384277</v>
+        <v>1.05493962637839</v>
       </c>
     </row>
     <row r="57">
@@ -4896,46 +4896,46 @@
         <v>3010.33905330945</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>0.996487499012638</v>
+        <v>0.996487498989654</v>
       </c>
       <c r="G57" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H57" s="8" t="n">
-        <v>3034.64093968749</v>
+        <v>3034.6409420002</v>
       </c>
       <c r="I57" s="9" t="n">
-        <v>2798.33758302846</v>
+        <v>2798.33674027616</v>
       </c>
       <c r="J57" s="10" t="n">
-        <v>2886.19881058453</v>
+        <v>2886.1985445531</v>
       </c>
       <c r="K57" s="11" t="n">
-        <v>3020.95014367187</v>
+        <v>3020.95014374154</v>
       </c>
       <c r="L57" s="12" t="n">
-        <v>3020.95014367187</v>
+        <v>3020.95014374154</v>
       </c>
       <c r="M57" s="13" t="n">
-        <v>3038.37703435034</v>
+        <v>3038.37703560412</v>
       </c>
       <c r="N57" s="14" t="n">
-        <v>3038.37703435034</v>
+        <v>3038.37703560412</v>
       </c>
       <c r="O57" s="15" t="n">
-        <v>0.064741549500191</v>
+        <v>0.0647415494770242</v>
       </c>
       <c r="P57" s="16" t="n">
-        <v>0.299792467907264</v>
+        <v>0.299792468241247</v>
       </c>
       <c r="Q57" s="17" t="n">
-        <v>0.0668832522392242</v>
+        <v>0.066883252214508</v>
       </c>
       <c r="R57" s="18" t="n">
-        <v>1.00123114883675</v>
+        <v>1.00123114848686</v>
       </c>
       <c r="S57" s="19" t="n">
-        <v>1.08577930439047</v>
+        <v>1.08577963183383</v>
       </c>
     </row>
     <row r="58">
@@ -4955,46 +4955,46 @@
         <v>3500.76983696121</v>
       </c>
       <c r="F58" s="6" t="n">
-        <v>1.07465963064821</v>
+        <v>1.0746596303329</v>
       </c>
       <c r="G58" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H58" s="8" t="n">
-        <v>3256.79647329729</v>
+        <v>3256.79647246786</v>
       </c>
       <c r="I58" s="9" t="n">
-        <v>2896.91067651132</v>
+        <v>2896.90951400878</v>
       </c>
       <c r="J58" s="10" t="n">
-        <v>2986.85963851648</v>
+        <v>2986.85932435526</v>
       </c>
       <c r="K58" s="11" t="n">
-        <v>3257.5614986576</v>
+        <v>3257.56149961339</v>
       </c>
       <c r="L58" s="12" t="n">
-        <v>3257.5614986576</v>
+        <v>3257.56149961339</v>
       </c>
       <c r="M58" s="13" t="n">
-        <v>3251.94752420705</v>
+        <v>3251.94752257282</v>
       </c>
       <c r="N58" s="14" t="n">
-        <v>3251.94752420705</v>
+        <v>3251.94752257282</v>
       </c>
       <c r="O58" s="15" t="n">
-        <v>0.0679305525085143</v>
+        <v>0.0679305515933285</v>
       </c>
       <c r="P58" s="16" t="n">
-        <v>0.302377404796722</v>
+        <v>0.302377404664923</v>
       </c>
       <c r="Q58" s="17" t="n">
-        <v>0.0702909768742288</v>
+        <v>0.0702909758947137</v>
       </c>
       <c r="R58" s="18" t="n">
-        <v>0.998511129224685</v>
+        <v>0.998511128977191</v>
       </c>
       <c r="S58" s="19" t="n">
-        <v>1.12255705727292</v>
+        <v>1.12255750718038</v>
       </c>
     </row>
     <row r="59">
@@ -5014,46 +5014,46 @@
         <v>3286.26557559881</v>
       </c>
       <c r="F59" s="6" t="n">
-        <v>0.946582229311556</v>
+        <v>0.946582231634082</v>
       </c>
       <c r="G59" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H59" s="8" t="n">
-        <v>3484.64702324328</v>
+        <v>3484.64701363752</v>
       </c>
       <c r="I59" s="9" t="n">
-        <v>2994.75837976477</v>
+        <v>2994.75684980222</v>
       </c>
       <c r="J59" s="10" t="n">
-        <v>3079.03661707504</v>
+        <v>3079.03625956491</v>
       </c>
       <c r="K59" s="11" t="n">
-        <v>3471.71695584112</v>
+        <v>3471.71694732294</v>
       </c>
       <c r="L59" s="12" t="n">
-        <v>3471.71695584112</v>
+        <v>3471.71694732294</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>3446.62981382275</v>
+        <v>3446.62980522555</v>
       </c>
       <c r="N59" s="14" t="n">
-        <v>3446.62981382275</v>
+        <v>3446.62980522555</v>
       </c>
       <c r="O59" s="15" t="n">
-        <v>0.0581428329528561</v>
+        <v>0.0581428309610145</v>
       </c>
       <c r="P59" s="16" t="n">
-        <v>0.290316698482243</v>
+        <v>0.290316695579186</v>
       </c>
       <c r="Q59" s="17" t="n">
-        <v>0.059866368742582</v>
+        <v>0.059866366631496</v>
       </c>
       <c r="R59" s="18" t="n">
-        <v>0.989090083108291</v>
+        <v>0.989090083367644</v>
       </c>
       <c r="S59" s="19" t="n">
-        <v>1.15088744291066</v>
+        <v>1.15088802800574</v>
       </c>
     </row>
     <row r="60">
@@ -5073,46 +5073,46 @@
         <v>3537.71845126756</v>
       </c>
       <c r="F60" s="6" t="n">
-        <v>0.981479099042537</v>
+        <v>0.981479095448701</v>
       </c>
       <c r="G60" s="7" t="n">
-        <v>0.74257472500752</v>
+        <v>0.742574391825869</v>
       </c>
       <c r="H60" s="8" t="n">
-        <v>3530.85228661603</v>
+        <v>3530.85227271397</v>
       </c>
       <c r="I60" s="9" t="n">
-        <v>3091.55866706065</v>
+        <v>3091.55672023495</v>
       </c>
       <c r="J60" s="10" t="n">
-        <v>3162.60403779627</v>
+        <v>3162.60364761897</v>
       </c>
       <c r="K60" s="11" t="n">
-        <v>3604.47660548117</v>
+        <v>3604.47661867951</v>
       </c>
       <c r="L60" s="12" t="n">
-        <v>3585.52384495117</v>
+        <v>3585.52382664291</v>
       </c>
       <c r="M60" s="13" t="n">
-        <v>3493.08786101514</v>
+        <v>3493.08784801417</v>
       </c>
       <c r="N60" s="14" t="n">
-        <v>3493.08786101514</v>
+        <v>3493.08784801417</v>
       </c>
       <c r="O60" s="15" t="n">
-        <v>0.013389230921915</v>
+        <v>0.0133892296943824</v>
       </c>
       <c r="P60" s="16" t="n">
-        <v>0.226548547262183</v>
+        <v>0.226548542162529</v>
       </c>
       <c r="Q60" s="17" t="n">
-        <v>0.0134792680682061</v>
+        <v>0.0134792668241273</v>
       </c>
       <c r="R60" s="18" t="n">
-        <v>0.989304444781211</v>
+        <v>0.989304444994304</v>
       </c>
       <c r="S60" s="19" t="n">
-        <v>1.12987920890282</v>
+        <v>1.12987991620891</v>
       </c>
     </row>
     <row r="61">
@@ -5132,46 +5132,46 @@
         <v>3321.73023465199</v>
       </c>
       <c r="F61" s="6" t="n">
-        <v>0.997640378779409</v>
+        <v>0.997640380837614</v>
       </c>
       <c r="G61" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H61" s="8" t="n">
-        <v>3366.34117248951</v>
+        <v>3366.34115604585</v>
       </c>
       <c r="I61" s="9" t="n">
-        <v>3187.28761178087</v>
+        <v>3187.28519794642</v>
       </c>
       <c r="J61" s="10" t="n">
-        <v>3239.39959391006</v>
+        <v>3239.39918939318</v>
       </c>
       <c r="K61" s="11" t="n">
-        <v>3329.5867983171</v>
+        <v>3329.58679144792</v>
       </c>
       <c r="L61" s="12" t="n">
-        <v>3329.5867983171</v>
+        <v>3329.58679144792</v>
       </c>
       <c r="M61" s="13" t="n">
-        <v>3348.60870977978</v>
+        <v>3348.60869702576</v>
       </c>
       <c r="N61" s="14" t="n">
-        <v>3348.60870977978</v>
+        <v>3348.60869702576</v>
       </c>
       <c r="O61" s="15" t="n">
-        <v>-0.0422411699042642</v>
+        <v>-0.0422411699911018</v>
       </c>
       <c r="P61" s="16" t="n">
-        <v>0.10210440373993</v>
+        <v>0.102104399087509</v>
       </c>
       <c r="Q61" s="17" t="n">
-        <v>-0.0413614420776051</v>
+        <v>-0.0413614421608509</v>
       </c>
       <c r="R61" s="18" t="n">
-        <v>0.994732422591434</v>
+        <v>0.994732423661743</v>
       </c>
       <c r="S61" s="19" t="n">
-        <v>1.05061391303459</v>
+        <v>1.05061470469705</v>
       </c>
     </row>
     <row r="62">
@@ -5191,46 +5191,46 @@
         <v>3386.00448971788</v>
       </c>
       <c r="F62" s="6" t="n">
-        <v>1.07501167950355</v>
+        <v>1.07501168597786</v>
       </c>
       <c r="G62" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H62" s="8" t="n">
-        <v>3121.46612131112</v>
+        <v>3121.46611343197</v>
       </c>
       <c r="I62" s="9" t="n">
-        <v>3282.23001554349</v>
+        <v>3282.22708501755</v>
       </c>
       <c r="J62" s="10" t="n">
-        <v>3313.37557768206</v>
+        <v>3313.3751866584</v>
       </c>
       <c r="K62" s="11" t="n">
-        <v>3149.73739753374</v>
+        <v>3149.73737856429</v>
       </c>
       <c r="L62" s="12" t="n">
-        <v>3149.73739753374</v>
+        <v>3149.73737856429</v>
       </c>
       <c r="M62" s="13" t="n">
-        <v>3160.84311165646</v>
+        <v>3160.84310906788</v>
       </c>
       <c r="N62" s="14" t="n">
-        <v>3160.84311165646</v>
+        <v>3160.84310906788</v>
       </c>
       <c r="O62" s="15" t="n">
-        <v>-0.0577061495599252</v>
+        <v>-0.0577061465701256</v>
       </c>
       <c r="P62" s="16" t="n">
-        <v>-0.0280153390767903</v>
+        <v>-0.0280153393843382</v>
       </c>
       <c r="Q62" s="17" t="n">
-        <v>-0.0560727198656986</v>
+        <v>-0.0560727170435452</v>
       </c>
       <c r="R62" s="18" t="n">
-        <v>1.01261490236159</v>
+        <v>1.01261490408833</v>
       </c>
       <c r="S62" s="19" t="n">
-        <v>0.963016941740162</v>
+        <v>0.963017800778089</v>
       </c>
     </row>
     <row r="63">
@@ -5250,46 +5250,46 @@
         <v>2696.05052423399</v>
       </c>
       <c r="F63" s="6" t="n">
-        <v>0.949598657368717</v>
+        <v>0.949598651661022</v>
       </c>
       <c r="G63" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H63" s="8" t="n">
-        <v>3014.31085324126</v>
+        <v>3014.31088769502</v>
       </c>
       <c r="I63" s="9" t="n">
-        <v>3376.7596169582</v>
+        <v>3376.75612202522</v>
       </c>
       <c r="J63" s="10" t="n">
-        <v>3388.93521739996</v>
+        <v>3388.93487919574</v>
       </c>
       <c r="K63" s="11" t="n">
-        <v>2839.14736327091</v>
+        <v>2839.147380336</v>
       </c>
       <c r="L63" s="12" t="n">
-        <v>3014.31085324126</v>
+        <v>3014.31088769502</v>
       </c>
       <c r="M63" s="13" t="n">
-        <v>3076.24960782439</v>
+        <v>3076.24963662544</v>
       </c>
       <c r="N63" s="14" t="n">
-        <v>3076.24960782439</v>
+        <v>3076.24963662544</v>
       </c>
       <c r="O63" s="15" t="n">
-        <v>-0.0271276042600945</v>
+        <v>-0.0271275940787509</v>
       </c>
       <c r="P63" s="16" t="n">
-        <v>-0.107461556942654</v>
+        <v>-0.107461546360029</v>
       </c>
       <c r="Q63" s="17" t="n">
-        <v>-0.0267629555924834</v>
+        <v>-0.0267629456836227</v>
       </c>
       <c r="R63" s="18" t="n">
-        <v>1.02054823062344</v>
+        <v>1.02054822851328</v>
       </c>
       <c r="S63" s="19" t="n">
-        <v>0.911006395710065</v>
+        <v>0.911007347128299</v>
       </c>
     </row>
     <row r="64">
@@ -5309,46 +5309,46 @@
         <v>3036.48849479411</v>
       </c>
       <c r="F64" s="6" t="n">
-        <v>0.971166859029569</v>
+        <v>0.971166838757224</v>
       </c>
       <c r="G64" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H64" s="8" t="n">
-        <v>3133.76543934477</v>
+        <v>3133.76547629038</v>
       </c>
       <c r="I64" s="9" t="n">
-        <v>3471.16734674839</v>
+        <v>3471.16324347978</v>
       </c>
       <c r="J64" s="10" t="n">
-        <v>3469.66355045072</v>
+        <v>3469.66331774586</v>
       </c>
       <c r="K64" s="11" t="n">
-        <v>3126.6393272813</v>
+        <v>3126.63939254744</v>
       </c>
       <c r="L64" s="12" t="n">
-        <v>3126.6393272813</v>
+        <v>3126.63939254744</v>
       </c>
       <c r="M64" s="13" t="n">
-        <v>3166.13360834461</v>
+        <v>3166.13363307417</v>
       </c>
       <c r="N64" s="14" t="n">
-        <v>3166.13360834461</v>
+        <v>3166.13363307417</v>
       </c>
       <c r="O64" s="15" t="n">
-        <v>0.0287999663234681</v>
+        <v>0.028799964771726</v>
       </c>
       <c r="P64" s="16" t="n">
-        <v>-0.0936003518032074</v>
+        <v>-0.093600341350096</v>
       </c>
       <c r="Q64" s="17" t="n">
-        <v>0.0292186954828384</v>
+        <v>0.0292186938857564</v>
       </c>
       <c r="R64" s="18" t="n">
-        <v>1.01032884229096</v>
+        <v>1.01032883827098</v>
       </c>
       <c r="S64" s="19" t="n">
-        <v>0.912123586121677</v>
+        <v>0.912124671468973</v>
       </c>
     </row>
     <row r="65">
@@ -5368,46 +5368,46 @@
         <v>3418.10930449306</v>
       </c>
       <c r="F65" s="6" t="n">
-        <v>1.00623041567708</v>
+        <v>1.00623043524744</v>
       </c>
       <c r="G65" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H65" s="8" t="n">
-        <v>3353.10017275911</v>
+        <v>3353.10009571791</v>
       </c>
       <c r="I65" s="9" t="n">
-        <v>3565.51760516016</v>
+        <v>3565.51285562011</v>
       </c>
       <c r="J65" s="10" t="n">
-        <v>3557.27249240048</v>
+        <v>3557.27243309191</v>
       </c>
       <c r="K65" s="11" t="n">
-        <v>3396.94492557458</v>
+        <v>3396.94485950678</v>
       </c>
       <c r="L65" s="12" t="n">
-        <v>3396.94492557458</v>
+        <v>3396.94485950678</v>
       </c>
       <c r="M65" s="13" t="n">
-        <v>3351.26132339571</v>
+        <v>3351.26127158573</v>
       </c>
       <c r="N65" s="14" t="n">
-        <v>3351.26132339571</v>
+        <v>3351.26127158573</v>
       </c>
       <c r="O65" s="15" t="n">
-        <v>0.056825627858051</v>
+        <v>0.056825604587556</v>
       </c>
       <c r="P65" s="16" t="n">
-        <v>0.000792153949843666</v>
+        <v>0.00079214228952007</v>
       </c>
       <c r="Q65" s="17" t="n">
-        <v>0.0584712264078751</v>
+        <v>0.0584712017767259</v>
       </c>
       <c r="R65" s="18" t="n">
-        <v>0.999451597247724</v>
+        <v>0.999451604759867</v>
       </c>
       <c r="S65" s="19" t="n">
-        <v>0.939908785906885</v>
+        <v>0.939910023407525</v>
       </c>
     </row>
     <row r="66">
@@ -5427,46 +5427,46 @@
         <v>3735.59369195447</v>
       </c>
       <c r="F66" s="6" t="n">
-        <v>1.07205522043944</v>
+        <v>1.07205526362618</v>
       </c>
       <c r="G66" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H66" s="8" t="n">
-        <v>3532.2332618115</v>
+        <v>3532.2332011785</v>
       </c>
       <c r="I66" s="9" t="n">
-        <v>3659.65946242742</v>
+        <v>3659.65403727826</v>
       </c>
       <c r="J66" s="10" t="n">
-        <v>3651.75883769957</v>
+        <v>3651.75903639106</v>
       </c>
       <c r="K66" s="11" t="n">
-        <v>3484.51611515238</v>
+        <v>3484.51597478192</v>
       </c>
       <c r="L66" s="12" t="n">
-        <v>3484.51611515238</v>
+        <v>3484.51597478192</v>
       </c>
       <c r="M66" s="13" t="n">
-        <v>3513.09710496147</v>
+        <v>3513.0970718549</v>
       </c>
       <c r="N66" s="14" t="n">
-        <v>3513.09710496147</v>
+        <v>3513.0970718549</v>
       </c>
       <c r="O66" s="15" t="n">
-        <v>0.0471612250878732</v>
+        <v>0.0471612311239622</v>
       </c>
       <c r="P66" s="16" t="n">
-        <v>0.111443048851739</v>
+        <v>0.111443039287988</v>
       </c>
       <c r="Q66" s="17" t="n">
-        <v>0.0482910062655983</v>
+        <v>0.0482910125931761</v>
       </c>
       <c r="R66" s="18" t="n">
-        <v>0.994582419837071</v>
+        <v>0.994582427537</v>
       </c>
       <c r="S66" s="19" t="n">
-        <v>0.959951913840437</v>
+        <v>0.959953327847254</v>
       </c>
     </row>
     <row r="67">
@@ -5486,46 +5486,46 @@
         <v>3551.93509050901</v>
       </c>
       <c r="F67" s="6" t="n">
-        <v>0.956071133078347</v>
+        <v>0.956071091829529</v>
       </c>
       <c r="G67" s="7" t="n">
-        <v>0.680771368515559</v>
+        <v>0.680771857441659</v>
       </c>
       <c r="H67" s="8" t="n">
-        <v>3625.15250002222</v>
+        <v>3625.15269194893</v>
       </c>
       <c r="I67" s="9" t="n">
-        <v>3753.33663085936</v>
+        <v>3753.33051228871</v>
       </c>
       <c r="J67" s="10" t="n">
-        <v>3752.31774296416</v>
+        <v>3752.31830093253</v>
       </c>
       <c r="K67" s="11" t="n">
-        <v>3715.13684245704</v>
+        <v>3715.13700274324</v>
       </c>
       <c r="L67" s="12" t="n">
-        <v>3686.41126396654</v>
+        <v>3686.41147834898</v>
       </c>
       <c r="M67" s="13" t="n">
-        <v>3624.61589297286</v>
+        <v>3624.61603948554</v>
       </c>
       <c r="N67" s="14" t="n">
-        <v>3624.61589297286</v>
+        <v>3624.61603948554</v>
       </c>
       <c r="O67" s="15" t="n">
-        <v>0.0312503076256594</v>
+        <v>0.0312503574709879</v>
       </c>
       <c r="P67" s="16" t="n">
-        <v>0.178258059343986</v>
+        <v>0.178258095939716</v>
       </c>
       <c r="Q67" s="17" t="n">
-        <v>0.0317437248898975</v>
+        <v>0.0317437763175037</v>
       </c>
       <c r="R67" s="18" t="n">
-        <v>0.999851976696331</v>
+        <v>0.999851964176686</v>
       </c>
       <c r="S67" s="19" t="n">
-        <v>0.965704984512135</v>
+        <v>0.965706597811798</v>
       </c>
     </row>
     <row r="68">
@@ -5545,46 +5545,46 @@
         <v>3501.98814428698</v>
       </c>
       <c r="F68" s="6" t="n">
-        <v>0.961787418108546</v>
+        <v>0.96178733948393</v>
       </c>
       <c r="G68" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H68" s="8" t="n">
-        <v>3682.59115582795</v>
+        <v>3682.59135938379</v>
       </c>
       <c r="I68" s="9" t="n">
-        <v>3846.1833581731</v>
+        <v>3846.17654319688</v>
       </c>
       <c r="J68" s="10" t="n">
-        <v>3857.3081511977</v>
+        <v>3857.30918469751</v>
       </c>
       <c r="K68" s="11" t="n">
-        <v>3641.12492880599</v>
+        <v>3641.12522646228</v>
       </c>
       <c r="L68" s="12" t="n">
-        <v>3641.12492880599</v>
+        <v>3641.12522646228</v>
       </c>
       <c r="M68" s="13" t="n">
-        <v>3693.38102731178</v>
+        <v>3693.38116479686</v>
       </c>
       <c r="N68" s="14" t="n">
-        <v>3693.38102731178</v>
+        <v>3693.38116479686</v>
       </c>
       <c r="O68" s="15" t="n">
-        <v>0.0187939839665086</v>
+        <v>0.0187939807696578</v>
       </c>
       <c r="P68" s="16" t="n">
-        <v>0.166527217164041</v>
+        <v>0.166527251476356</v>
       </c>
       <c r="Q68" s="17" t="n">
-        <v>0.01897170248363</v>
+        <v>0.0189716992261295</v>
       </c>
       <c r="R68" s="18" t="n">
-        <v>1.00292996725057</v>
+        <v>1.00292994914724</v>
       </c>
       <c r="S68" s="19" t="n">
-        <v>0.96027169881628</v>
+        <v>0.960273436051633</v>
       </c>
     </row>
     <row r="69">
@@ -5604,46 +5604,46 @@
         <v>3831.21508377001</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>1.00692589882653</v>
+        <v>1.00692596756849</v>
       </c>
       <c r="G69" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H69" s="8" t="n">
-        <v>3803.11627358847</v>
+        <v>3803.11601760423</v>
       </c>
       <c r="I69" s="9" t="n">
-        <v>3937.79206373146</v>
+        <v>3937.784568152</v>
       </c>
       <c r="J69" s="10" t="n">
-        <v>3964.75947300864</v>
+        <v>3964.76111155427</v>
       </c>
       <c r="K69" s="11" t="n">
-        <v>3804.86298766861</v>
+        <v>3804.86272791392</v>
       </c>
       <c r="L69" s="12" t="n">
-        <v>3804.86298766861</v>
+        <v>3804.86272791392</v>
       </c>
       <c r="M69" s="13" t="n">
-        <v>3827.81249593353</v>
+        <v>3827.81230744308</v>
       </c>
       <c r="N69" s="14" t="n">
-        <v>3827.81249593353</v>
+        <v>3827.81230744308</v>
       </c>
       <c r="O69" s="15" t="n">
-        <v>0.0357511840377989</v>
+        <v>0.0357510975707359</v>
       </c>
       <c r="P69" s="16" t="n">
-        <v>0.142200540796665</v>
+        <v>0.14220050221028</v>
       </c>
       <c r="Q69" s="17" t="n">
-        <v>0.0363979420557083</v>
+        <v>0.0363978524414261</v>
       </c>
       <c r="R69" s="18" t="n">
-        <v>1.00649368059467</v>
+        <v>1.00649369877872</v>
       </c>
       <c r="S69" s="19" t="n">
-        <v>0.972070752843736</v>
+        <v>0.972072555314897</v>
       </c>
     </row>
     <row r="70">
@@ -5663,46 +5663,46 @@
         <v>4375.22212253129</v>
       </c>
       <c r="F70" s="6" t="n">
-        <v>1.07753500007494</v>
+        <v>1.07753514128417</v>
       </c>
       <c r="G70" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H70" s="8" t="n">
-        <v>4057.13858979235</v>
+        <v>4057.13818680907</v>
       </c>
       <c r="I70" s="9" t="n">
-        <v>4027.62700537892</v>
+        <v>4027.6188682303</v>
       </c>
       <c r="J70" s="10" t="n">
-        <v>4071.62020289349</v>
+        <v>4071.62258557991</v>
       </c>
       <c r="K70" s="11" t="n">
-        <v>4060.39907959092</v>
+        <v>4060.39854748221</v>
       </c>
       <c r="L70" s="12" t="n">
-        <v>4060.39907959092</v>
+        <v>4060.39854748221</v>
       </c>
       <c r="M70" s="13" t="n">
-        <v>4060.53300058404</v>
+        <v>4060.5327575007</v>
       </c>
       <c r="N70" s="14" t="n">
-        <v>4060.53300058404</v>
+        <v>4060.5327575007</v>
       </c>
       <c r="O70" s="15" t="n">
-        <v>0.0590207557915653</v>
+        <v>0.0590207451690189</v>
       </c>
       <c r="P70" s="16" t="n">
-        <v>0.155827146038588</v>
+        <v>0.15582708773736</v>
       </c>
       <c r="Q70" s="17" t="n">
-        <v>0.0607972581984475</v>
+        <v>0.0607972469300795</v>
       </c>
       <c r="R70" s="18" t="n">
-        <v>1.00083665142725</v>
+        <v>1.00083669092235</v>
       </c>
       <c r="S70" s="19" t="n">
-        <v>1.00817007015823</v>
+        <v>1.00817204664772</v>
       </c>
     </row>
     <row r="71">
@@ -5722,46 +5722,46 @@
         <v>4129.41074094782</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>0.956663644722589</v>
+        <v>0.956663566788567</v>
       </c>
       <c r="G71" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H71" s="8" t="n">
-        <v>4305.68071809192</v>
+        <v>4305.68129466638</v>
       </c>
       <c r="I71" s="9" t="n">
-        <v>4115.06936028742</v>
+        <v>4115.06064835789</v>
       </c>
       <c r="J71" s="10" t="n">
-        <v>4174.03935292203</v>
+        <v>4174.04261893332</v>
       </c>
       <c r="K71" s="11" t="n">
-        <v>4316.47085548574</v>
+        <v>4316.47120712444</v>
       </c>
       <c r="L71" s="12" t="n">
-        <v>4316.47085548574</v>
+        <v>4316.47120712444</v>
       </c>
       <c r="M71" s="13" t="n">
-        <v>4304.89038066416</v>
+        <v>4304.89079944793</v>
       </c>
       <c r="N71" s="14" t="n">
-        <v>4304.89038066416</v>
+        <v>4304.89079944793</v>
       </c>
       <c r="O71" s="15" t="n">
-        <v>0.058437428366058</v>
+        <v>0.0584375855118779</v>
       </c>
       <c r="P71" s="16" t="n">
-        <v>0.187681814508998</v>
+        <v>0.187681882039826</v>
       </c>
       <c r="Q71" s="17" t="n">
-        <v>0.0601786465089609</v>
+        <v>0.0601788131116165</v>
       </c>
       <c r="R71" s="18" t="n">
-        <v>0.999816443094715</v>
+        <v>0.999816406472204</v>
       </c>
       <c r="S71" s="19" t="n">
-        <v>1.04612826753508</v>
+        <v>1.04613058404517</v>
       </c>
     </row>
     <row r="72">
@@ -5781,46 +5781,46 @@
         <v>4333.19154339499</v>
       </c>
       <c r="F72" s="6" t="n">
-        <v>0.957353120820965</v>
+        <v>0.957352802713101</v>
       </c>
       <c r="G72" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H72" s="8" t="n">
-        <v>4565.45239992308</v>
+        <v>4565.45321510761</v>
       </c>
       <c r="I72" s="9" t="n">
-        <v>4199.52078817524</v>
+        <v>4199.5116007604</v>
       </c>
       <c r="J72" s="10" t="n">
-        <v>4268.10982954756</v>
+        <v>4268.1141035829</v>
       </c>
       <c r="K72" s="11" t="n">
-        <v>4526.22073209426</v>
+        <v>4526.22223606062</v>
       </c>
       <c r="L72" s="12" t="n">
-        <v>4526.22073209426</v>
+        <v>4526.22223606062</v>
       </c>
       <c r="M72" s="13" t="n">
-        <v>4539.6637102036</v>
+        <v>4539.66429358201</v>
       </c>
       <c r="N72" s="14" t="n">
-        <v>4539.6637102036</v>
+        <v>4539.66429358201</v>
       </c>
       <c r="O72" s="15" t="n">
-        <v>0.0531012623722224</v>
+        <v>0.0531012935982475</v>
       </c>
       <c r="P72" s="16" t="n">
-        <v>0.229134951588731</v>
+        <v>0.229135063786922</v>
       </c>
       <c r="Q72" s="17" t="n">
-        <v>0.0545364245728415</v>
+        <v>0.0545364575018228</v>
       </c>
       <c r="R72" s="18" t="n">
-        <v>0.994351339700769</v>
+        <v>0.994351289935408</v>
       </c>
       <c r="S72" s="19" t="n">
-        <v>1.08099565145293</v>
+        <v>1.08099815529978</v>
       </c>
     </row>
     <row r="73">
@@ -5840,46 +5840,46 @@
         <v>4811.64490558585</v>
       </c>
       <c r="F73" s="6" t="n">
-        <v>1.00457276865072</v>
+        <v>1.00457298385017</v>
       </c>
       <c r="G73" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H73" s="8" t="n">
-        <v>4727.16729410256</v>
+        <v>4727.16649750148</v>
       </c>
       <c r="I73" s="9" t="n">
-        <v>4280.50882469521</v>
+        <v>4280.49929926269</v>
       </c>
       <c r="J73" s="10" t="n">
-        <v>4350.63669673618</v>
+        <v>4350.64207443801</v>
       </c>
       <c r="K73" s="11" t="n">
-        <v>4789.74252114016</v>
+        <v>4789.74149508235</v>
       </c>
       <c r="L73" s="12" t="n">
-        <v>4789.74252114016</v>
+        <v>4789.74149508235</v>
       </c>
       <c r="M73" s="13" t="n">
-        <v>4694.63446409654</v>
+        <v>4694.63387485595</v>
       </c>
       <c r="N73" s="14" t="n">
-        <v>4694.63446409654</v>
+        <v>4694.63387485595</v>
       </c>
       <c r="O73" s="15" t="n">
-        <v>0.033567316539431</v>
+        <v>0.0335670625188415</v>
       </c>
       <c r="P73" s="16" t="n">
-        <v>0.226453612627024</v>
+        <v>0.226453519083827</v>
       </c>
       <c r="Q73" s="17" t="n">
-        <v>0.0341370559111278</v>
+        <v>0.0341367932190566</v>
       </c>
       <c r="R73" s="18" t="n">
-        <v>0.993117901698422</v>
+        <v>0.993117944404386</v>
       </c>
       <c r="S73" s="19" t="n">
-        <v>1.09674682528679</v>
+        <v>1.09674912823011</v>
       </c>
     </row>
     <row r="74">
@@ -5899,46 +5899,46 @@
         <v>5066.12763917827</v>
       </c>
       <c r="F74" s="6" t="n">
-        <v>1.08416642204643</v>
+        <v>1.08416684171809</v>
       </c>
       <c r="G74" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H74" s="8" t="n">
-        <v>4698.72539565374</v>
+        <v>4698.72421548481</v>
       </c>
       <c r="I74" s="9" t="n">
-        <v>4357.76519296509</v>
+        <v>4357.75551183669</v>
       </c>
       <c r="J74" s="10" t="n">
-        <v>4419.71557296672</v>
+        <v>4419.72210707039</v>
       </c>
       <c r="K74" s="11" t="n">
-        <v>4672.83208201159</v>
+        <v>4672.83027319847</v>
       </c>
       <c r="L74" s="12" t="n">
-        <v>4672.83208201159</v>
+        <v>4672.83027319847</v>
       </c>
       <c r="M74" s="13" t="n">
-        <v>4682.22673901443</v>
+        <v>4682.22594317819</v>
       </c>
       <c r="N74" s="14" t="n">
-        <v>4682.22673901443</v>
+        <v>4682.22594317819</v>
       </c>
       <c r="O74" s="15" t="n">
-        <v>-0.00264645749895483</v>
+        <v>-0.0026465019549437</v>
       </c>
       <c r="P74" s="16" t="n">
-        <v>0.153106436603511</v>
+        <v>0.153106309641041</v>
       </c>
       <c r="Q74" s="17" t="n">
-        <v>-0.00264295871744735</v>
+        <v>-0.0026430030559399</v>
       </c>
       <c r="R74" s="18" t="n">
-        <v>0.996488695284349</v>
+        <v>0.996488776197536</v>
       </c>
       <c r="S74" s="19" t="n">
-        <v>1.07445594970861</v>
+        <v>1.07445815407959</v>
       </c>
     </row>
     <row r="75">
@@ -5958,46 +5958,46 @@
         <v>4383.03555041862</v>
       </c>
       <c r="F75" s="6" t="n">
-        <v>0.954182059853283</v>
+        <v>0.954181756505334</v>
       </c>
       <c r="G75" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H75" s="8" t="n">
-        <v>4617.37046737778</v>
+        <v>4617.37168368486</v>
       </c>
       <c r="I75" s="9" t="n">
-        <v>4431.33988716292</v>
+        <v>4431.33028282671</v>
       </c>
       <c r="J75" s="10" t="n">
-        <v>4475.63760584005</v>
+        <v>4475.64527415502</v>
       </c>
       <c r="K75" s="11" t="n">
-        <v>4593.50027089438</v>
+        <v>4593.50173123344</v>
       </c>
       <c r="L75" s="12" t="n">
-        <v>4593.50027089438</v>
+        <v>4593.50173123344</v>
       </c>
       <c r="M75" s="13" t="n">
-        <v>4619.23707406685</v>
+        <v>4619.23798315863</v>
       </c>
       <c r="N75" s="14" t="n">
-        <v>4619.23707406685</v>
+        <v>4619.23798315863</v>
       </c>
       <c r="O75" s="15" t="n">
-        <v>-0.0135442397339241</v>
+        <v>-0.0135438729587099</v>
       </c>
       <c r="P75" s="16" t="n">
-        <v>0.0730208357487128</v>
+        <v>0.0730209425407526</v>
       </c>
       <c r="Q75" s="17" t="n">
-        <v>-0.0134529292276084</v>
+        <v>-0.0134525673865289</v>
       </c>
       <c r="R75" s="18" t="n">
-        <v>1.00040425751026</v>
+        <v>1.0004041908691</v>
       </c>
       <c r="S75" s="19" t="n">
-        <v>1.04240189010287</v>
+        <v>1.04240435452535</v>
       </c>
     </row>
     <row r="76">
@@ -6017,46 +6017,46 @@
         <v>4429.87614408065</v>
       </c>
       <c r="F76" s="6" t="n">
-        <v>0.959446645553423</v>
+        <v>0.959446120956701</v>
       </c>
       <c r="G76" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H76" s="8" t="n">
-        <v>4562.08829656908</v>
+        <v>4562.09001230052</v>
       </c>
       <c r="I76" s="9" t="n">
-        <v>4501.47981827239</v>
+        <v>4501.47057830292</v>
       </c>
       <c r="J76" s="10" t="n">
-        <v>4519.95952550224</v>
+        <v>4519.96818919751</v>
       </c>
       <c r="K76" s="11" t="n">
-        <v>4617.11567246706</v>
+        <v>4617.11819696916</v>
       </c>
       <c r="L76" s="12" t="n">
-        <v>4617.11567246706</v>
+        <v>4617.11819696916</v>
       </c>
       <c r="M76" s="13" t="n">
-        <v>4577.9222861633</v>
+        <v>4577.92352606472</v>
       </c>
       <c r="N76" s="14" t="n">
-        <v>4577.9222861633</v>
+        <v>4577.92352606472</v>
       </c>
       <c r="O76" s="15" t="n">
-        <v>-0.00898431008712427</v>
+        <v>-0.00898423604905211</v>
       </c>
       <c r="P76" s="16" t="n">
-        <v>0.0084276233663978</v>
+        <v>0.00842776690267621</v>
       </c>
       <c r="Q76" s="17" t="n">
-        <v>-0.00894407176793255</v>
+        <v>-0.0089439983920595</v>
       </c>
       <c r="R76" s="18" t="n">
-        <v>1.00347077666299</v>
+        <v>1.0034706710568</v>
       </c>
       <c r="S76" s="19" t="n">
-        <v>1.016981630703</v>
+        <v>1.01698399365983</v>
       </c>
     </row>
     <row r="77">
@@ -6076,46 +6076,46 @@
         <v>4465.28611985202</v>
       </c>
       <c r="F77" s="6" t="n">
-        <v>0.995835953205919</v>
+        <v>0.995836297385128</v>
       </c>
       <c r="G77" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H77" s="8" t="n">
-        <v>4554.38624023972</v>
+        <v>4554.38510067621</v>
       </c>
       <c r="I77" s="9" t="n">
-        <v>4568.53324751702</v>
+        <v>4568.52472149073</v>
       </c>
       <c r="J77" s="10" t="n">
-        <v>4554.82737542465</v>
+        <v>4554.83674798886</v>
       </c>
       <c r="K77" s="11" t="n">
-        <v>4483.95752882472</v>
+        <v>4483.95597908711</v>
       </c>
       <c r="L77" s="12" t="n">
-        <v>4483.95752882472</v>
+        <v>4483.95597908711</v>
       </c>
       <c r="M77" s="13" t="n">
-        <v>4567.18906622118</v>
+        <v>4567.18825220102</v>
       </c>
       <c r="N77" s="14" t="n">
-        <v>4567.18906622118</v>
+        <v>4567.18825220102</v>
       </c>
       <c r="O77" s="15" t="n">
-        <v>-0.00234731420029296</v>
+        <v>-0.00234776327617299</v>
       </c>
       <c r="P77" s="16" t="n">
-        <v>-0.0271470332461524</v>
+        <v>-0.0271470845335806</v>
       </c>
       <c r="Q77" s="17" t="n">
-        <v>-0.00234456141262263</v>
+        <v>-0.00234500943551608</v>
       </c>
       <c r="R77" s="18" t="n">
-        <v>1.0028110979847</v>
+        <v>1.00281117016717</v>
       </c>
       <c r="S77" s="19" t="n">
-        <v>0.999705773992873</v>
+        <v>0.999707461517408</v>
       </c>
     </row>
     <row r="78">
@@ -6135,46 +6135,46 @@
         <v>5131.88191643965</v>
       </c>
       <c r="F78" s="6" t="n">
-        <v>1.0956837411468</v>
+        <v>1.09568436834999</v>
       </c>
       <c r="G78" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H78" s="8" t="n">
-        <v>4645.69110930167</v>
+        <v>4645.68920364397</v>
       </c>
       <c r="I78" s="9" t="n">
-        <v>4632.92070852923</v>
+        <v>4632.91331537724</v>
       </c>
       <c r="J78" s="10" t="n">
-        <v>4582.87297981346</v>
+        <v>4582.88259635893</v>
       </c>
       <c r="K78" s="11" t="n">
-        <v>4683.72553476823</v>
+        <v>4683.72285366071</v>
       </c>
       <c r="L78" s="12" t="n">
-        <v>4683.72553476823</v>
+        <v>4683.72285366071</v>
       </c>
       <c r="M78" s="13" t="n">
-        <v>4649.58900223759</v>
+        <v>4649.58768062056</v>
       </c>
       <c r="N78" s="14" t="n">
-        <v>4649.58900223759</v>
+        <v>4649.58768062056</v>
       </c>
       <c r="O78" s="15" t="n">
-        <v>0.0178808973908653</v>
+        <v>0.0178807913792013</v>
       </c>
       <c r="P78" s="16" t="n">
-        <v>-0.00697055879521802</v>
+        <v>-0.00697067227291404</v>
       </c>
       <c r="Q78" s="17" t="n">
-        <v>0.0180417177440353</v>
+        <v>0.0180416098197445</v>
       </c>
       <c r="R78" s="18" t="n">
-        <v>1.0008390340305</v>
+        <v>1.00083916009137</v>
       </c>
       <c r="S78" s="19" t="n">
-        <v>1.00359779386633</v>
+        <v>1.00359911012968</v>
       </c>
     </row>
     <row r="79">
@@ -6194,46 +6194,46 @@
         <v>4499.44907972728</v>
       </c>
       <c r="F79" s="6" t="n">
-        <v>0.947861581463955</v>
+        <v>0.947861256890359</v>
       </c>
       <c r="G79" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H79" s="8" t="n">
-        <v>4743.1062120753</v>
+        <v>4743.10578018329</v>
       </c>
       <c r="I79" s="9" t="n">
-        <v>4695.00987511721</v>
+        <v>4695.00410748553</v>
       </c>
       <c r="J79" s="10" t="n">
-        <v>4606.37381364184</v>
+        <v>4606.38297629307</v>
       </c>
       <c r="K79" s="11" t="n">
-        <v>4746.94741058917</v>
+        <v>4746.94903607368</v>
       </c>
       <c r="L79" s="12" t="n">
-        <v>4746.94741058917</v>
+        <v>4746.94903607368</v>
       </c>
       <c r="M79" s="13" t="n">
-        <v>4724.94097102942</v>
+        <v>4724.94193955551</v>
       </c>
       <c r="N79" s="14" t="n">
-        <v>4724.94097102942</v>
+        <v>4724.94193955551</v>
       </c>
       <c r="O79" s="15" t="n">
-        <v>0.0160762388864782</v>
+        <v>0.0160767281119646</v>
       </c>
       <c r="P79" s="16" t="n">
-        <v>0.0228834102401911</v>
+        <v>0.0228834186033005</v>
       </c>
       <c r="Q79" s="17" t="n">
-        <v>0.0162061568787206</v>
+        <v>0.0162066540327936</v>
       </c>
       <c r="R79" s="18" t="n">
-        <v>0.996170180418978</v>
+        <v>0.996170475323644</v>
       </c>
       <c r="S79" s="19" t="n">
-        <v>1.0063750868919</v>
+        <v>1.00637652947359</v>
       </c>
     </row>
     <row r="80">
@@ -6253,46 +6253,46 @@
         <v>4539.76782551238</v>
       </c>
       <c r="F80" s="6" t="n">
-        <v>0.961378619355652</v>
+        <v>0.961377946647128</v>
       </c>
       <c r="G80" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H80" s="8" t="n">
-        <v>4739.22986968411</v>
+        <v>4739.23720794605</v>
       </c>
       <c r="I80" s="9" t="n">
-        <v>4755.20017410558</v>
+        <v>4755.19660130009</v>
       </c>
       <c r="J80" s="10" t="n">
-        <v>4628.11161465774</v>
+        <v>4628.11933106314</v>
       </c>
       <c r="K80" s="11" t="n">
-        <v>4722.14352817112</v>
+        <v>4722.14683241397</v>
       </c>
       <c r="L80" s="12" t="n">
-        <v>4722.14352817112</v>
+        <v>4722.14683241397</v>
       </c>
       <c r="M80" s="13" t="n">
-        <v>4718.8417789891</v>
+        <v>4718.85544533656</v>
       </c>
       <c r="N80" s="14" t="n">
-        <v>4718.8417789891</v>
+        <v>4718.85544533656</v>
       </c>
       <c r="O80" s="15" t="n">
-        <v>-0.00129168428579694</v>
+        <v>-0.0012889931483329</v>
       </c>
       <c r="P80" s="16" t="n">
-        <v>0.0307824126354708</v>
+        <v>0.0307851187267398</v>
       </c>
       <c r="Q80" s="17" t="n">
-        <v>-0.00129085042071864</v>
+        <v>-0.00128816275349408</v>
       </c>
       <c r="R80" s="18" t="n">
-        <v>0.995698016079484</v>
+        <v>0.995699357994717</v>
       </c>
       <c r="S80" s="19" t="n">
-        <v>0.992353971697245</v>
+        <v>0.992357591281588</v>
       </c>
     </row>
     <row r="81">
@@ -6312,46 +6312,46 @@
         <v>4837.70906203481</v>
       </c>
       <c r="F81" s="6" t="n">
-        <v>0.989622736038117</v>
+        <v>0.989622902661591</v>
       </c>
       <c r="G81" s="7" t="n">
-        <v>0.00704851441233645</v>
+        <v>0.00717607351480565</v>
       </c>
       <c r="H81" s="8" t="n">
-        <v>4682.68237989658</v>
+        <v>4682.70271720447</v>
       </c>
       <c r="I81" s="9" t="n">
-        <v>4813.92349327863</v>
+        <v>4813.92276588582</v>
       </c>
       <c r="J81" s="10" t="n">
-        <v>4651.57098859386</v>
+        <v>4651.57593423991</v>
       </c>
       <c r="K81" s="11" t="n">
-        <v>4888.43767009864</v>
+        <v>4888.4368470291</v>
       </c>
       <c r="L81" s="12" t="n">
-        <v>4684.13264902498</v>
+        <v>4684.1790804446</v>
       </c>
       <c r="M81" s="13" t="n">
-        <v>4661.92460825817</v>
+        <v>4661.95513840587</v>
       </c>
       <c r="N81" s="14" t="n">
-        <v>4661.92460825817</v>
+        <v>4661.95513840587</v>
       </c>
       <c r="O81" s="15" t="n">
-        <v>-0.0121350147400354</v>
+        <v>-0.012131362051415</v>
       </c>
       <c r="P81" s="16" t="n">
-        <v>0.0207426363707286</v>
+        <v>0.0207495029702736</v>
       </c>
       <c r="Q81" s="17" t="n">
-        <v>-0.0120616823781534</v>
+        <v>-0.0120580737405124</v>
       </c>
       <c r="R81" s="18" t="n">
-        <v>0.995567119451124</v>
+        <v>0.995569315403608</v>
       </c>
       <c r="S81" s="19" t="n">
-        <v>0.968425155648469</v>
+        <v>0.968431644031167</v>
       </c>
     </row>
     <row r="82">
@@ -6371,46 +6371,46 @@
         <v>4964.35954377805</v>
       </c>
       <c r="F82" s="6" t="n">
-        <v>1.10780903367625</v>
+        <v>1.10780968052968</v>
       </c>
       <c r="G82" s="7" t="n">
-        <v>0.419851049233782</v>
+        <v>0.419729148555875</v>
       </c>
       <c r="H82" s="8" t="n">
-        <v>4612.32543939119</v>
+        <v>4612.34452104126</v>
       </c>
       <c r="I82" s="9" t="n">
-        <v>4871.59106001692</v>
+        <v>4871.59391420203</v>
       </c>
       <c r="J82" s="10" t="n">
-        <v>4680.70670075044</v>
+        <v>4680.70719690088</v>
       </c>
       <c r="K82" s="11" t="n">
-        <v>4481.24125446413</v>
+        <v>4481.23863785378</v>
       </c>
       <c r="L82" s="12" t="n">
-        <v>4557.28960681161</v>
+        <v>4557.31556032031</v>
       </c>
       <c r="M82" s="13" t="n">
-        <v>4592.47015350171</v>
+        <v>4592.49453901105</v>
       </c>
       <c r="N82" s="14" t="n">
-        <v>4592.47015350171</v>
+        <v>4592.49453901105</v>
       </c>
       <c r="O82" s="15" t="n">
-        <v>-0.0150103298173186</v>
+        <v>-0.0150115687495437</v>
       </c>
       <c r="P82" s="16" t="n">
-        <v>-0.0122847091879281</v>
+        <v>-0.0122791837752571</v>
       </c>
       <c r="Q82" s="17" t="n">
-        <v>-0.0148982363707537</v>
+        <v>-0.0148994568443177</v>
       </c>
       <c r="R82" s="18" t="n">
-        <v>0.995695168055596</v>
+        <v>0.99569633579199</v>
       </c>
       <c r="S82" s="19" t="n">
-        <v>0.942704364328512</v>
+        <v>0.942708817666979</v>
       </c>
     </row>
     <row r="83">
@@ -6430,46 +6430,46 @@
         <v>4294.14828388207</v>
       </c>
       <c r="F83" s="6" t="n">
-        <v>0.939398328404692</v>
+        <v>0.939398492068888</v>
       </c>
       <c r="G83" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H83" s="8" t="n">
-        <v>4536.19987637636</v>
+        <v>4536.20528818417</v>
       </c>
       <c r="I83" s="9" t="n">
-        <v>4928.53298242337</v>
+        <v>4928.54026940465</v>
       </c>
       <c r="J83" s="10" t="n">
-        <v>4719.6363247299</v>
+        <v>4719.63054585461</v>
       </c>
       <c r="K83" s="11" t="n">
-        <v>4571.16875135864</v>
+        <v>4571.16795495896</v>
       </c>
       <c r="L83" s="12" t="n">
-        <v>4571.16875135864</v>
+        <v>4571.16795495896</v>
       </c>
       <c r="M83" s="13" t="n">
-        <v>4543.90149811923</v>
+        <v>4543.90836074325</v>
       </c>
       <c r="N83" s="14" t="n">
-        <v>4543.90149811923</v>
+        <v>4543.90836074325</v>
       </c>
       <c r="O83" s="15" t="n">
-        <v>-0.0106320352873205</v>
+        <v>-0.0106358348706202</v>
       </c>
       <c r="P83" s="16" t="n">
-        <v>-0.0383157110364384</v>
+        <v>-0.0383144557389615</v>
       </c>
       <c r="Q83" s="17" t="n">
-        <v>-0.0105757149767089</v>
+        <v>-0.0105794743695565</v>
       </c>
       <c r="R83" s="18" t="n">
-        <v>1.00169781357805</v>
+        <v>1.00169813138289</v>
       </c>
       <c r="S83" s="19" t="n">
-        <v>0.921958220493633</v>
+        <v>0.921958249778517</v>
       </c>
     </row>
     <row r="84">
@@ -6489,46 +6489,46 @@
         <v>4320.30298531754</v>
       </c>
       <c r="F84" s="6" t="n">
-        <v>0.965219697924945</v>
+        <v>0.965219031630258</v>
       </c>
       <c r="G84" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H84" s="8" t="n">
-        <v>4523.07036580422</v>
+        <v>4523.07197568784</v>
       </c>
       <c r="I84" s="9" t="n">
-        <v>4984.88293019265</v>
+        <v>4984.89563067841</v>
       </c>
       <c r="J84" s="10" t="n">
-        <v>4771.86034866496</v>
+        <v>4771.84644972674</v>
       </c>
       <c r="K84" s="11" t="n">
-        <v>4475.97888294804</v>
+        <v>4475.98197273476</v>
       </c>
       <c r="L84" s="12" t="n">
-        <v>4475.97888294804</v>
+        <v>4475.98197273476</v>
       </c>
       <c r="M84" s="13" t="n">
-        <v>4520.6252867477</v>
+        <v>4520.62785585213</v>
       </c>
       <c r="N84" s="14" t="n">
-        <v>4520.6252867477</v>
+        <v>4520.62785585213</v>
       </c>
       <c r="O84" s="15" t="n">
-        <v>-0.00513568178098053</v>
+        <v>-0.00513662376599043</v>
       </c>
       <c r="P84" s="16" t="n">
-        <v>-0.0420053270537639</v>
+        <v>-0.0420075570825817</v>
       </c>
       <c r="Q84" s="17" t="n">
-        <v>-0.00512251671414277</v>
+        <v>-0.00512345387337731</v>
       </c>
       <c r="R84" s="18" t="n">
-        <v>0.999459420513329</v>
+        <v>0.999459632778596</v>
       </c>
       <c r="S84" s="19" t="n">
-        <v>0.906866891370102</v>
+        <v>0.906865096238113</v>
       </c>
     </row>
     <row r="85">
@@ -6548,46 +6548,46 @@
         <v>4458.85316814996</v>
       </c>
       <c r="F85" s="6" t="n">
-        <v>0.97795279621672</v>
+        <v>0.977951746652501</v>
       </c>
       <c r="G85" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H85" s="8" t="n">
-        <v>4495.82715265267</v>
+        <v>4495.83031388389</v>
       </c>
       <c r="I85" s="9" t="n">
-        <v>5040.551220375</v>
+        <v>5040.57043951156</v>
       </c>
       <c r="J85" s="10" t="n">
-        <v>4840.13692282147</v>
+        <v>4840.11306418841</v>
       </c>
       <c r="K85" s="11" t="n">
-        <v>4559.37462973607</v>
+        <v>4559.37952298003</v>
       </c>
       <c r="L85" s="12" t="n">
-        <v>4559.37462973607</v>
+        <v>4559.37952298003</v>
       </c>
       <c r="M85" s="13" t="n">
-        <v>4510.14827057273</v>
+        <v>4510.15007711996</v>
       </c>
       <c r="N85" s="14" t="n">
-        <v>4510.14827057273</v>
+        <v>4510.15007711996</v>
       </c>
       <c r="O85" s="15" t="n">
-        <v>-0.00232029311973034</v>
+        <v>-0.00232046087533998</v>
       </c>
       <c r="P85" s="16" t="n">
-        <v>-0.0325565834798327</v>
+        <v>-0.0325625315514774</v>
       </c>
       <c r="Q85" s="17" t="n">
-        <v>-0.00231760332042608</v>
+        <v>-0.00231777068723071</v>
       </c>
       <c r="R85" s="18" t="n">
-        <v>1.00318542449116</v>
+        <v>1.00318512093124</v>
       </c>
       <c r="S85" s="19" t="n">
-        <v>0.894772828087081</v>
+        <v>0.89476977481878</v>
       </c>
     </row>
     <row r="86">
@@ -6607,46 +6607,46 @@
         <v>5009.75394783902</v>
       </c>
       <c r="F86" s="6" t="n">
-        <v>1.12683448903526</v>
+        <v>1.12683592108946</v>
       </c>
       <c r="G86" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H86" s="8" t="n">
-        <v>4494.7029390206</v>
+        <v>4494.69504103381</v>
       </c>
       <c r="I86" s="9" t="n">
-        <v>5095.13010499114</v>
+        <v>5095.15706635607</v>
       </c>
       <c r="J86" s="10" t="n">
-        <v>4925.74479013671</v>
+        <v>4925.70922252584</v>
       </c>
       <c r="K86" s="11" t="n">
-        <v>4445.86493987074</v>
+        <v>4445.859289785</v>
       </c>
       <c r="L86" s="12" t="n">
-        <v>4445.86493987074</v>
+        <v>4445.859289785</v>
       </c>
       <c r="M86" s="13" t="n">
-        <v>4519.12984686168</v>
+        <v>4519.12444115572</v>
       </c>
       <c r="N86" s="14" t="n">
-        <v>4519.12984686168</v>
+        <v>4519.12444115572</v>
       </c>
       <c r="O86" s="15" t="n">
-        <v>0.00198943462244615</v>
+        <v>0.00198783788726035</v>
       </c>
       <c r="P86" s="16" t="n">
-        <v>-0.015969686070602</v>
+        <v>-0.015976088209159</v>
       </c>
       <c r="Q86" s="17" t="n">
-        <v>0.00199141486047161</v>
+        <v>0.00198981494680095</v>
       </c>
       <c r="R86" s="18" t="n">
-        <v>1.00543459894291</v>
+        <v>1.00543516298634</v>
       </c>
       <c r="S86" s="19" t="n">
-        <v>0.886950824363598</v>
+        <v>0.88694507005408</v>
       </c>
     </row>
     <row r="87">
@@ -6666,46 +6666,46 @@
         <v>4294.11901736909</v>
       </c>
       <c r="F87" s="6" t="n">
-        <v>0.928374887585103</v>
+        <v>0.928377941603579</v>
       </c>
       <c r="G87" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H87" s="8" t="n">
-        <v>4627.02579155106</v>
+        <v>4627.01769399572</v>
       </c>
       <c r="I87" s="9" t="n">
-        <v>5147.91110069264</v>
+        <v>5147.94713734113</v>
       </c>
       <c r="J87" s="10" t="n">
-        <v>5028.55888208253</v>
+        <v>5028.51009031917</v>
       </c>
       <c r="K87" s="11" t="n">
-        <v>4625.41487796917</v>
+        <v>4625.39966207286</v>
       </c>
       <c r="L87" s="12" t="n">
-        <v>4625.41487796917</v>
+        <v>4625.39966207286</v>
       </c>
       <c r="M87" s="13" t="n">
-        <v>4654.88929210415</v>
+        <v>4654.88530523199</v>
       </c>
       <c r="N87" s="14" t="n">
-        <v>4654.88929210415</v>
+        <v>4654.88530523199</v>
       </c>
       <c r="O87" s="15" t="n">
-        <v>0.0295986643141318</v>
+        <v>0.029599004006108</v>
       </c>
       <c r="P87" s="16" t="n">
-        <v>0.0244256602021098</v>
+        <v>0.0244232356108927</v>
       </c>
       <c r="Q87" s="17" t="n">
-        <v>0.030041058753103</v>
+        <v>0.0300414086498453</v>
       </c>
       <c r="R87" s="18" t="n">
-        <v>1.00602190301251</v>
+        <v>1.00602280195998</v>
       </c>
       <c r="S87" s="19" t="n">
-        <v>0.904228764066622</v>
+        <v>0.904221659827726</v>
       </c>
     </row>
     <row r="88">
@@ -6725,46 +6725,46 @@
         <v>4771.89666477564</v>
       </c>
       <c r="F88" s="6" t="n">
-        <v>0.969333734453903</v>
+        <v>0.969329769918344</v>
       </c>
       <c r="G88" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H88" s="8" t="n">
-        <v>4905.3535401569</v>
+        <v>4905.38009798983</v>
       </c>
       <c r="I88" s="9" t="n">
-        <v>5197.77993340288</v>
+        <v>5197.82646748555</v>
       </c>
       <c r="J88" s="10" t="n">
-        <v>5146.05473087944</v>
+        <v>5145.99158348487</v>
       </c>
       <c r="K88" s="11" t="n">
-        <v>4922.86247260753</v>
+        <v>4922.88260699722</v>
       </c>
       <c r="L88" s="12" t="n">
-        <v>4922.86247260753</v>
+        <v>4922.88260699722</v>
       </c>
       <c r="M88" s="13" t="n">
-        <v>4903.06161669108</v>
+        <v>4903.07972849311</v>
       </c>
       <c r="N88" s="14" t="n">
-        <v>4903.06161669108</v>
+        <v>4903.07972849311</v>
       </c>
       <c r="O88" s="15" t="n">
-        <v>0.0519417018616386</v>
+        <v>0.051946252324537</v>
       </c>
       <c r="P88" s="16" t="n">
-        <v>0.0845981043959791</v>
+        <v>0.0846014944906126</v>
       </c>
       <c r="Q88" s="17" t="n">
-        <v>0.0533143344585862</v>
+        <v>0.0533191275372908</v>
       </c>
       <c r="R88" s="18" t="n">
-        <v>0.999532770992538</v>
+        <v>0.999531051732839</v>
       </c>
       <c r="S88" s="19" t="n">
-        <v>0.943299193023194</v>
+        <v>0.943294232534272</v>
       </c>
     </row>
     <row r="89">
@@ -6784,46 +6784,46 @@
         <v>4952.78741323696</v>
       </c>
       <c r="F89" s="6" t="n">
-        <v>0.963369903913917</v>
+        <v>0.963361022976676</v>
       </c>
       <c r="G89" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H89" s="8" t="n">
-        <v>5156.30398867296</v>
+        <v>5156.32035980713</v>
       </c>
       <c r="I89" s="9" t="n">
-        <v>5243.29576890601</v>
+        <v>5243.3542796361</v>
       </c>
       <c r="J89" s="10" t="n">
-        <v>5273.6921487274</v>
+        <v>5273.61406579816</v>
       </c>
       <c r="K89" s="11" t="n">
-        <v>5141.1066435801</v>
+        <v>5141.15403790514</v>
       </c>
       <c r="L89" s="12" t="n">
-        <v>5141.1066435801</v>
+        <v>5141.15403790514</v>
       </c>
       <c r="M89" s="13" t="n">
-        <v>5131.6442638132</v>
+        <v>5131.65451364393</v>
       </c>
       <c r="N89" s="14" t="n">
-        <v>5131.6442638132</v>
+        <v>5131.65451364393</v>
       </c>
       <c r="O89" s="15" t="n">
-        <v>0.0455662973583076</v>
+        <v>0.0455646007625661</v>
       </c>
       <c r="P89" s="16" t="n">
-        <v>0.13779945934273</v>
+        <v>0.137801276209604</v>
       </c>
       <c r="Q89" s="17" t="n">
-        <v>0.0466203904809133</v>
+        <v>0.0466186147907222</v>
       </c>
       <c r="R89" s="18" t="n">
-        <v>0.995217557980691</v>
+        <v>0.995216386019095</v>
       </c>
       <c r="S89" s="19" t="n">
-        <v>0.978705854101359</v>
+        <v>0.978696887519887</v>
       </c>
     </row>
     <row r="90">
@@ -6843,46 +6843,46 @@
         <v>6108.57642446564</v>
       </c>
       <c r="F90" s="6" t="n">
-        <v>1.14790471434224</v>
+        <v>1.1479206606997</v>
       </c>
       <c r="G90" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H90" s="8" t="n">
-        <v>5268.63207687357</v>
+        <v>5268.57252801938</v>
       </c>
       <c r="I90" s="9" t="n">
-        <v>5282.84594957322</v>
+        <v>5282.91795672676</v>
       </c>
       <c r="J90" s="10" t="n">
-        <v>5405.814986535</v>
+        <v>5405.72235615181</v>
       </c>
       <c r="K90" s="11" t="n">
-        <v>5321.50129548506</v>
+        <v>5321.42737176822</v>
       </c>
       <c r="L90" s="12" t="n">
-        <v>5321.50129548506</v>
+        <v>5321.42737176822</v>
       </c>
       <c r="M90" s="13" t="n">
-        <v>5270.63405024202</v>
+        <v>5270.59348670266</v>
       </c>
       <c r="N90" s="14" t="n">
-        <v>5270.63405024202</v>
+        <v>5270.59348670266</v>
       </c>
       <c r="O90" s="15" t="n">
-        <v>0.026724541365943</v>
+        <v>0.026714847820489</v>
       </c>
       <c r="P90" s="16" t="n">
-        <v>0.16629400544935</v>
+        <v>0.166286424578907</v>
       </c>
       <c r="Q90" s="17" t="n">
-        <v>0.0270848444053167</v>
+        <v>0.027074888359947</v>
       </c>
       <c r="R90" s="18" t="n">
-        <v>1.00037997972514</v>
+        <v>1.00038358752253</v>
       </c>
       <c r="S90" s="19" t="n">
-        <v>0.99768838625094</v>
+        <v>0.997667109327638</v>
       </c>
     </row>
     <row r="91">
@@ -6902,46 +6902,46 @@
         <v>4881.31680020904</v>
       </c>
       <c r="F91" s="6" t="n">
-        <v>0.921276603631135</v>
+        <v>0.921287349560973</v>
       </c>
       <c r="G91" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H91" s="8" t="n">
-        <v>5383.36765094198</v>
+        <v>5383.34869465452</v>
       </c>
       <c r="I91" s="9" t="n">
-        <v>5314.75394957233</v>
+        <v>5314.8410065404</v>
       </c>
       <c r="J91" s="10" t="n">
-        <v>5536.1041676851</v>
+        <v>5535.99897329915</v>
       </c>
       <c r="K91" s="11" t="n">
-        <v>5298.42696641784</v>
+        <v>5298.36516536905</v>
       </c>
       <c r="L91" s="12" t="n">
-        <v>5298.42696641784</v>
+        <v>5298.36516536905</v>
       </c>
       <c r="M91" s="13" t="n">
-        <v>5386.16195716155</v>
+        <v>5386.15507797732</v>
       </c>
       <c r="N91" s="14" t="n">
-        <v>5386.16195716155</v>
+        <v>5386.15507797732</v>
       </c>
       <c r="O91" s="15" t="n">
-        <v>0.0216823955084661</v>
+        <v>0.0216888144816625</v>
       </c>
       <c r="P91" s="16" t="n">
-        <v>0.157097756609984</v>
+        <v>0.157097269813159</v>
       </c>
       <c r="Q91" s="17" t="n">
-        <v>0.0219191668057908</v>
+        <v>0.0219257264985846</v>
       </c>
       <c r="R91" s="18" t="n">
-        <v>1.0005190628619</v>
+        <v>1.00052130810802</v>
       </c>
       <c r="S91" s="19" t="n">
-        <v>1.0134358068627</v>
+        <v>1.01341791247361</v>
       </c>
     </row>
     <row r="92">
@@ -6961,46 +6961,46 @@
         <v>5446.86304040468</v>
       </c>
       <c r="F92" s="6" t="n">
-        <v>0.968108740041283</v>
+        <v>0.968079487687676</v>
       </c>
       <c r="G92" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H92" s="8" t="n">
-        <v>5538.95726313622</v>
+        <v>5539.0995353269</v>
       </c>
       <c r="I92" s="9" t="n">
-        <v>5337.36740266239</v>
+        <v>5337.4710052443</v>
       </c>
       <c r="J92" s="10" t="n">
-        <v>5657.81904710531</v>
+        <v>5657.70496107159</v>
       </c>
       <c r="K92" s="11" t="n">
-        <v>5626.29260032547</v>
+        <v>5626.46260940296</v>
       </c>
       <c r="L92" s="12" t="n">
-        <v>5626.29260032547</v>
+        <v>5626.46260940296</v>
       </c>
       <c r="M92" s="13" t="n">
-        <v>5563.42702022374</v>
+        <v>5563.52763664167</v>
       </c>
       <c r="N92" s="14" t="n">
-        <v>5563.42702022374</v>
+        <v>5563.52763664167</v>
       </c>
       <c r="O92" s="15" t="n">
-        <v>0.0323812249644306</v>
+        <v>0.0324005873284365</v>
       </c>
       <c r="P92" s="16" t="n">
-        <v>0.134684296294509</v>
+        <v>0.134700625876124</v>
       </c>
       <c r="Q92" s="17" t="n">
-        <v>0.0329112017930491</v>
+        <v>0.032931201589345</v>
       </c>
       <c r="R92" s="18" t="n">
-        <v>1.00441775517034</v>
+        <v>1.00441012138507</v>
       </c>
       <c r="S92" s="19" t="n">
-        <v>1.04235414212793</v>
+        <v>1.04235276054432</v>
       </c>
     </row>
     <row r="93">
@@ -7020,46 +7020,46 @@
         <v>5439.60580468164</v>
       </c>
       <c r="F93" s="6" t="n">
-        <v>0.95386566053668</v>
+        <v>0.953844878461034</v>
       </c>
       <c r="G93" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H93" s="8" t="n">
-        <v>5795.77370899857</v>
+        <v>5795.81765605808</v>
       </c>
       <c r="I93" s="9" t="n">
-        <v>5349.02373823797</v>
+        <v>5349.14523160503</v>
       </c>
       <c r="J93" s="10" t="n">
-        <v>5763.0305937169</v>
+        <v>5762.91319426087</v>
       </c>
       <c r="K93" s="11" t="n">
-        <v>5702.69591382619</v>
+        <v>5702.8201623917</v>
       </c>
       <c r="L93" s="12" t="n">
-        <v>5702.69591382619</v>
+        <v>5702.8201623917</v>
       </c>
       <c r="M93" s="13" t="n">
-        <v>5786.58579188053</v>
+        <v>5786.61077075792</v>
       </c>
       <c r="N93" s="14" t="n">
-        <v>5786.58579188053</v>
+        <v>5786.61077075792</v>
       </c>
       <c r="O93" s="15" t="n">
-        <v>0.0393281554808918</v>
+        <v>0.03931438699094</v>
       </c>
       <c r="P93" s="16" t="n">
-        <v>0.127628006618811</v>
+        <v>0.127630621931505</v>
       </c>
       <c r="Q93" s="17" t="n">
-        <v>0.0401117460237339</v>
+        <v>0.0400974253541972</v>
       </c>
       <c r="R93" s="18" t="n">
-        <v>0.998414721212498</v>
+        <v>0.998411460496771</v>
       </c>
       <c r="S93" s="19" t="n">
-        <v>1.08180222692126</v>
+        <v>1.08178232600008</v>
       </c>
     </row>
     <row r="94">
@@ -7079,46 +7079,46 @@
         <v>7098.31965039088</v>
       </c>
       <c r="F94" s="6" t="n">
-        <v>1.16086930648887</v>
+        <v>1.16092979415471</v>
       </c>
       <c r="G94" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H94" s="8" t="n">
-        <v>6023.50843250802</v>
+        <v>6023.2563916658</v>
       </c>
       <c r="I94" s="9" t="n">
-        <v>5348.24096394216</v>
+        <v>5348.38158414171</v>
       </c>
       <c r="J94" s="10" t="n">
-        <v>5843.65214420722</v>
+        <v>5843.54033590039</v>
       </c>
       <c r="K94" s="11" t="n">
-        <v>6114.65873954429</v>
+        <v>6114.34014884533</v>
       </c>
       <c r="L94" s="12" t="n">
-        <v>6114.65873954429</v>
+        <v>6114.34014884533</v>
       </c>
       <c r="M94" s="13" t="n">
-        <v>6028.39634457253</v>
+        <v>6028.22201466541</v>
       </c>
       <c r="N94" s="14" t="n">
-        <v>6028.39634457253</v>
+        <v>6028.22201466541</v>
       </c>
       <c r="O94" s="15" t="n">
-        <v>0.0409385847865122</v>
+        <v>0.0409053495680626</v>
       </c>
       <c r="P94" s="16" t="n">
-        <v>0.143770614143799</v>
+        <v>0.143746340876828</v>
       </c>
       <c r="Q94" s="17" t="n">
-        <v>0.0417881219407983</v>
+        <v>0.04175349846035</v>
       </c>
       <c r="R94" s="18" t="n">
-        <v>1.0008114726026</v>
+        <v>1.0008244083726</v>
       </c>
       <c r="S94" s="19" t="n">
-        <v>1.12717366050183</v>
+        <v>1.12711142984627</v>
       </c>
     </row>
     <row r="95">
@@ -7138,46 +7138,46 @@
         <v>5694.02546550393</v>
       </c>
       <c r="F95" s="6" t="n">
-        <v>0.92112903950243</v>
+        <v>0.921156516186209</v>
       </c>
       <c r="G95" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H95" s="8" t="n">
-        <v>6254.47962521761</v>
+        <v>6254.43118486861</v>
       </c>
       <c r="I95" s="9" t="n">
-        <v>5333.75813252781</v>
+        <v>5333.91900820527</v>
       </c>
       <c r="J95" s="10" t="n">
-        <v>5891.2953618642</v>
+        <v>5891.20258386422</v>
       </c>
       <c r="K95" s="11" t="n">
-        <v>6181.57198537535</v>
+        <v>6181.38759857928</v>
       </c>
       <c r="L95" s="12" t="n">
-        <v>6181.57198537535</v>
+        <v>6181.38759857928</v>
       </c>
       <c r="M95" s="13" t="n">
-        <v>6235.50241038185</v>
+        <v>6235.47922844063</v>
       </c>
       <c r="N95" s="14" t="n">
-        <v>6235.50241038185</v>
+        <v>6235.47922844063</v>
       </c>
       <c r="O95" s="15" t="n">
-        <v>0.0337781257410718</v>
+        <v>0.0338033265410155</v>
       </c>
       <c r="P95" s="16" t="n">
-        <v>0.157689363961847</v>
+        <v>0.157686538572941</v>
       </c>
       <c r="Q95" s="17" t="n">
-        <v>0.0343550844986804</v>
+        <v>0.0343811514026877</v>
       </c>
       <c r="R95" s="18" t="n">
-        <v>0.996965820344311</v>
+        <v>0.9969698353267</v>
       </c>
       <c r="S95" s="19" t="n">
-        <v>1.16906358620853</v>
+        <v>1.16902398008828</v>
       </c>
     </row>
     <row r="96">
@@ -7197,46 +7197,46 @@
         <v>6209.22803193611</v>
       </c>
       <c r="F96" s="6" t="n">
-        <v>0.960555269655066</v>
+        <v>0.960466917175441</v>
       </c>
       <c r="G96" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H96" s="8" t="n">
-        <v>6403.65678070529</v>
+        <v>6404.14019165404</v>
       </c>
       <c r="I96" s="9" t="n">
-        <v>5304.79330785751</v>
+        <v>5304.97517324952</v>
       </c>
       <c r="J96" s="10" t="n">
-        <v>5898.92694295244</v>
+        <v>5898.87013509115</v>
       </c>
       <c r="K96" s="11" t="n">
-        <v>6464.20693123243</v>
+        <v>6464.80156775865</v>
       </c>
       <c r="L96" s="12" t="n">
-        <v>6464.20693123243</v>
+        <v>6464.80156775865</v>
       </c>
       <c r="M96" s="13" t="n">
-        <v>6405.35981410067</v>
+        <v>6405.67093570381</v>
       </c>
       <c r="N96" s="14" t="n">
-        <v>6405.35981410067</v>
+        <v>6405.67093570381</v>
       </c>
       <c r="O96" s="15" t="n">
-        <v>0.0268759558992221</v>
+        <v>0.0269282445336432</v>
       </c>
       <c r="P96" s="16" t="n">
-        <v>0.151333483986831</v>
+        <v>0.151368583758934</v>
       </c>
       <c r="Q96" s="17" t="n">
-        <v>0.0272403717519234</v>
+        <v>0.0272940861524986</v>
       </c>
       <c r="R96" s="18" t="n">
-        <v>1.00026594701336</v>
+        <v>1.00023902413188</v>
       </c>
       <c r="S96" s="19" t="n">
-        <v>1.20746642562171</v>
+        <v>1.20748367834115</v>
       </c>
     </row>
     <row r="97">
@@ -7256,46 +7256,46 @@
         <v>6200.06740637572</v>
       </c>
       <c r="F97" s="6" t="n">
-        <v>0.957086614786144</v>
+        <v>0.956981457689963</v>
       </c>
       <c r="G97" s="7" t="n">
-        <v>0.738222036138048</v>
+        <v>0.740204389221789</v>
       </c>
       <c r="H97" s="8" t="n">
-        <v>6605.61534687007</v>
+        <v>6605.48274043381</v>
       </c>
       <c r="I97" s="9" t="n">
-        <v>5261.09443745191</v>
+        <v>5261.29741659729</v>
       </c>
       <c r="J97" s="10" t="n">
-        <v>5860.9649668541</v>
+        <v>5860.96411159353</v>
       </c>
       <c r="K97" s="11" t="n">
-        <v>6478.06302020126</v>
+        <v>6478.77485666434</v>
       </c>
       <c r="L97" s="12" t="n">
-        <v>6511.45340856247</v>
+        <v>6511.69300871865</v>
       </c>
       <c r="M97" s="13" t="n">
-        <v>6564.93642479668</v>
+        <v>6564.82168108839</v>
       </c>
       <c r="N97" s="14" t="n">
-        <v>6564.93642479668</v>
+        <v>6564.82168108839</v>
       </c>
       <c r="O97" s="15" t="n">
-        <v>0.0246077129112449</v>
+        <v>0.0245416635988072</v>
       </c>
       <c r="P97" s="16" t="n">
-        <v>0.13450947776637</v>
+        <v>0.134484751292255</v>
       </c>
       <c r="Q97" s="17" t="n">
-        <v>0.0249129815228679</v>
+        <v>0.0248452889606781</v>
       </c>
       <c r="R97" s="18" t="n">
-        <v>0.993841766446079</v>
+        <v>0.993844347045746</v>
       </c>
       <c r="S97" s="19" t="n">
-        <v>1.24782713993179</v>
+        <v>1.24775719015219</v>
       </c>
     </row>
     <row r="98">
@@ -7315,46 +7315,46 @@
         <v>7870.36784763967</v>
       </c>
       <c r="F98" s="6" t="n">
-        <v>1.16208409149945</v>
+        <v>1.16234715899003</v>
       </c>
       <c r="G98" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H98" s="8" t="n">
-        <v>6748.32024038277</v>
+        <v>6747.41011688783</v>
       </c>
       <c r="I98" s="9" t="n">
-        <v>5203.13410234622</v>
+        <v>5203.35796706795</v>
       </c>
       <c r="J98" s="10" t="n">
-        <v>5774.65391289274</v>
+        <v>5774.73529254708</v>
       </c>
       <c r="K98" s="11" t="n">
-        <v>6772.63195082935</v>
+        <v>6771.0991391576</v>
       </c>
       <c r="L98" s="12" t="n">
-        <v>6772.63195082935</v>
+        <v>6771.0991391576</v>
       </c>
       <c r="M98" s="13" t="n">
-        <v>6653.939128881</v>
+        <v>6653.23926537768</v>
       </c>
       <c r="N98" s="14" t="n">
-        <v>6653.939128881</v>
+        <v>6653.23926537768</v>
       </c>
       <c r="O98" s="15" t="n">
-        <v>0.0134662057583299</v>
+        <v>0.0133784983172356</v>
       </c>
       <c r="P98" s="16" t="n">
-        <v>0.103766034705342</v>
+        <v>0.103681856638946</v>
       </c>
       <c r="Q98" s="17" t="n">
-        <v>0.0135572834716484</v>
+        <v>0.0134683908542417</v>
       </c>
       <c r="R98" s="18" t="n">
-        <v>0.98601413268194</v>
+        <v>0.986043407784796</v>
       </c>
       <c r="S98" s="19" t="n">
-        <v>1.27883291070291</v>
+        <v>1.2786433890357</v>
       </c>
     </row>
     <row r="99">
@@ -7374,46 +7374,46 @@
         <v>6054.57948367958</v>
       </c>
       <c r="F99" s="6" t="n">
-        <v>0.923089387662846</v>
+        <v>0.923085648453107</v>
       </c>
       <c r="G99" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H99" s="8" t="n">
-        <v>6441.2237605388</v>
+        <v>6441.01366540176</v>
       </c>
       <c r="I99" s="9" t="n">
-        <v>5132.16635793263</v>
+        <v>5132.41055072596</v>
       </c>
       <c r="J99" s="10" t="n">
-        <v>5640.49070260046</v>
+        <v>5640.68810161311</v>
       </c>
       <c r="K99" s="11" t="n">
-        <v>6559.03920530282</v>
+        <v>6559.06577447689</v>
       </c>
       <c r="L99" s="12" t="n">
-        <v>6559.03920530282</v>
+        <v>6559.06577447689</v>
       </c>
       <c r="M99" s="13" t="n">
-        <v>6369.89496040189</v>
+        <v>6369.8168590219</v>
       </c>
       <c r="N99" s="14" t="n">
-        <v>6369.89496040189</v>
+        <v>6369.8168590219</v>
       </c>
       <c r="O99" s="15" t="n">
-        <v>-0.0436260497900103</v>
+        <v>-0.0435331250202169</v>
       </c>
       <c r="P99" s="16" t="n">
-        <v>0.0215528021922144</v>
+        <v>0.0215440747470599</v>
       </c>
       <c r="Q99" s="17" t="n">
-        <v>-0.0426881224756376</v>
+        <v>-0.0425991603564699</v>
       </c>
       <c r="R99" s="18" t="n">
-        <v>0.98892620365498</v>
+        <v>0.988946335145616</v>
       </c>
       <c r="S99" s="19" t="n">
-        <v>1.24117078756735</v>
+        <v>1.24109651713675</v>
       </c>
     </row>
     <row r="100">
@@ -7433,46 +7433,46 @@
         <v>5310.71118746629</v>
       </c>
       <c r="F100" s="6" t="n">
-        <v>0.95022995371549</v>
+        <v>0.95003153411987</v>
       </c>
       <c r="G100" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H100" s="8" t="n">
-        <v>5710.89599757455</v>
+        <v>5712.27796101655</v>
       </c>
       <c r="I100" s="9" t="n">
-        <v>5050.42619575865</v>
+        <v>5050.68873186838</v>
       </c>
       <c r="J100" s="10" t="n">
-        <v>5463.96214769905</v>
+        <v>5464.308781686</v>
       </c>
       <c r="K100" s="11" t="n">
-        <v>5588.86948017256</v>
+        <v>5590.03674797621</v>
       </c>
       <c r="L100" s="12" t="n">
-        <v>5588.86948017256</v>
+        <v>5590.03674797621</v>
       </c>
       <c r="M100" s="13" t="n">
-        <v>5725.67014302872</v>
+        <v>5726.60210862959</v>
       </c>
       <c r="N100" s="14" t="n">
-        <v>5725.67014302872</v>
+        <v>5726.60210862959</v>
       </c>
       <c r="O100" s="15" t="n">
-        <v>-0.106623381574582</v>
+        <v>-0.106448364031452</v>
       </c>
       <c r="P100" s="16" t="n">
-        <v>-0.106112644847162</v>
+        <v>-0.106010569991855</v>
       </c>
       <c r="Q100" s="17" t="n">
-        <v>-0.101135861953448</v>
+        <v>-0.100978531192979</v>
       </c>
       <c r="R100" s="18" t="n">
-        <v>1.00258701006995</v>
+        <v>1.00250760689707</v>
       </c>
       <c r="S100" s="19" t="n">
-        <v>1.13370038905571</v>
+        <v>1.13382598149365</v>
       </c>
     </row>
     <row r="101">
@@ -7492,46 +7492,46 @@
         <v>5041.77244509139</v>
       </c>
       <c r="F101" s="6" t="n">
-        <v>0.975971291826929</v>
+        <v>0.975713144600666</v>
       </c>
       <c r="G101" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H101" s="8" t="n">
-        <v>5128.27075548834</v>
+        <v>5128.48670185038</v>
       </c>
       <c r="I101" s="9" t="n">
-        <v>4961.04040290133</v>
+        <v>4961.31773430704</v>
       </c>
       <c r="J101" s="10" t="n">
-        <v>5255.14780242379</v>
+        <v>5255.67546402444</v>
       </c>
       <c r="K101" s="11" t="n">
-        <v>5165.90240646695</v>
+        <v>5167.26916408906</v>
       </c>
       <c r="L101" s="12" t="n">
-        <v>5165.90240646695</v>
+        <v>5167.26916408906</v>
       </c>
       <c r="M101" s="13" t="n">
-        <v>5213.17673925916</v>
+        <v>5213.44657549919</v>
       </c>
       <c r="N101" s="14" t="n">
-        <v>5213.17673925916</v>
+        <v>5213.44657549919</v>
       </c>
       <c r="O101" s="15" t="n">
-        <v>-0.0937701893692805</v>
+        <v>-0.0938811867370911</v>
       </c>
       <c r="P101" s="16" t="n">
-        <v>-0.205905982643143</v>
+        <v>-0.205850999652004</v>
       </c>
       <c r="Q101" s="17" t="n">
-        <v>-0.0895080210643199</v>
+        <v>-0.0896090776687821</v>
       </c>
       <c r="R101" s="18" t="n">
-        <v>1.01655645495705</v>
+        <v>1.01656626575987</v>
       </c>
       <c r="S101" s="19" t="n">
-        <v>1.05082327815963</v>
+        <v>1.05081892648171</v>
       </c>
     </row>
     <row r="102">
@@ -7551,46 +7551,46 @@
         <v>5651.60509658883</v>
       </c>
       <c r="F102" s="6" t="n">
-        <v>1.1458977427139</v>
+        <v>1.1465536447209</v>
       </c>
       <c r="G102" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H102" s="8" t="n">
-        <v>4978.46339520441</v>
+        <v>4977.32885113739</v>
       </c>
       <c r="I102" s="9" t="n">
-        <v>4867.47229349055</v>
+        <v>4867.75987436388</v>
       </c>
       <c r="J102" s="10" t="n">
-        <v>5024.75175767235</v>
+        <v>5025.49491971858</v>
       </c>
       <c r="K102" s="11" t="n">
-        <v>4932.03266393019</v>
+        <v>4929.21122584244</v>
       </c>
       <c r="L102" s="12" t="n">
-        <v>4932.03266393019</v>
+        <v>4929.21122584244</v>
       </c>
       <c r="M102" s="13" t="n">
-        <v>5017.90747832376</v>
+        <v>5017.04573801244</v>
       </c>
       <c r="N102" s="14" t="n">
-        <v>5017.90747832376</v>
+        <v>5017.04573801244</v>
       </c>
       <c r="O102" s="15" t="n">
-        <v>-0.0381763989557725</v>
+        <v>-0.0383999057896228</v>
       </c>
       <c r="P102" s="16" t="n">
-        <v>-0.245874153470408</v>
+        <v>-0.245924347840564</v>
       </c>
       <c r="Q102" s="17" t="n">
-        <v>-0.0374568656889903</v>
+        <v>-0.0376719766171077</v>
       </c>
       <c r="R102" s="18" t="n">
-        <v>1.00792294328353</v>
+        <v>1.00797955852685</v>
       </c>
       <c r="S102" s="19" t="n">
-        <v>1.03090622314058</v>
+        <v>1.03066828839171</v>
       </c>
     </row>
     <row r="103">
@@ -7610,46 +7610,46 @@
         <v>4665.68219017201</v>
       </c>
       <c r="F103" s="6" t="n">
-        <v>0.925425390387284</v>
+        <v>0.925273218935836</v>
       </c>
       <c r="G103" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H103" s="8" t="n">
-        <v>5026.4316080737</v>
+        <v>5026.29468554782</v>
       </c>
       <c r="I103" s="9" t="n">
-        <v>4773.31322040837</v>
+        <v>4773.60618800443</v>
       </c>
       <c r="J103" s="10" t="n">
-        <v>4783.03187736261</v>
+        <v>4784.03188835889</v>
       </c>
       <c r="K103" s="11" t="n">
-        <v>5041.66217896773</v>
+        <v>5042.49133627584</v>
       </c>
       <c r="L103" s="12" t="n">
-        <v>5041.66217896773</v>
+        <v>5042.49133627584</v>
       </c>
       <c r="M103" s="13" t="n">
-        <v>5008.05188991002</v>
+        <v>5008.15389165387</v>
       </c>
       <c r="N103" s="14" t="n">
-        <v>5008.05188991002</v>
+        <v>5008.15389165387</v>
       </c>
       <c r="O103" s="15" t="n">
-        <v>-0.00196601466777626</v>
+        <v>-0.00177389957680997</v>
       </c>
       <c r="P103" s="16" t="n">
-        <v>-0.213793646356446</v>
+        <v>-0.213767993257048</v>
       </c>
       <c r="Q103" s="17" t="n">
-        <v>-0.00196408332682818</v>
+        <v>-0.0017723271468707</v>
       </c>
       <c r="R103" s="18" t="n">
-        <v>0.99634338640276</v>
+        <v>0.996390821663101</v>
       </c>
       <c r="S103" s="19" t="n">
-        <v>1.04917730277955</v>
+        <v>1.04913428012534</v>
       </c>
     </row>
     <row r="104">
@@ -7669,46 +7669,46 @@
         <v>4755.00405694119</v>
       </c>
       <c r="F104" s="6" t="n">
-        <v>0.947806601200958</v>
+        <v>0.947509868899968</v>
       </c>
       <c r="G104" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H104" s="8" t="n">
-        <v>4979.21195515049</v>
+        <v>4980.68965473422</v>
       </c>
       <c r="I104" s="9" t="n">
-        <v>4682.1948867684</v>
+        <v>4682.48611828891</v>
       </c>
       <c r="J104" s="10" t="n">
-        <v>4539.78242994373</v>
+        <v>4541.06969106646</v>
       </c>
       <c r="K104" s="11" t="n">
-        <v>5016.85053777444</v>
+        <v>5018.42166822137</v>
       </c>
       <c r="L104" s="12" t="n">
-        <v>5016.85053777444</v>
+        <v>5018.42166822137</v>
       </c>
       <c r="M104" s="13" t="n">
-        <v>4915.61161283322</v>
+        <v>4917.05800619094</v>
       </c>
       <c r="N104" s="14" t="n">
-        <v>4915.61161283322</v>
+        <v>4917.05800619094</v>
       </c>
       <c r="O104" s="15" t="n">
-        <v>-0.0186308112776512</v>
+        <v>-0.0183569770600191</v>
       </c>
       <c r="P104" s="16" t="n">
-        <v>-0.141478378942557</v>
+        <v>-0.141365523059255</v>
       </c>
       <c r="Q104" s="17" t="n">
-        <v>-0.018458330526296</v>
+        <v>-0.0181895140272642</v>
       </c>
       <c r="R104" s="18" t="n">
-        <v>0.987226825672387</v>
+        <v>0.987224329770718</v>
       </c>
       <c r="S104" s="19" t="n">
-        <v>1.04985198858861</v>
+        <v>1.05009558639925</v>
       </c>
     </row>
     <row r="105">
@@ -7728,46 +7728,46 @@
         <v>4573.30287832837</v>
       </c>
       <c r="F105" s="6" t="n">
-        <v>0.996995842914409</v>
+        <v>0.996601694803687</v>
       </c>
       <c r="G105" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H105" s="8" t="n">
-        <v>4625.71630906119</v>
+        <v>4628.50551444339</v>
       </c>
       <c r="I105" s="9" t="n">
-        <v>4597.91671378333</v>
+        <v>4598.19716149521</v>
       </c>
       <c r="J105" s="10" t="n">
-        <v>4306.09083537291</v>
+        <v>4307.68394620198</v>
       </c>
       <c r="K105" s="11" t="n">
-        <v>4587.08319681628</v>
+        <v>4588.89735204517</v>
       </c>
       <c r="L105" s="12" t="n">
-        <v>4587.08319681628</v>
+        <v>4588.89735204517</v>
       </c>
       <c r="M105" s="13" t="n">
-        <v>4556.73280206019</v>
+        <v>4559.35150722393</v>
       </c>
       <c r="N105" s="14" t="n">
-        <v>4556.73280206019</v>
+        <v>4559.35150722393</v>
       </c>
       <c r="O105" s="15" t="n">
-        <v>-0.0758103079223922</v>
+        <v>-0.0755299853448246</v>
       </c>
       <c r="P105" s="16" t="n">
-        <v>-0.125920138531934</v>
+        <v>-0.125463080670896</v>
       </c>
       <c r="Q105" s="17" t="n">
-        <v>-0.0730079670729277</v>
+        <v>-0.072748073851606</v>
       </c>
       <c r="R105" s="18" t="n">
-        <v>0.985086956831773</v>
+        <v>0.985059106659014</v>
       </c>
       <c r="S105" s="19" t="n">
-        <v>0.991042919155173</v>
+        <v>0.991551981590399</v>
       </c>
     </row>
     <row r="106">
@@ -7787,46 +7787,46 @@
         <v>4670.88465711875</v>
       </c>
       <c r="F106" s="6" t="n">
-        <v>1.12125284700462</v>
+        <v>1.12226411269904</v>
       </c>
       <c r="G106" s="7" t="n">
-        <v>0.517259165555896</v>
+        <v>0.537601147454715</v>
       </c>
       <c r="H106" s="8" t="n">
-        <v>3896.77019088394</v>
+        <v>3900.70911733125</v>
       </c>
       <c r="I106" s="9" t="n">
-        <v>4524.48728244776</v>
+        <v>4524.74677361996</v>
       </c>
       <c r="J106" s="10" t="n">
-        <v>4095.4298541465</v>
+        <v>4097.33703201188</v>
       </c>
       <c r="K106" s="11" t="n">
-        <v>4165.77284026241</v>
+        <v>4162.01908647448</v>
       </c>
       <c r="L106" s="12" t="n">
-        <v>4035.91427683377</v>
+        <v>4041.18965658401</v>
       </c>
       <c r="M106" s="13" t="n">
-        <v>3926.40547632595</v>
+        <v>3930.18568776593</v>
       </c>
       <c r="N106" s="14" t="n">
-        <v>3926.40547632595</v>
+        <v>3930.18568776593</v>
       </c>
       <c r="O106" s="15" t="n">
-        <v>-0.14888150566956</v>
+        <v>-0.148493726524553</v>
       </c>
       <c r="P106" s="16" t="n">
-        <v>-0.217521348632445</v>
+        <v>-0.216633474558892</v>
       </c>
       <c r="Q106" s="17" t="n">
-        <v>-0.138328787996799</v>
+        <v>-0.137994585076658</v>
       </c>
       <c r="R106" s="18" t="n">
-        <v>1.00760508934074</v>
+        <v>1.00755672098278</v>
       </c>
       <c r="S106" s="19" t="n">
-        <v>0.867812247270092</v>
+        <v>0.868597931420069</v>
       </c>
     </row>
     <row r="107">
@@ -7846,46 +7846,46 @@
         <v>2175.26624692192</v>
       </c>
       <c r="F107" s="6" t="n">
-        <v>0.928719611116047</v>
+        <v>0.928438799018247</v>
       </c>
       <c r="G107" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H107" s="8" t="n">
-        <v>3046.71015481996</v>
+        <v>3049.46608585052</v>
       </c>
       <c r="I107" s="9" t="n">
-        <v>4465.90840280817</v>
+        <v>4466.1365982788</v>
       </c>
       <c r="J107" s="10" t="n">
-        <v>3922.67720856805</v>
+        <v>3924.89739377183</v>
       </c>
       <c r="K107" s="11" t="n">
-        <v>2342.22064537637</v>
+        <v>2342.92906459973</v>
       </c>
       <c r="L107" s="12" t="n">
-        <v>3046.71015481996</v>
+        <v>3049.46608585052</v>
       </c>
       <c r="M107" s="13" t="n">
-        <v>3160.98412839761</v>
+        <v>3163.92537249691</v>
       </c>
       <c r="N107" s="14" t="n">
-        <v>3160.98412839761</v>
+        <v>3163.92537249691</v>
       </c>
       <c r="O107" s="15" t="n">
-        <v>-0.216840958127437</v>
+        <v>-0.216873210375329</v>
       </c>
       <c r="P107" s="16" t="n">
-        <v>-0.368819613317864</v>
+        <v>-0.36824517757539</v>
       </c>
       <c r="Q107" s="17" t="n">
-        <v>-0.194942002944781</v>
+        <v>-0.194967967456161</v>
       </c>
       <c r="R107" s="18" t="n">
-        <v>1.03750733340908</v>
+        <v>1.03753420547206</v>
       </c>
       <c r="S107" s="19" t="n">
-        <v>0.707803170886796</v>
+        <v>0.708425571603935</v>
       </c>
     </row>
     <row r="108">
@@ -7905,46 +7905,46 @@
         <v>2405.16348217783</v>
       </c>
       <c r="F108" s="6" t="n">
-        <v>0.956478819268072</v>
+        <v>0.956107063033724</v>
       </c>
       <c r="G108" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H108" s="8" t="n">
-        <v>2520.51656766497</v>
+        <v>2521.66646423985</v>
       </c>
       <c r="I108" s="9" t="n">
-        <v>4425.8765267825</v>
+        <v>4426.0660558893</v>
       </c>
       <c r="J108" s="10" t="n">
-        <v>3802.41304305457</v>
+        <v>3804.95273988037</v>
       </c>
       <c r="K108" s="11" t="n">
-        <v>2514.60192711674</v>
+        <v>2515.57966170259</v>
       </c>
       <c r="L108" s="12" t="n">
-        <v>2514.60192711674</v>
+        <v>2515.57966170259</v>
       </c>
       <c r="M108" s="13" t="n">
-        <v>2624.2850934869</v>
+        <v>2626.31919297082</v>
       </c>
       <c r="N108" s="14" t="n">
-        <v>2624.2850934869</v>
+        <v>2626.31919297082</v>
       </c>
       <c r="O108" s="15" t="n">
-        <v>-0.1860748985383</v>
+        <v>-0.186230143674107</v>
       </c>
       <c r="P108" s="16" t="n">
-        <v>-0.466132538495177</v>
+        <v>-0.46587589781042</v>
       </c>
       <c r="Q108" s="17" t="n">
-        <v>-0.169788588967948</v>
+        <v>-0.169917465247236</v>
       </c>
       <c r="R108" s="18" t="n">
-        <v>1.04116954720836</v>
+        <v>1.04150141591486</v>
       </c>
       <c r="S108" s="19" t="n">
-        <v>0.5929413253186</v>
+        <v>0.593375507687296</v>
       </c>
     </row>
     <row r="109">
@@ -7964,46 +7964,46 @@
         <v>2776.70598703957</v>
       </c>
       <c r="F109" s="6" t="n">
-        <v>1.00535229645862</v>
+        <v>1.00492158659525</v>
       </c>
       <c r="G109" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H109" s="8" t="n">
-        <v>2421.22636489416</v>
+        <v>2424.65136262757</v>
       </c>
       <c r="I109" s="9" t="n">
-        <v>4407.20110738375</v>
+        <v>4407.34914779872</v>
       </c>
       <c r="J109" s="10" t="n">
-        <v>3744.83766675432</v>
+        <v>3747.71362219639</v>
       </c>
       <c r="K109" s="11" t="n">
-        <v>2761.92335445056</v>
+        <v>2763.10711609575</v>
       </c>
       <c r="L109" s="12" t="n">
-        <v>2421.22636489416</v>
+        <v>2424.65136262757</v>
       </c>
       <c r="M109" s="13" t="n">
-        <v>2465.83794901746</v>
+        <v>2469.46017266611</v>
       </c>
       <c r="N109" s="14" t="n">
-        <v>2465.83794901746</v>
+        <v>2469.46017266611</v>
       </c>
       <c r="O109" s="15" t="n">
-        <v>-0.062276825134492</v>
+        <v>-0.0615837463338475</v>
       </c>
       <c r="P109" s="16" t="n">
-        <v>-0.458858340804489</v>
+        <v>-0.458374690182706</v>
       </c>
       <c r="Q109" s="17" t="n">
-        <v>-0.060377260406151</v>
+        <v>-0.0597258020748334</v>
       </c>
       <c r="R109" s="18" t="n">
-        <v>1.01842520169536</v>
+        <v>1.01848051671642</v>
       </c>
       <c r="S109" s="19" t="n">
-        <v>0.559502026101382</v>
+        <v>0.560305092665394</v>
       </c>
     </row>
     <row r="110">
@@ -8023,46 +8023,46 @@
         <v>2640.35379506736</v>
       </c>
       <c r="F110" s="6" t="n">
-        <v>1.09632835378491</v>
+        <v>1.09742468882657</v>
       </c>
       <c r="G110" s="7" t="n">
-        <v>0.492393251756519</v>
+        <v>0.464090469881112</v>
       </c>
       <c r="H110" s="8" t="n">
-        <v>2601.29861135991</v>
+        <v>2605.62222140463</v>
       </c>
       <c r="I110" s="9" t="n">
-        <v>4411.49705100006</v>
+        <v>4411.60582135793</v>
       </c>
       <c r="J110" s="10" t="n">
-        <v>3753.71233323585</v>
+        <v>3756.94372718793</v>
       </c>
       <c r="K110" s="11" t="n">
-        <v>2408.36040220244</v>
+        <v>2405.95443309243</v>
       </c>
       <c r="L110" s="12" t="n">
-        <v>2506.29713916478</v>
+        <v>2512.9583037067</v>
       </c>
       <c r="M110" s="13" t="n">
-        <v>2627.72920679092</v>
+        <v>2632.09632916578</v>
       </c>
       <c r="N110" s="14" t="n">
-        <v>2627.72920679092</v>
+        <v>2632.09632916578</v>
       </c>
       <c r="O110" s="15" t="n">
-        <v>0.0635883652792078</v>
+        <v>0.0637810388433592</v>
       </c>
       <c r="P110" s="16" t="n">
-        <v>-0.330754497304297</v>
+        <v>-0.330287030111808</v>
       </c>
       <c r="Q110" s="17" t="n">
-        <v>0.0656536484232342</v>
+        <v>0.0658589914912819</v>
       </c>
       <c r="R110" s="18" t="n">
-        <v>1.01016053878459</v>
+        <v>1.0101603784093</v>
       </c>
       <c r="S110" s="19" t="n">
-        <v>0.595654757650859</v>
+        <v>0.596629988205883</v>
       </c>
     </row>
     <row r="111">
@@ -8082,46 +8082,46 @@
         <v>2885.42830497867</v>
       </c>
       <c r="F111" s="6" t="n">
-        <v>0.937711443678087</v>
+        <v>0.937491728723069</v>
       </c>
       <c r="G111" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H111" s="8" t="n">
-        <v>3009.01857983908</v>
+        <v>3011.5220244965</v>
       </c>
       <c r="I111" s="9" t="n">
-        <v>4439.13802980557</v>
+        <v>4439.21683780215</v>
       </c>
       <c r="J111" s="10" t="n">
-        <v>3826.18023955846</v>
+        <v>3829.7914300252</v>
       </c>
       <c r="K111" s="11" t="n">
-        <v>3077.09618393996</v>
+        <v>3077.81734662217</v>
       </c>
       <c r="L111" s="12" t="n">
-        <v>3077.09618393996</v>
+        <v>3077.81734662217</v>
       </c>
       <c r="M111" s="13" t="n">
-        <v>3052.29669024517</v>
+        <v>3054.78144935867</v>
       </c>
       <c r="N111" s="14" t="n">
-        <v>3052.29669024517</v>
+        <v>3054.78144935867</v>
       </c>
       <c r="O111" s="15" t="n">
-        <v>0.149774266685016</v>
+        <v>0.148927439372621</v>
       </c>
       <c r="P111" s="16" t="n">
-        <v>-0.0343840505796955</v>
+        <v>-0.034496364575157</v>
       </c>
       <c r="Q111" s="17" t="n">
-        <v>0.161572007631923</v>
+        <v>0.160588773104231</v>
       </c>
       <c r="R111" s="18" t="n">
-        <v>1.01438279932735</v>
+        <v>1.01436463838228</v>
       </c>
       <c r="S111" s="19" t="n">
-        <v>0.687587696023694</v>
+        <v>0.68813521865967</v>
       </c>
     </row>
     <row r="112">
@@ -8141,46 +8141,46 @@
         <v>3444.49013745048</v>
       </c>
       <c r="F112" s="6" t="n">
-        <v>0.970635106624008</v>
+        <v>0.970133309846143</v>
       </c>
       <c r="G112" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H112" s="8" t="n">
-        <v>3632.30105709357</v>
+        <v>3633.75158220778</v>
       </c>
       <c r="I112" s="9" t="n">
-        <v>4489.30696602952</v>
+        <v>4489.37630366799</v>
       </c>
       <c r="J112" s="10" t="n">
-        <v>3953.14750681104</v>
+        <v>3957.18517876095</v>
       </c>
       <c r="K112" s="11" t="n">
-        <v>3548.69725393598</v>
+        <v>3550.53280048363</v>
       </c>
       <c r="L112" s="12" t="n">
-        <v>3548.69725393598</v>
+        <v>3550.53280048363</v>
       </c>
       <c r="M112" s="13" t="n">
-        <v>3624.97037740167</v>
+        <v>3626.39038269609</v>
       </c>
       <c r="N112" s="14" t="n">
-        <v>3624.97037740167</v>
+        <v>3626.39038269609</v>
       </c>
       <c r="O112" s="15" t="n">
-        <v>0.171951796079718</v>
+        <v>0.171529717222783</v>
       </c>
       <c r="P112" s="16" t="n">
-        <v>0.381317291478098</v>
+        <v>0.380788135883065</v>
       </c>
       <c r="Q112" s="17" t="n">
-        <v>0.187620583866145</v>
+        <v>0.18711942010039</v>
       </c>
       <c r="R112" s="18" t="n">
-        <v>0.99798180834224</v>
+        <v>0.997974214982738</v>
       </c>
       <c r="S112" s="19" t="n">
-        <v>0.807467701547642</v>
+        <v>0.807771533817112</v>
       </c>
     </row>
     <row r="113">
@@ -8200,46 +8200,46 @@
         <v>4318.55493831423</v>
       </c>
       <c r="F113" s="6" t="n">
-        <v>0.998419592640646</v>
+        <v>0.998122429312809</v>
       </c>
       <c r="G113" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H113" s="8" t="n">
-        <v>4198.90382675011</v>
+        <v>4198.87973935827</v>
       </c>
       <c r="I113" s="9" t="n">
-        <v>4560.3355057475</v>
+        <v>4560.42745081015</v>
       </c>
       <c r="J113" s="10" t="n">
-        <v>4121.77483580443</v>
+        <v>4126.29355103097</v>
       </c>
       <c r="K113" s="11" t="n">
-        <v>4325.39081779476</v>
+        <v>4326.67858319494</v>
       </c>
       <c r="L113" s="12" t="n">
-        <v>4325.39081779476</v>
+        <v>4326.67858319494</v>
       </c>
       <c r="M113" s="13" t="n">
-        <v>4211.20674711855</v>
+        <v>4211.29897511004</v>
       </c>
       <c r="N113" s="14" t="n">
-        <v>4211.20674711855</v>
+        <v>4211.29897511004</v>
       </c>
       <c r="O113" s="15" t="n">
-        <v>0.149903128369843</v>
+        <v>0.149533376644938</v>
       </c>
       <c r="P113" s="16" t="n">
-        <v>0.707819748980889</v>
+        <v>0.70535205294013</v>
       </c>
       <c r="Q113" s="17" t="n">
-        <v>0.161721699402433</v>
+        <v>0.161292230203602</v>
       </c>
       <c r="R113" s="18" t="n">
-        <v>1.00293003147394</v>
+        <v>1.00295774981011</v>
       </c>
       <c r="S113" s="19" t="n">
-        <v>0.923442308534332</v>
+        <v>0.923443914092288</v>
       </c>
     </row>
     <row r="114">
@@ -8259,46 +8259,46 @@
         <v>5038.84746379941</v>
       </c>
       <c r="F114" s="6" t="n">
-        <v>1.08470826221608</v>
+        <v>1.08565294680484</v>
       </c>
       <c r="G114" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H114" s="8" t="n">
-        <v>4789.41758565675</v>
+        <v>4787.37528561545</v>
       </c>
       <c r="I114" s="9" t="n">
-        <v>4649.96741396498</v>
+        <v>4650.12673389375</v>
       </c>
       <c r="J114" s="10" t="n">
-        <v>4317.20067608507</v>
+        <v>4322.25186257961</v>
       </c>
       <c r="K114" s="11" t="n">
-        <v>4645.34809894869</v>
+        <v>4641.30593356664</v>
       </c>
       <c r="L114" s="12" t="n">
-        <v>4645.34809894869</v>
+        <v>4641.30593356664</v>
       </c>
       <c r="M114" s="13" t="n">
-        <v>4771.36492268739</v>
+        <v>4769.8137701521</v>
       </c>
       <c r="N114" s="14" t="n">
-        <v>4771.36492268739</v>
+        <v>4769.8137701521</v>
       </c>
       <c r="O114" s="15" t="n">
-        <v>0.124883166390005</v>
+        <v>0.12453611698046</v>
       </c>
       <c r="P114" s="16" t="n">
-        <v>0.815774970402812</v>
+        <v>0.812172950244507</v>
       </c>
       <c r="Q114" s="17" t="n">
-        <v>0.133016070975883</v>
+        <v>0.132622926641647</v>
       </c>
       <c r="R114" s="18" t="n">
-        <v>0.996230718527567</v>
+        <v>0.996331702777487</v>
       </c>
       <c r="S114" s="19" t="n">
-        <v>1.02610717407563</v>
+        <v>1.02573844609137</v>
       </c>
     </row>
     <row r="115">
@@ -8318,46 +8318,46 @@
         <v>5155.69426033944</v>
       </c>
       <c r="F115" s="6" t="n">
-        <v>0.942648191419015</v>
+        <v>0.9425461787813</v>
       </c>
       <c r="G115" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H115" s="8" t="n">
-        <v>5412.64326316968</v>
+        <v>5412.09730846092</v>
       </c>
       <c r="I115" s="9" t="n">
-        <v>4755.79961525752</v>
+        <v>4756.08451454174</v>
       </c>
       <c r="J115" s="10" t="n">
-        <v>4525.58155710935</v>
+        <v>4531.19735431208</v>
       </c>
       <c r="K115" s="11" t="n">
-        <v>5469.37267505741</v>
+        <v>5469.96463028017</v>
       </c>
       <c r="L115" s="12" t="n">
-        <v>5469.37267505741</v>
+        <v>5469.96463028017</v>
       </c>
       <c r="M115" s="13" t="n">
-        <v>5345.06809322883</v>
+        <v>5345.02854622695</v>
       </c>
       <c r="N115" s="14" t="n">
-        <v>5345.06809322883</v>
+        <v>5345.02854622695</v>
       </c>
       <c r="O115" s="15" t="n">
-        <v>0.11354187272653</v>
+        <v>0.113859622956183</v>
       </c>
       <c r="P115" s="16" t="n">
-        <v>0.751162693427255</v>
+        <v>0.749725351824795</v>
       </c>
       <c r="Q115" s="17" t="n">
-        <v>0.120238795363049</v>
+        <v>0.120594808056104</v>
       </c>
       <c r="R115" s="18" t="n">
-        <v>0.987515310606064</v>
+        <v>0.987607620777787</v>
       </c>
       <c r="S115" s="19" t="n">
-        <v>1.12390523689872</v>
+        <v>1.12382959762059</v>
       </c>
     </row>
     <row r="116">
@@ -8377,46 +8377,46 @@
         <v>5721.03663102072</v>
       </c>
       <c r="F116" s="6" t="n">
-        <v>0.987035891434982</v>
+        <v>0.986576308992848</v>
       </c>
       <c r="G116" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H116" s="8" t="n">
-        <v>5657.07980504644</v>
+        <v>5661.50329735893</v>
       </c>
       <c r="I116" s="9" t="n">
-        <v>4875.42614712878</v>
+        <v>4875.90564137679</v>
       </c>
       <c r="J116" s="10" t="n">
-        <v>4734.71474544799</v>
+        <v>4740.86253748853</v>
       </c>
       <c r="K116" s="11" t="n">
-        <v>5796.1789238518</v>
+        <v>5798.87899078082</v>
       </c>
       <c r="L116" s="12" t="n">
-        <v>5796.1789238518</v>
+        <v>5798.87899078082</v>
       </c>
       <c r="M116" s="13" t="n">
-        <v>5614.70307693081</v>
+        <v>5617.5234389497</v>
       </c>
       <c r="N116" s="14" t="n">
-        <v>5614.70307693081</v>
+        <v>5617.5234389497</v>
       </c>
       <c r="O116" s="15" t="n">
-        <v>0.0492144224509366</v>
+        <v>0.0497240123589068</v>
       </c>
       <c r="P116" s="16" t="n">
-        <v>0.548896264624195</v>
+        <v>0.549067487536538</v>
       </c>
       <c r="Q116" s="17" t="n">
-        <v>0.0504455657063669</v>
+        <v>0.0509809985795304</v>
       </c>
       <c r="R116" s="18" t="n">
-        <v>0.992509080731399</v>
+        <v>0.992231770238525</v>
       </c>
       <c r="S116" s="19" t="n">
-        <v>1.15163329470951</v>
+        <v>1.15209847198017</v>
       </c>
     </row>
     <row r="117">
@@ -8436,46 +8436,46 @@
         <v>5275.14336147936</v>
       </c>
       <c r="F117" s="6" t="n">
-        <v>0.977406600762914</v>
+        <v>0.976449640521288</v>
       </c>
       <c r="G117" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H117" s="8" t="n">
-        <v>5642.64498098043</v>
+        <v>5642.55092944371</v>
       </c>
       <c r="I117" s="9" t="n">
-        <v>5006.88703024474</v>
+        <v>5007.64113809396</v>
       </c>
       <c r="J117" s="10" t="n">
-        <v>4937.11646326144</v>
+        <v>4943.67375974891</v>
       </c>
       <c r="K117" s="11" t="n">
-        <v>5397.08178496222</v>
+        <v>5402.37114395697</v>
       </c>
       <c r="L117" s="12" t="n">
-        <v>5397.08178496222</v>
+        <v>5402.37114395697</v>
       </c>
       <c r="M117" s="13" t="n">
-        <v>5632.03405364325</v>
+        <v>5632.32765195105</v>
       </c>
       <c r="N117" s="14" t="n">
-        <v>5632.03405364325</v>
+        <v>5632.32765195105</v>
       </c>
       <c r="O117" s="15" t="n">
-        <v>0.00308195883470447</v>
+        <v>0.00263189644508422</v>
       </c>
       <c r="P117" s="16" t="n">
-        <v>0.337391961935109</v>
+        <v>0.337432389683016</v>
       </c>
       <c r="Q117" s="17" t="n">
-        <v>0.00308671295257779</v>
+        <v>0.00263536292500466</v>
       </c>
       <c r="R117" s="18" t="n">
-        <v>0.998119511794035</v>
+        <v>0.998188181618475</v>
       </c>
       <c r="S117" s="19" t="n">
-        <v>1.12485742530683</v>
+        <v>1.124746661478</v>
       </c>
     </row>
     <row r="118">
@@ -8495,46 +8495,46 @@
         <v>6493.81689277761</v>
       </c>
       <c r="F118" s="6" t="n">
-        <v>1.09364137558929</v>
+        <v>1.09587535426086</v>
       </c>
       <c r="G118" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H118" s="8" t="n">
-        <v>5756.91378782402</v>
+        <v>5751.93441874867</v>
       </c>
       <c r="I118" s="9" t="n">
-        <v>5148.79775575692</v>
+        <v>5149.91888673164</v>
       </c>
       <c r="J118" s="10" t="n">
-        <v>5130.61025360219</v>
+        <v>5137.34745099966</v>
       </c>
       <c r="K118" s="11" t="n">
-        <v>5937.79372079675</v>
+        <v>5925.68932910944</v>
       </c>
       <c r="L118" s="12" t="n">
-        <v>5937.79372079675</v>
+        <v>5925.68932910944</v>
       </c>
       <c r="M118" s="13" t="n">
-        <v>5753.08989006544</v>
+        <v>5749.20291300958</v>
       </c>
       <c r="N118" s="14" t="n">
-        <v>5753.08989006544</v>
+        <v>5749.20291300958</v>
       </c>
       <c r="O118" s="15" t="n">
-        <v>0.0212664173678209</v>
+        <v>0.0205384273742331</v>
       </c>
       <c r="P118" s="16" t="n">
-        <v>0.205753486326322</v>
+        <v>0.205330687958127</v>
       </c>
       <c r="Q118" s="17" t="n">
-        <v>0.0214941591739639</v>
+        <v>0.0207507922622436</v>
       </c>
       <c r="R118" s="18" t="n">
-        <v>0.999335772968032</v>
+        <v>0.999525115284661</v>
       </c>
       <c r="S118" s="19" t="n">
-        <v>1.11736567699379</v>
+        <v>1.11636766315329</v>
       </c>
     </row>
     <row r="119">
@@ -8554,46 +8554,46 @@
         <v>5401.39020454682</v>
       </c>
       <c r="F119" s="6" t="n">
-        <v>0.94105951549815</v>
+        <v>0.94050705803842</v>
       </c>
       <c r="G119" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H119" s="8" t="n">
-        <v>5799.02042505393</v>
+        <v>5798.23224797383</v>
       </c>
       <c r="I119" s="9" t="n">
-        <v>5300.01768653847</v>
+        <v>5301.61347558193</v>
       </c>
       <c r="J119" s="10" t="n">
-        <v>5315.31948613121</v>
+        <v>5321.89352806826</v>
       </c>
       <c r="K119" s="11" t="n">
-        <v>5739.69033370604</v>
+        <v>5743.06184986246</v>
       </c>
       <c r="L119" s="12" t="n">
-        <v>5739.69033370604</v>
+        <v>5743.06184986246</v>
       </c>
       <c r="M119" s="13" t="n">
-        <v>5751.18350868386</v>
+        <v>5751.72660923032</v>
       </c>
       <c r="N119" s="14" t="n">
-        <v>5751.18350868386</v>
+        <v>5751.72660923032</v>
       </c>
       <c r="O119" s="15" t="n">
-        <v>-0.000331421434966943</v>
+        <v>0.000438868224758535</v>
       </c>
       <c r="P119" s="16" t="n">
-        <v>0.0759794652512473</v>
+        <v>0.0760890347892444</v>
       </c>
       <c r="Q119" s="17" t="n">
-        <v>-0.000331366520949894</v>
+        <v>0.000438964541507492</v>
       </c>
       <c r="R119" s="18" t="n">
-        <v>0.991750862583032</v>
+        <v>0.991979341848585</v>
       </c>
       <c r="S119" s="19" t="n">
-        <v>1.08512534274957</v>
+        <v>1.08490115994339</v>
       </c>
     </row>
     <row r="120">
@@ -8613,46 +8613,46 @@
         <v>5551.08998343361</v>
       </c>
       <c r="F120" s="6" t="n">
-        <v>0.993473060620363</v>
+        <v>0.992135354775361</v>
       </c>
       <c r="G120" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H120" s="8" t="n">
-        <v>5614.71876408106</v>
+        <v>5627.00877104371</v>
       </c>
       <c r="I120" s="9" t="n">
-        <v>5459.89930794071</v>
+        <v>5462.08434946338</v>
       </c>
       <c r="J120" s="10" t="n">
-        <v>5495.40344784545</v>
+        <v>5501.26361717274</v>
       </c>
       <c r="K120" s="11" t="n">
-        <v>5587.55964652659</v>
+        <v>5595.09340808693</v>
       </c>
       <c r="L120" s="12" t="n">
-        <v>5587.55964652659</v>
+        <v>5595.09340808693</v>
       </c>
       <c r="M120" s="13" t="n">
-        <v>5593.24499238622</v>
+        <v>5601.06727316237</v>
       </c>
       <c r="N120" s="14" t="n">
-        <v>5593.24499238622</v>
+        <v>5601.06727316237</v>
       </c>
       <c r="O120" s="15" t="n">
-        <v>-0.0278460429521086</v>
+        <v>-0.0265429255249599</v>
       </c>
       <c r="P120" s="16" t="n">
-        <v>-0.00382176657439925</v>
+        <v>-0.00292943429007009</v>
       </c>
       <c r="Q120" s="17" t="n">
-        <v>-0.0274619156316549</v>
+        <v>-0.0261937582057841</v>
       </c>
       <c r="R120" s="18" t="n">
-        <v>0.996175450169968</v>
+        <v>0.995389824516564</v>
       </c>
       <c r="S120" s="19" t="n">
-        <v>1.02442273692696</v>
+        <v>1.02544503431417</v>
       </c>
     </row>
     <row r="121">
@@ -8672,46 +8672,46 @@
         <v>5250.36031896855</v>
       </c>
       <c r="F121" s="6" t="n">
-        <v>0.961926797669157</v>
+        <v>0.959667467777816</v>
       </c>
       <c r="G121" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H121" s="8" t="n">
-        <v>5343.59371324115</v>
+        <v>5341.26406542263</v>
       </c>
       <c r="I121" s="9" t="n">
-        <v>5628.06990071946</v>
+        <v>5630.96685842848</v>
       </c>
       <c r="J121" s="10" t="n">
-        <v>5677.14327997974</v>
+        <v>5681.51518614008</v>
       </c>
       <c r="K121" s="11" t="n">
-        <v>5458.17034278564</v>
+        <v>5471.02042661315</v>
       </c>
       <c r="L121" s="12" t="n">
-        <v>5458.17034278564</v>
+        <v>5471.02042661315</v>
       </c>
       <c r="M121" s="13" t="n">
-        <v>5365.57753071063</v>
+        <v>5365.63918542427</v>
       </c>
       <c r="N121" s="14" t="n">
-        <v>5365.57753071063</v>
+        <v>5365.63918542427</v>
       </c>
       <c r="O121" s="15" t="n">
-        <v>-0.041555600136562</v>
+        <v>-0.0429416552153472</v>
       </c>
       <c r="P121" s="16" t="n">
-        <v>-0.0473108863324874</v>
+        <v>-0.0473496009122271</v>
       </c>
       <c r="Q121" s="17" t="n">
-        <v>-0.0407040031297564</v>
+        <v>-0.042032719168748</v>
       </c>
       <c r="R121" s="18" t="n">
-        <v>1.00411405107671</v>
+        <v>1.00456354894704</v>
       </c>
       <c r="S121" s="19" t="n">
-        <v>0.953360143950011</v>
+        <v>0.952880618963852</v>
       </c>
     </row>
     <row r="122">
@@ -8731,46 +8731,46 @@
         <v>5507.50065379131</v>
       </c>
       <c r="F122" s="6" t="n">
-        <v>1.11073930679783</v>
+        <v>1.1181783239358</v>
       </c>
       <c r="G122" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H122" s="8" t="n">
-        <v>5071.79381763342</v>
+        <v>5062.94087115105</v>
       </c>
       <c r="I122" s="9" t="n">
-        <v>5804.23653334215</v>
+        <v>5807.97948319137</v>
       </c>
       <c r="J122" s="10" t="n">
-        <v>5867.28090476231</v>
+        <v>5869.17485175186</v>
       </c>
       <c r="K122" s="11" t="n">
-        <v>4958.40979074467</v>
+        <v>4925.42248038383</v>
       </c>
       <c r="L122" s="12" t="n">
-        <v>4958.40979074467</v>
+        <v>4925.42248038383</v>
       </c>
       <c r="M122" s="13" t="n">
-        <v>5157.64496418412</v>
+        <v>5150.47564841264</v>
       </c>
       <c r="N122" s="14" t="n">
-        <v>5157.64496418412</v>
+        <v>5150.47564841264</v>
       </c>
       <c r="O122" s="15" t="n">
-        <v>-0.0395239451178418</v>
+        <v>-0.0409264395342206</v>
       </c>
       <c r="P122" s="16" t="n">
-        <v>-0.103500021251111</v>
+        <v>-0.10414091721169</v>
       </c>
       <c r="Q122" s="17" t="n">
-        <v>-0.038753063456149</v>
+        <v>-0.0401002619773839</v>
       </c>
       <c r="R122" s="18" t="n">
-        <v>1.01692717599288</v>
+        <v>1.01728931454846</v>
       </c>
       <c r="S122" s="19" t="n">
-        <v>0.88860006558249</v>
+        <v>0.886793016972324</v>
       </c>
     </row>
     <row r="123">
@@ -8790,46 +8790,46 @@
         <v>4914.98939569154</v>
       </c>
       <c r="F123" s="6" t="n">
-        <v>0.935192710780913</v>
+        <v>0.930862644273658</v>
       </c>
       <c r="G123" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H123" s="8" t="n">
-        <v>5255.18652323692</v>
+        <v>5267.29004475133</v>
       </c>
       <c r="I123" s="9" t="n">
-        <v>5988.00008705247</v>
+        <v>5992.74073794629</v>
       </c>
       <c r="J123" s="10" t="n">
-        <v>6071.46337973542</v>
+        <v>6069.716756992</v>
       </c>
       <c r="K123" s="11" t="n">
-        <v>5255.58993246149</v>
+        <v>5280.03720626973</v>
       </c>
       <c r="L123" s="12" t="n">
-        <v>5255.58993246149</v>
+        <v>5280.03720626973</v>
       </c>
       <c r="M123" s="13" t="n">
-        <v>5360.6074760561</v>
+        <v>5367.30740542785</v>
       </c>
       <c r="N123" s="14" t="n">
-        <v>5360.6074760561</v>
+        <v>5367.30740542785</v>
       </c>
       <c r="O123" s="15" t="n">
-        <v>0.038597230725523</v>
+        <v>0.0412372991854631</v>
       </c>
       <c r="P123" s="16" t="n">
-        <v>-0.0679122883208327</v>
+        <v>-0.0668354443664891</v>
       </c>
       <c r="Q123" s="17" t="n">
-        <v>0.0393517803729033</v>
+        <v>0.0420993655376356</v>
       </c>
       <c r="R123" s="18" t="n">
-        <v>1.02006036367178</v>
+        <v>1.01898839058164</v>
       </c>
       <c r="S123" s="19" t="n">
-        <v>0.895225016386866</v>
+        <v>0.89563484224202</v>
       </c>
     </row>
     <row r="124">
@@ -8849,46 +8849,46 @@
         <v>5928.99236351443</v>
       </c>
       <c r="F124" s="6" t="n">
-        <v>0.992658788245188</v>
+        <v>0.990851803087674</v>
       </c>
       <c r="G124" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H124" s="8" t="n">
-        <v>5971.12455846846</v>
+        <v>5966.05529466858</v>
       </c>
       <c r="I124" s="9" t="n">
-        <v>6178.43280138002</v>
+        <v>6184.31753876074</v>
       </c>
       <c r="J124" s="10" t="n">
-        <v>6290.79340687125</v>
+        <v>6283.8962829876</v>
       </c>
       <c r="K124" s="11" t="n">
-        <v>5972.84024855675</v>
+        <v>5983.73272878812</v>
       </c>
       <c r="L124" s="12" t="n">
-        <v>5972.84024855675</v>
+        <v>5983.73272878812</v>
       </c>
       <c r="M124" s="13" t="n">
-        <v>5981.31064303143</v>
+        <v>5978.25240581796</v>
       </c>
       <c r="N124" s="14" t="n">
-        <v>5981.31064303143</v>
+        <v>5978.25240581796</v>
       </c>
       <c r="O124" s="15" t="n">
-        <v>0.10956241127769</v>
+        <v>0.107801916911026</v>
       </c>
       <c r="P124" s="16" t="n">
-        <v>0.0693811286960366</v>
+        <v>0.0673416536992655</v>
       </c>
       <c r="Q124" s="17" t="n">
-        <v>0.115789706623323</v>
+        <v>0.113827093222249</v>
       </c>
       <c r="R124" s="18" t="n">
-        <v>1.00170589048398</v>
+        <v>1.00204441805296</v>
       </c>
       <c r="S124" s="19" t="n">
-        <v>0.968095119800516</v>
+        <v>0.966679406150922</v>
       </c>
     </row>
     <row r="125">
@@ -8908,46 +8908,46 @@
         <v>5702.27255722485</v>
       </c>
       <c r="F125" s="6" t="n">
-        <v>0.949905591257464</v>
+        <v>0.946150288642704</v>
       </c>
       <c r="G125" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H125" s="8" t="n">
-        <v>6723.97214255071</v>
+        <v>6665.50695942586</v>
       </c>
       <c r="I125" s="9" t="n">
-        <v>6374.14915950777</v>
+        <v>6381.33136199489</v>
       </c>
       <c r="J125" s="10" t="n">
-        <v>6522.2943209056</v>
+        <v>6508.52041311213</v>
       </c>
       <c r="K125" s="11" t="n">
-        <v>6002.98872825489</v>
+        <v>6026.81479430189</v>
       </c>
       <c r="L125" s="12" t="n">
-        <v>6723.97214255071</v>
+        <v>6665.50695942586</v>
       </c>
       <c r="M125" s="13" t="n">
-        <v>6645.08811343644</v>
+        <v>6611.53528942518</v>
       </c>
       <c r="N125" s="14" t="n">
-        <v>6645.08811343644</v>
+        <v>6611.53528942518</v>
       </c>
       <c r="O125" s="15" t="n">
-        <v>0.105238237164562</v>
+        <v>0.10068760916038</v>
       </c>
       <c r="P125" s="16" t="n">
-        <v>0.238466516493769</v>
+        <v>0.232199009464779</v>
       </c>
       <c r="Q125" s="17" t="n">
-        <v>0.11097525442494</v>
+        <v>0.105931105048513</v>
       </c>
       <c r="R125" s="18" t="n">
-        <v>0.988268239748485</v>
+        <v>0.991902840949802</v>
       </c>
       <c r="S125" s="19" t="n">
-        <v>1.04250590112479</v>
+        <v>1.03607459233371</v>
       </c>
     </row>
     <row r="126">
@@ -8967,46 +8967,46 @@
         <v>9211.04255893011</v>
       </c>
       <c r="F126" s="6" t="n">
-        <v>1.13089488910937</v>
+        <v>1.1443115916447</v>
       </c>
       <c r="G126" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H126" s="8" t="n">
-        <v>7159.56792008758</v>
+        <v>7131.3945100609</v>
       </c>
       <c r="I126" s="9" t="n">
-        <v>6573.63514927317</v>
+        <v>6582.27831850273</v>
       </c>
       <c r="J126" s="10" t="n">
-        <v>6761.39969078269</v>
+        <v>6738.89531296809</v>
       </c>
       <c r="K126" s="11" t="n">
-        <v>8144.91483482096</v>
+        <v>8049.41820583259</v>
       </c>
       <c r="L126" s="12" t="n">
-        <v>7159.56792008758</v>
+        <v>7131.3945100609</v>
       </c>
       <c r="M126" s="13" t="n">
-        <v>7067.3867107934</v>
+        <v>7054.11257073709</v>
       </c>
       <c r="N126" s="14" t="n">
-        <v>7067.3867107934</v>
+        <v>7054.11257073709</v>
       </c>
       <c r="O126" s="15" t="n">
-        <v>0.061612828667796</v>
+        <v>0.0647948955297716</v>
       </c>
       <c r="P126" s="16" t="n">
-        <v>0.370273983546943</v>
+        <v>0.369604101110768</v>
       </c>
       <c r="Q126" s="17" t="n">
-        <v>0.0635504887441702</v>
+        <v>0.0669401677428518</v>
       </c>
       <c r="R126" s="18" t="n">
-        <v>0.987124752453909</v>
+        <v>0.98916313783864</v>
       </c>
       <c r="S126" s="19" t="n">
-        <v>1.07511088618522</v>
+        <v>1.07168251316691</v>
       </c>
     </row>
     <row r="127">
@@ -9026,46 +9026,46 @@
         <v>6724.14325832842</v>
       </c>
       <c r="F127" s="6" t="n">
-        <v>0.930491959896248</v>
+        <v>0.922612636671384</v>
       </c>
       <c r="G127" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H127" s="8" t="n">
-        <v>7272.46208154932</v>
+        <v>7306.42780191736</v>
       </c>
       <c r="I127" s="9" t="n">
-        <v>6775.59539787808</v>
+        <v>6785.8321288866</v>
       </c>
       <c r="J127" s="10" t="n">
-        <v>7004.55147455499</v>
+        <v>6971.11208088951</v>
       </c>
       <c r="K127" s="11" t="n">
-        <v>7226.43886044773</v>
+        <v>7288.1543034007</v>
       </c>
       <c r="L127" s="12" t="n">
-        <v>7226.43886044773</v>
+        <v>7288.1543034007</v>
       </c>
       <c r="M127" s="13" t="n">
-        <v>7223.09387188955</v>
+        <v>7252.67606502294</v>
       </c>
       <c r="N127" s="14" t="n">
-        <v>7223.09387188955</v>
+        <v>7252.67606502294</v>
       </c>
       <c r="O127" s="15" t="n">
-        <v>0.0217925943749924</v>
+        <v>0.0277597230657722</v>
       </c>
       <c r="P127" s="16" t="n">
-        <v>0.347439428115657</v>
+        <v>0.351268991540982</v>
       </c>
       <c r="Q127" s="17" t="n">
-        <v>0.0220317873448681</v>
+        <v>0.0281486143430083</v>
       </c>
       <c r="R127" s="18" t="n">
-        <v>0.993211623641872</v>
+        <v>0.992643226163089</v>
       </c>
       <c r="S127" s="19" t="n">
-        <v>1.06604563108234</v>
+        <v>1.06879685899523</v>
       </c>
     </row>
     <row r="128">
@@ -9085,46 +9085,46 @@
         <v>7175.59727581782</v>
       </c>
       <c r="F128" s="6" t="n">
-        <v>0.985668464812691</v>
+        <v>0.982554587502737</v>
       </c>
       <c r="G128" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H128" s="8" t="n">
-        <v>7191.79622619522</v>
+        <v>7238.87379428502</v>
       </c>
       <c r="I128" s="9" t="n">
-        <v>6979.10074050611</v>
+        <v>6991.00971136858</v>
       </c>
       <c r="J128" s="10" t="n">
-        <v>7250.18247142148</v>
+        <v>7203.22431119592</v>
       </c>
       <c r="K128" s="11" t="n">
-        <v>7279.92984657515</v>
+        <v>7303.00114322944</v>
       </c>
       <c r="L128" s="12" t="n">
-        <v>7279.92984657515</v>
+        <v>7303.00114322944</v>
       </c>
       <c r="M128" s="13" t="n">
-        <v>7250.86360622431</v>
+        <v>7286.35185868603</v>
       </c>
       <c r="N128" s="14" t="n">
-        <v>7250.86360622431</v>
+        <v>7286.35185868603</v>
       </c>
       <c r="O128" s="15" t="n">
-        <v>0.00383720464158265</v>
+        <v>0.00463247667765424</v>
       </c>
       <c r="P128" s="16" t="n">
-        <v>0.212253306835349</v>
+        <v>0.218809672805894</v>
       </c>
       <c r="Q128" s="17" t="n">
-        <v>0.003844576136943</v>
+        <v>0.00464322318564658</v>
       </c>
       <c r="R128" s="18" t="n">
-        <v>1.00821316096443</v>
+        <v>1.00655876393901</v>
       </c>
       <c r="S128" s="19" t="n">
-        <v>1.03893952470709</v>
+        <v>1.04224599299829</v>
       </c>
     </row>
     <row r="129">
@@ -9144,46 +9144,46 @@
         <v>6831.01219133661</v>
       </c>
       <c r="F129" s="6" t="n">
-        <v>0.946496419524731</v>
+        <v>0.94204604660113</v>
       </c>
       <c r="G129" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H129" s="8" t="n">
-        <v>7415.79916705863</v>
+        <v>7465.47169778484</v>
       </c>
       <c r="I129" s="9" t="n">
-        <v>7183.503789505</v>
+        <v>7197.14193552982</v>
       </c>
       <c r="J129" s="10" t="n">
-        <v>7497.8349175106</v>
+        <v>7434.87080931939</v>
       </c>
       <c r="K129" s="11" t="n">
-        <v>7217.15587129923</v>
+        <v>7251.25084488456</v>
       </c>
       <c r="L129" s="12" t="n">
-        <v>7217.15587129923</v>
+        <v>7251.25084488456</v>
       </c>
       <c r="M129" s="13" t="n">
-        <v>7450.98145509224</v>
+        <v>7462.36617699143</v>
       </c>
       <c r="N129" s="14" t="n">
-        <v>7450.98145509224</v>
+        <v>7462.36617699143</v>
       </c>
       <c r="O129" s="15" t="n">
-        <v>0.0272251827807207</v>
+        <v>0.0238695559704954</v>
       </c>
       <c r="P129" s="16" t="n">
-        <v>0.121276547112487</v>
+        <v>0.128688852183411</v>
       </c>
       <c r="Q129" s="17" t="n">
-        <v>0.0275991743516097</v>
+        <v>0.0241567140482746</v>
       </c>
       <c r="R129" s="18" t="n">
-        <v>1.00474423420066</v>
+        <v>0.999584015462233</v>
       </c>
       <c r="S129" s="19" t="n">
-        <v>1.03723498635555</v>
+        <v>1.03685132846308</v>
       </c>
     </row>
     <row r="130">
@@ -9191,92 +9191,118 @@
         <v>181</v>
       </c>
       <c r="B130" s="2" t="n">
-        <v>9236.94244651634</v>
+        <v>9333.69307463597</v>
       </c>
       <c r="C130" s="3" t="n">
-        <v>9236.94244651634</v>
+        <v>9333.69307463597</v>
       </c>
       <c r="D130" s="4" t="n">
-        <v>9236.94244651634</v>
+        <v>9333.69307463597</v>
       </c>
       <c r="E130" s="5" t="n">
-        <v>9236.94244651634</v>
+        <v>9333.69307463597</v>
       </c>
       <c r="F130" s="6" t="n">
-        <v>1.1418174285341</v>
+        <v>1.16033531979838</v>
       </c>
       <c r="G130" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H130" s="8" t="n">
-        <v>7923.74041025814</v>
+        <v>7782.31615887717</v>
       </c>
       <c r="I130" s="9" t="n">
-        <v>7388.34517541375</v>
+        <v>7403.75466559639</v>
       </c>
       <c r="J130" s="10" t="n">
-        <v>7747.19978582656</v>
+        <v>7666.18926485215</v>
       </c>
       <c r="K130" s="11" t="n">
-        <v>8089.68423119536</v>
+        <v>8043.96187496714</v>
       </c>
       <c r="L130" s="12" t="n">
-        <v>8089.68423119536</v>
+        <v>8043.96187496714</v>
       </c>
       <c r="M130" s="13" t="n">
-        <v>7798.84144456332</v>
+        <v>7753.4708245638</v>
       </c>
       <c r="N130" s="14" t="n">
-        <v>7798.84144456332</v>
+        <v>7753.4708245638</v>
       </c>
       <c r="O130" s="15" t="n">
-        <v>0.0456294272619603</v>
+        <v>0.0382680456154764</v>
       </c>
       <c r="P130" s="16" t="n">
-        <v>0.103497199700821</v>
+        <v>0.0991419185352802</v>
       </c>
       <c r="Q130" s="17" t="n">
-        <v>0.0466864656109616</v>
+        <v>0.0390096975500791</v>
       </c>
       <c r="R130" s="18" t="n">
-        <v>0.984237372853213</v>
+        <v>0.996293476938679</v>
       </c>
       <c r="S130" s="19" t="n">
-        <v>1.05555997444672</v>
+        <v>1.04723497397779</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s">
         <v>182</v>
       </c>
-      <c r="B131" s="2"/>
+      <c r="B131" s="2" t="n">
+        <v>7044.74659185994</v>
+      </c>
       <c r="C131" s="3" t="n">
-        <v>7658.98972803735</v>
+        <v>7044.74659185994</v>
       </c>
       <c r="D131" s="4" t="n">
-        <v>9882.14994851058</v>
+        <v>7044.74659185994</v>
       </c>
       <c r="E131" s="5" t="n">
-        <v>5935.96777622494</v>
+        <v>7044.74659185994</v>
       </c>
       <c r="F131" s="6" t="n">
-        <v>0.929066261033592</v>
-      </c>
-      <c r="G131" s="7"/>
-      <c r="H131" s="8"/>
-      <c r="I131" s="9"/>
-      <c r="J131" s="10"/>
-      <c r="K131" s="11"/>
-      <c r="L131" s="12"/>
-      <c r="M131" s="13"/>
+        <v>0.917917130679584</v>
+      </c>
+      <c r="G131" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H131" s="8" t="n">
+        <v>7788.01439833602</v>
+      </c>
+      <c r="I131" s="9" t="n">
+        <v>7610.40758386268</v>
+      </c>
+      <c r="J131" s="10" t="n">
+        <v>7896.39926756428</v>
+      </c>
+      <c r="K131" s="11" t="n">
+        <v>7674.70870343636</v>
+      </c>
+      <c r="L131" s="12" t="n">
+        <v>7674.70870343636</v>
+      </c>
+      <c r="M131" s="13" t="n">
+        <v>7797.79309394662</v>
+      </c>
       <c r="N131" s="14" t="n">
-        <v>8243.7497186871</v>
-      </c>
-      <c r="O131" s="15"/>
-      <c r="P131" s="16"/>
-      <c r="Q131" s="17"/>
-      <c r="R131" s="18"/>
-      <c r="S131" s="19"/>
+        <v>7797.79309394662</v>
+      </c>
+      <c r="O131" s="15" t="n">
+        <v>0.00570016554596728</v>
+      </c>
+      <c r="P131" s="16" t="n">
+        <v>0.0751608129242929</v>
+      </c>
+      <c r="Q131" s="17" t="n">
+        <v>0.00571644240182101</v>
+      </c>
+      <c r="R131" s="18" t="n">
+        <v>1.00125560831175</v>
+      </c>
+      <c r="S131" s="19" t="n">
+        <v>1.02462226996637</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="s">
@@ -9284,16 +9310,16 @@
       </c>
       <c r="B132" s="2"/>
       <c r="C132" s="3" t="n">
-        <v>8128.35509063935</v>
+        <v>7526.80593582262</v>
       </c>
       <c r="D132" s="4" t="n">
-        <v>11552.520436258</v>
+        <v>9749.37075812489</v>
       </c>
       <c r="E132" s="5" t="n">
-        <v>5719.11184611792</v>
+        <v>5810.91939172808</v>
       </c>
       <c r="F132" s="6" t="n">
-        <v>0.981023807567379</v>
+        <v>0.977452518546331</v>
       </c>
       <c r="G132" s="7"/>
       <c r="H132" s="8"/>
@@ -9303,7 +9329,7 @@
       <c r="L132" s="12"/>
       <c r="M132" s="13"/>
       <c r="N132" s="14" t="n">
-        <v>8285.58392562871</v>
+        <v>7700.43126700057</v>
       </c>
       <c r="O132" s="15"/>
       <c r="P132" s="16"/>
@@ -9317,16 +9343,16 @@
       </c>
       <c r="B133" s="2"/>
       <c r="C133" s="3" t="n">
-        <v>8307.56626156905</v>
+        <v>7645.00371753034</v>
       </c>
       <c r="D133" s="4" t="n">
-        <v>12730.9782207024</v>
+        <v>11022.6758235306</v>
       </c>
       <c r="E133" s="5" t="n">
-        <v>5421.08045382803</v>
+        <v>5302.34969954256</v>
       </c>
       <c r="F133" s="6" t="n">
-        <v>0.944907245427715</v>
+        <v>0.939772229856072</v>
       </c>
       <c r="G133" s="7"/>
       <c r="H133" s="8"/>
@@ -9336,7 +9362,7 @@
       <c r="L133" s="12"/>
       <c r="M133" s="13"/>
       <c r="N133" s="14" t="n">
-        <v>8791.93836407573</v>
+        <v>8134.95384802037</v>
       </c>
       <c r="O133" s="15"/>
       <c r="P133" s="16"/>
@@ -9350,16 +9376,16 @@
       </c>
       <c r="B134" s="2"/>
       <c r="C134" s="3" t="n">
-        <v>9725.02491967474</v>
+        <v>9070.34314865139</v>
       </c>
       <c r="D134" s="4" t="n">
-        <v>15886.5362667497</v>
+        <v>14198.6518193665</v>
       </c>
       <c r="E134" s="5" t="n">
-        <v>5953.22404457926</v>
+        <v>5794.29130884609</v>
       </c>
       <c r="F134" s="6" t="n">
-        <v>1.1482396978931</v>
+        <v>1.16731523396778</v>
       </c>
       <c r="G134" s="7"/>
       <c r="H134" s="8"/>
@@ -9369,7 +9395,7 @@
       <c r="L134" s="12"/>
       <c r="M134" s="13"/>
       <c r="N134" s="14" t="n">
-        <v>8469.50766248471</v>
+        <v>7770.26023880517</v>
       </c>
       <c r="O134" s="15"/>
       <c r="P134" s="16"/>
@@ -9382,10 +9408,18 @@
         <v>186</v>
       </c>
       <c r="B135" s="2"/>
-      <c r="C135" s="3"/>
-      <c r="D135" s="4"/>
-      <c r="E135" s="5"/>
-      <c r="F135" s="6"/>
+      <c r="C135" s="3" t="n">
+        <v>7470.65619792525</v>
+      </c>
+      <c r="D135" s="4" t="n">
+        <v>12534.0229609341</v>
+      </c>
+      <c r="E135" s="5" t="n">
+        <v>4452.73669926641</v>
+      </c>
+      <c r="F135" s="6" t="n">
+        <v>0.916322704427733</v>
+      </c>
       <c r="G135" s="7"/>
       <c r="H135" s="8"/>
       <c r="I135" s="9"/>
@@ -9393,7 +9427,9 @@
       <c r="K135" s="11"/>
       <c r="L135" s="12"/>
       <c r="M135" s="13"/>
-      <c r="N135" s="14"/>
+      <c r="N135" s="14" t="n">
+        <v>8152.8659737738</v>
+      </c>
       <c r="O135" s="15"/>
       <c r="P135" s="16"/>
       <c r="Q135" s="17"/>
@@ -9868,7 +9904,7 @@
         <v>222</v>
       </c>
       <c r="B5" s="1" t="n">
-        <v>-0.0800230812481268</v>
+        <v>-0.0734308336778946</v>
       </c>
     </row>
     <row r="6">
@@ -9876,7 +9912,7 @@
         <v>223</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>0.0268663599897096</v>
+        <v>0.0358453299800551</v>
       </c>
     </row>
     <row r="7">
@@ -9884,7 +9920,7 @@
         <v>224</v>
       </c>
       <c r="B7" s="1" t="n">
-        <v>0.205285041368578</v>
+        <v>0.206822353009034</v>
       </c>
     </row>
     <row r="8">
@@ -9892,7 +9928,7 @@
         <v>225</v>
       </c>
       <c r="B8" s="1" t="n">
-        <v>0.414727493300084</v>
+        <v>0.40733040412779</v>
       </c>
     </row>
     <row r="9">
@@ -9900,7 +9936,7 @@
         <v>226</v>
       </c>
       <c r="B9" s="1" t="n">
-        <v>0.566138820054058</v>
+        <v>0.559220298916463</v>
       </c>
     </row>
     <row r="10">
@@ -9908,7 +9944,7 @@
         <v>227</v>
       </c>
       <c r="B10" s="1" t="n">
-        <v>0.562999802565544</v>
+        <v>0.562395345897271</v>
       </c>
     </row>
     <row r="11">
@@ -9916,7 +9952,7 @@
         <v>228</v>
       </c>
       <c r="B11" s="1" t="n">
-        <v>0.411683231664236</v>
+        <v>0.419538559602286</v>
       </c>
     </row>
     <row r="12">
@@ -9924,7 +9960,7 @@
         <v>229</v>
       </c>
       <c r="B12" s="1" t="n">
-        <v>0.226080937367733</v>
+        <v>0.236395749058776</v>
       </c>
     </row>
     <row r="13">
@@ -9932,7 +9968,7 @@
         <v>230</v>
       </c>
       <c r="B13" s="1" t="n">
-        <v>0.0997382216013041</v>
+        <v>0.105182628470601</v>
       </c>
     </row>
     <row r="14">
@@ -9990,4 +10026,237 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C5B9F2161CEE1040BBC03CB11300495F" ma:contentTypeVersion="12" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="a7cec21613a3259523bdab11a1e26aca">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b5dd4176-d247-4204-85b8-921214f3ccea" xmlns:ns3="359b39ce-e1f9-4933-8424-33b611e6fdcd" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="68943c349d3a016936c8f8cb3335004b" ns2:_="" ns3:_="">
+    <xsd:import namespace="b5dd4176-d247-4204-85b8-921214f3ccea"/>
+    <xsd:import namespace="359b39ce-e1f9-4933-8424-33b611e6fdcd"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="b5dd4176-d247-4204-85b8-921214f3ccea" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Etiquetas de imagen" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="01529062-7a8b-4d76-943d-e0db5644ee6d" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="15" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="16" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="17" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="18" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="19" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="359b39ce-e1f9-4933-8424-33b611e6fdcd" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="14" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{c9b73259-0823-4f05-8927-4a40ee49fbe1}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="359b39ce-e1f9-4933-8424-33b611e6fdcd">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de contenido"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="359b39ce-e1f9-4933-8424-33b611e6fdcd" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b5dd4176-d247-4204-85b8-921214f3ccea">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4182547-153A-40E7-931F-435D2BAA4E29}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8DE7C3D9-B913-40AC-82A8-125A7A86422C}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D868E89-4429-4ED9-B568-9B0B6E9B09CE}"/>
 </file>